--- a/Assets/Excel/Stage.xlsx
+++ b/Assets/Excel/Stage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenBox\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8135003F-F861-496A-9508-8D03A85B4643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E545D60D-A5B0-47AC-9D5C-4E4D14A45084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10725" yWindow="2145" windowWidth="21645" windowHeight="13440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2820" yWindow="825" windowWidth="21645" windowHeight="13440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipment" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="33">
   <si>
     <t>Int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -148,6 +148,22 @@
   </si>
   <si>
     <t>MonsterAvatar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>过关奖励体力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>过关奖励加速道具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RewardEnergy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RewardSpeedUp</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -488,7 +504,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N103"/>
+  <dimension ref="A1:O103"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.25" style="2" customWidth="1"/>
@@ -504,10 +520,12 @@
     <col min="11" max="11" width="8.875" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.25" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="2"/>
+    <col min="14" max="14" width="13.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -547,9 +565,14 @@
       <c r="M1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="N1" s="1"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -589,8 +612,14 @@
       <c r="M2" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -630,8 +659,14 @@
       <c r="M3" s="2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -671,8 +706,14 @@
       <c r="M4" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N4" s="2">
+        <v>10</v>
+      </c>
+      <c r="O4" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -724,8 +765,14 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N5" s="2">
+        <v>11</v>
+      </c>
+      <c r="O5" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -777,8 +824,14 @@
         <f t="shared" ref="M6:M69" si="12">M5</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N6" s="2">
+        <v>12</v>
+      </c>
+      <c r="O6" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -830,8 +883,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N7" s="2">
+        <v>13</v>
+      </c>
+      <c r="O7" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -883,8 +942,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N8" s="2">
+        <v>14</v>
+      </c>
+      <c r="O8" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>6</v>
       </c>
@@ -936,8 +1001,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N9" s="2">
+        <v>15</v>
+      </c>
+      <c r="O9" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>7</v>
       </c>
@@ -989,8 +1060,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N10" s="2">
+        <v>16</v>
+      </c>
+      <c r="O10" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>8</v>
       </c>
@@ -1042,8 +1119,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N11" s="2">
+        <v>17</v>
+      </c>
+      <c r="O11" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>9</v>
       </c>
@@ -1095,8 +1178,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N12" s="2">
+        <v>18</v>
+      </c>
+      <c r="O12" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>10</v>
       </c>
@@ -1148,8 +1237,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="2">
+        <v>19</v>
+      </c>
+      <c r="O13" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>11</v>
       </c>
@@ -1201,8 +1296,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N14" s="2">
+        <v>20</v>
+      </c>
+      <c r="O14" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>12</v>
       </c>
@@ -1254,8 +1355,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N15" s="2">
+        <v>21</v>
+      </c>
+      <c r="O15" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>13</v>
       </c>
@@ -1307,8 +1414,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="2">
+        <v>22</v>
+      </c>
+      <c r="O16" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>14</v>
       </c>
@@ -1360,8 +1473,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="2">
+        <v>23</v>
+      </c>
+      <c r="O17" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>15</v>
       </c>
@@ -1413,8 +1532,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="2">
+        <v>24</v>
+      </c>
+      <c r="O18" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>16</v>
       </c>
@@ -1466,8 +1591,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="2">
+        <v>25</v>
+      </c>
+      <c r="O19" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>17</v>
       </c>
@@ -1519,8 +1650,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="2">
+        <v>26</v>
+      </c>
+      <c r="O20" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>18</v>
       </c>
@@ -1572,8 +1709,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="2">
+        <v>27</v>
+      </c>
+      <c r="O21" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>19</v>
       </c>
@@ -1625,8 +1768,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="2">
+        <v>28</v>
+      </c>
+      <c r="O22" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>20</v>
       </c>
@@ -1678,8 +1827,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="2">
+        <v>29</v>
+      </c>
+      <c r="O23" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>21</v>
       </c>
@@ -1731,8 +1886,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="2">
+        <v>30</v>
+      </c>
+      <c r="O24" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>22</v>
       </c>
@@ -1784,8 +1945,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="2">
+        <v>31</v>
+      </c>
+      <c r="O25" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>23</v>
       </c>
@@ -1837,8 +2004,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="2">
+        <v>32</v>
+      </c>
+      <c r="O26" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>24</v>
       </c>
@@ -1890,8 +2063,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="2">
+        <v>33</v>
+      </c>
+      <c r="O27" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>25</v>
       </c>
@@ -1943,8 +2122,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="2">
+        <v>34</v>
+      </c>
+      <c r="O28" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>26</v>
       </c>
@@ -1996,8 +2181,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="2">
+        <v>35</v>
+      </c>
+      <c r="O29" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>27</v>
       </c>
@@ -2049,8 +2240,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="2">
+        <v>36</v>
+      </c>
+      <c r="O30" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>28</v>
       </c>
@@ -2102,8 +2299,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="2">
+        <v>37</v>
+      </c>
+      <c r="O31" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>29</v>
       </c>
@@ -2155,8 +2358,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="2">
+        <v>38</v>
+      </c>
+      <c r="O32" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>30</v>
       </c>
@@ -2208,8 +2417,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="2">
+        <v>39</v>
+      </c>
+      <c r="O33" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>31</v>
       </c>
@@ -2261,8 +2476,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="2">
+        <v>40</v>
+      </c>
+      <c r="O34" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>32</v>
       </c>
@@ -2314,8 +2535,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="2">
+        <v>41</v>
+      </c>
+      <c r="O35" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>33</v>
       </c>
@@ -2367,8 +2594,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N36" s="2">
+        <v>42</v>
+      </c>
+      <c r="O36" s="2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>34</v>
       </c>
@@ -2420,8 +2653,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N37" s="2">
+        <v>43</v>
+      </c>
+      <c r="O37" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>35</v>
       </c>
@@ -2473,8 +2712,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N38" s="2">
+        <v>44</v>
+      </c>
+      <c r="O38" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>36</v>
       </c>
@@ -2526,8 +2771,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="2">
+        <v>45</v>
+      </c>
+      <c r="O39" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>37</v>
       </c>
@@ -2579,8 +2830,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="2">
+        <v>46</v>
+      </c>
+      <c r="O40" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>38</v>
       </c>
@@ -2632,8 +2889,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="2">
+        <v>47</v>
+      </c>
+      <c r="O41" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>39</v>
       </c>
@@ -2685,8 +2948,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="2">
+        <v>48</v>
+      </c>
+      <c r="O42" s="2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>40</v>
       </c>
@@ -2738,8 +3007,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="2">
+        <v>49</v>
+      </c>
+      <c r="O43" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>41</v>
       </c>
@@ -2791,8 +3066,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="2">
+        <v>50</v>
+      </c>
+      <c r="O44" s="2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>42</v>
       </c>
@@ -2844,8 +3125,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="2">
+        <v>51</v>
+      </c>
+      <c r="O45" s="2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>43</v>
       </c>
@@ -2897,8 +3184,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="2">
+        <v>52</v>
+      </c>
+      <c r="O46" s="2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>44</v>
       </c>
@@ -2950,8 +3243,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="2">
+        <v>53</v>
+      </c>
+      <c r="O47" s="2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <v>45</v>
       </c>
@@ -3003,8 +3302,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="2">
+        <v>54</v>
+      </c>
+      <c r="O48" s="2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <v>46</v>
       </c>
@@ -3056,8 +3361,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="2">
+        <v>55</v>
+      </c>
+      <c r="O49" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
         <v>47</v>
       </c>
@@ -3109,8 +3420,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="2">
+        <v>56</v>
+      </c>
+      <c r="O50" s="2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
         <v>48</v>
       </c>
@@ -3162,8 +3479,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="2">
+        <v>57</v>
+      </c>
+      <c r="O51" s="2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
         <v>49</v>
       </c>
@@ -3215,8 +3538,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="2">
+        <v>58</v>
+      </c>
+      <c r="O52" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
         <v>50</v>
       </c>
@@ -3268,8 +3597,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="2">
+        <v>59</v>
+      </c>
+      <c r="O53" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
         <v>51</v>
       </c>
@@ -3321,8 +3656,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="2">
+        <v>60</v>
+      </c>
+      <c r="O54" s="2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
         <v>52</v>
       </c>
@@ -3374,8 +3715,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="2">
+        <v>61</v>
+      </c>
+      <c r="O55" s="2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
         <v>53</v>
       </c>
@@ -3427,8 +3774,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="2">
+        <v>62</v>
+      </c>
+      <c r="O56" s="2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
         <v>54</v>
       </c>
@@ -3480,8 +3833,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="2">
+        <v>63</v>
+      </c>
+      <c r="O57" s="2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
         <v>55</v>
       </c>
@@ -3533,8 +3892,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="2">
+        <v>64</v>
+      </c>
+      <c r="O58" s="2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
         <v>56</v>
       </c>
@@ -3586,8 +3951,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="2">
+        <v>65</v>
+      </c>
+      <c r="O59" s="2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
         <v>57</v>
       </c>
@@ -3639,8 +4010,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="2">
+        <v>66</v>
+      </c>
+      <c r="O60" s="2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
         <v>58</v>
       </c>
@@ -3692,8 +4069,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="2">
+        <v>67</v>
+      </c>
+      <c r="O61" s="2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
         <v>59</v>
       </c>
@@ -3745,8 +4128,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="2">
+        <v>68</v>
+      </c>
+      <c r="O62" s="2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
         <v>60</v>
       </c>
@@ -3798,8 +4187,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="2">
+        <v>69</v>
+      </c>
+      <c r="O63" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
         <v>61</v>
       </c>
@@ -3851,8 +4246,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="2">
+        <v>70</v>
+      </c>
+      <c r="O64" s="2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
         <v>62</v>
       </c>
@@ -3904,8 +4305,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="2">
+        <v>71</v>
+      </c>
+      <c r="O65" s="2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
         <v>63</v>
       </c>
@@ -3957,8 +4364,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="2">
+        <v>72</v>
+      </c>
+      <c r="O66" s="2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
         <v>64</v>
       </c>
@@ -4010,8 +4423,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="2">
+        <v>73</v>
+      </c>
+      <c r="O67" s="2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
         <v>65</v>
       </c>
@@ -4063,8 +4482,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="2">
+        <v>74</v>
+      </c>
+      <c r="O68" s="2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
         <v>66</v>
       </c>
@@ -4116,8 +4541,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="2">
+        <v>75</v>
+      </c>
+      <c r="O69" s="2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
         <v>67</v>
       </c>
@@ -4169,8 +4600,14 @@
         <f t="shared" ref="M70:M103" si="24">M69</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="2">
+        <v>76</v>
+      </c>
+      <c r="O70" s="2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
         <v>68</v>
       </c>
@@ -4222,8 +4659,14 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="2">
+        <v>77</v>
+      </c>
+      <c r="O71" s="2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
         <v>69</v>
       </c>
@@ -4275,8 +4718,14 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="2">
+        <v>78</v>
+      </c>
+      <c r="O72" s="2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
         <v>70</v>
       </c>
@@ -4328,8 +4777,14 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="2">
+        <v>79</v>
+      </c>
+      <c r="O73" s="2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
         <v>71</v>
       </c>
@@ -4381,8 +4836,14 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="2">
+        <v>80</v>
+      </c>
+      <c r="O74" s="2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
         <v>72</v>
       </c>
@@ -4434,8 +4895,14 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="2">
+        <v>81</v>
+      </c>
+      <c r="O75" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
         <v>73</v>
       </c>
@@ -4487,8 +4954,14 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="2">
+        <v>82</v>
+      </c>
+      <c r="O76" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
         <v>74</v>
       </c>
@@ -4540,8 +5013,14 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="2">
+        <v>83</v>
+      </c>
+      <c r="O77" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
         <v>75</v>
       </c>
@@ -4593,8 +5072,14 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N78" s="2">
+        <v>84</v>
+      </c>
+      <c r="O78" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
         <v>76</v>
       </c>
@@ -4646,8 +5131,14 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N79" s="2">
+        <v>85</v>
+      </c>
+      <c r="O79" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
         <v>77</v>
       </c>
@@ -4699,8 +5190,14 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N80" s="2">
+        <v>86</v>
+      </c>
+      <c r="O80" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
         <v>78</v>
       </c>
@@ -4752,8 +5249,14 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="2">
+        <v>87</v>
+      </c>
+      <c r="O81" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
         <v>79</v>
       </c>
@@ -4805,8 +5308,14 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="2">
+        <v>88</v>
+      </c>
+      <c r="O82" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
         <v>80</v>
       </c>
@@ -4858,8 +5367,14 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="2">
+        <v>89</v>
+      </c>
+      <c r="O83" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
         <v>81</v>
       </c>
@@ -4911,8 +5426,14 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="2">
+        <v>90</v>
+      </c>
+      <c r="O84" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
         <v>82</v>
       </c>
@@ -4964,8 +5485,14 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="2">
+        <v>91</v>
+      </c>
+      <c r="O85" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
         <v>83</v>
       </c>
@@ -5017,8 +5544,14 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="2">
+        <v>92</v>
+      </c>
+      <c r="O86" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
         <v>84</v>
       </c>
@@ -5070,8 +5603,14 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="2">
+        <v>93</v>
+      </c>
+      <c r="O87" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
         <v>85</v>
       </c>
@@ -5123,8 +5662,14 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="2">
+        <v>94</v>
+      </c>
+      <c r="O88" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
         <v>86</v>
       </c>
@@ -5176,8 +5721,14 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="2">
+        <v>95</v>
+      </c>
+      <c r="O89" s="2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
         <v>87</v>
       </c>
@@ -5229,8 +5780,14 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="2">
+        <v>96</v>
+      </c>
+      <c r="O90" s="2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
         <v>88</v>
       </c>
@@ -5282,8 +5839,14 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="2">
+        <v>97</v>
+      </c>
+      <c r="O91" s="2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
         <v>89</v>
       </c>
@@ -5335,8 +5898,14 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="2">
+        <v>98</v>
+      </c>
+      <c r="O92" s="2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
         <v>90</v>
       </c>
@@ -5388,8 +5957,14 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="2">
+        <v>99</v>
+      </c>
+      <c r="O93" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
         <v>91</v>
       </c>
@@ -5441,8 +6016,14 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="2">
+        <v>100</v>
+      </c>
+      <c r="O94" s="2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
         <v>92</v>
       </c>
@@ -5494,8 +6075,14 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="2">
+        <v>101</v>
+      </c>
+      <c r="O95" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
         <v>93</v>
       </c>
@@ -5547,8 +6134,14 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="2">
+        <v>102</v>
+      </c>
+      <c r="O96" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
         <v>94</v>
       </c>
@@ -5600,8 +6193,14 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="2">
+        <v>103</v>
+      </c>
+      <c r="O97" s="2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
         <v>95</v>
       </c>
@@ -5653,8 +6252,14 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="2">
+        <v>104</v>
+      </c>
+      <c r="O98" s="2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
         <v>96</v>
       </c>
@@ -5706,8 +6311,14 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="2">
+        <v>105</v>
+      </c>
+      <c r="O99" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
         <v>97</v>
       </c>
@@ -5759,8 +6370,14 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="2">
+        <v>106</v>
+      </c>
+      <c r="O100" s="2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
         <v>98</v>
       </c>
@@ -5812,8 +6429,14 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="2">
+        <v>107</v>
+      </c>
+      <c r="O101" s="2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
         <v>99</v>
       </c>
@@ -5865,8 +6488,14 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N102" s="2">
+        <v>108</v>
+      </c>
+      <c r="O102" s="2">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
         <v>100</v>
       </c>
@@ -5917,6 +6546,12 @@
       <c r="M103" s="2">
         <f t="shared" si="24"/>
         <v>0</v>
+      </c>
+      <c r="N103" s="2">
+        <v>109</v>
+      </c>
+      <c r="O103" s="2">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excel/Stage.xlsx
+++ b/Assets/Excel/Stage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenBox\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E545D60D-A5B0-47AC-9D5C-4E4D14A45084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{819691D6-694C-4A34-8934-22069BE15743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2820" yWindow="825" windowWidth="21645" windowHeight="13440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipment" sheetId="1" r:id="rId1"/>
@@ -704,7 +704,7 @@
         <v>10</v>
       </c>
       <c r="M4" s="2">
-        <v>0</v>
+        <v>1001</v>
       </c>
       <c r="N4" s="2">
         <v>10</v>
@@ -762,8 +762,7 @@
         <v>10</v>
       </c>
       <c r="M5" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1002</v>
       </c>
       <c r="N5" s="2">
         <v>11</v>
@@ -821,8 +820,7 @@
         <v>10</v>
       </c>
       <c r="M6" s="2">
-        <f t="shared" ref="M6:M69" si="12">M5</f>
-        <v>0</v>
+        <v>1003</v>
       </c>
       <c r="N6" s="2">
         <v>12</v>
@@ -880,8 +878,7 @@
         <v>10</v>
       </c>
       <c r="M7" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1004</v>
       </c>
       <c r="N7" s="2">
         <v>13</v>
@@ -939,8 +936,7 @@
         <v>10</v>
       </c>
       <c r="M8" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1005</v>
       </c>
       <c r="N8" s="2">
         <v>14</v>
@@ -998,8 +994,7 @@
         <v>10</v>
       </c>
       <c r="M9" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1006</v>
       </c>
       <c r="N9" s="2">
         <v>15</v>
@@ -1057,8 +1052,7 @@
         <v>10</v>
       </c>
       <c r="M10" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1007</v>
       </c>
       <c r="N10" s="2">
         <v>16</v>
@@ -1116,8 +1110,7 @@
         <v>10</v>
       </c>
       <c r="M11" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="N11" s="2">
         <v>17</v>
@@ -1175,8 +1168,7 @@
         <v>10</v>
       </c>
       <c r="M12" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1009</v>
       </c>
       <c r="N12" s="2">
         <v>18</v>
@@ -1234,8 +1226,7 @@
         <v>10</v>
       </c>
       <c r="M13" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1010</v>
       </c>
       <c r="N13" s="2">
         <v>19</v>
@@ -1293,8 +1284,7 @@
         <v>10</v>
       </c>
       <c r="M14" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1011</v>
       </c>
       <c r="N14" s="2">
         <v>20</v>
@@ -1352,8 +1342,7 @@
         <v>10</v>
       </c>
       <c r="M15" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1012</v>
       </c>
       <c r="N15" s="2">
         <v>21</v>
@@ -1411,8 +1400,7 @@
         <v>10</v>
       </c>
       <c r="M16" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1013</v>
       </c>
       <c r="N16" s="2">
         <v>22</v>
@@ -1470,8 +1458,7 @@
         <v>10</v>
       </c>
       <c r="M17" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1014</v>
       </c>
       <c r="N17" s="2">
         <v>23</v>
@@ -1529,8 +1516,7 @@
         <v>10</v>
       </c>
       <c r="M18" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1015</v>
       </c>
       <c r="N18" s="2">
         <v>24</v>
@@ -1588,8 +1574,7 @@
         <v>10</v>
       </c>
       <c r="M19" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1016</v>
       </c>
       <c r="N19" s="2">
         <v>25</v>
@@ -1647,8 +1632,7 @@
         <v>10</v>
       </c>
       <c r="M20" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1017</v>
       </c>
       <c r="N20" s="2">
         <v>26</v>
@@ -1706,8 +1690,7 @@
         <v>10</v>
       </c>
       <c r="M21" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1018</v>
       </c>
       <c r="N21" s="2">
         <v>27</v>
@@ -1765,8 +1748,7 @@
         <v>10</v>
       </c>
       <c r="M22" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1019</v>
       </c>
       <c r="N22" s="2">
         <v>28</v>
@@ -1824,8 +1806,7 @@
         <v>10</v>
       </c>
       <c r="M23" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1020</v>
       </c>
       <c r="N23" s="2">
         <v>29</v>
@@ -1883,8 +1864,7 @@
         <v>10</v>
       </c>
       <c r="M24" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1001</v>
       </c>
       <c r="N24" s="2">
         <v>30</v>
@@ -1942,8 +1922,7 @@
         <v>10</v>
       </c>
       <c r="M25" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1002</v>
       </c>
       <c r="N25" s="2">
         <v>31</v>
@@ -2001,8 +1980,7 @@
         <v>10</v>
       </c>
       <c r="M26" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1003</v>
       </c>
       <c r="N26" s="2">
         <v>32</v>
@@ -2060,8 +2038,7 @@
         <v>10</v>
       </c>
       <c r="M27" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1004</v>
       </c>
       <c r="N27" s="2">
         <v>33</v>
@@ -2119,8 +2096,7 @@
         <v>10</v>
       </c>
       <c r="M28" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1005</v>
       </c>
       <c r="N28" s="2">
         <v>34</v>
@@ -2178,8 +2154,7 @@
         <v>10</v>
       </c>
       <c r="M29" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1006</v>
       </c>
       <c r="N29" s="2">
         <v>35</v>
@@ -2237,8 +2212,7 @@
         <v>10</v>
       </c>
       <c r="M30" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1007</v>
       </c>
       <c r="N30" s="2">
         <v>36</v>
@@ -2296,8 +2270,7 @@
         <v>10</v>
       </c>
       <c r="M31" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="N31" s="2">
         <v>37</v>
@@ -2355,8 +2328,7 @@
         <v>10</v>
       </c>
       <c r="M32" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1009</v>
       </c>
       <c r="N32" s="2">
         <v>38</v>
@@ -2414,8 +2386,7 @@
         <v>10</v>
       </c>
       <c r="M33" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1010</v>
       </c>
       <c r="N33" s="2">
         <v>39</v>
@@ -2473,8 +2444,7 @@
         <v>10</v>
       </c>
       <c r="M34" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1011</v>
       </c>
       <c r="N34" s="2">
         <v>40</v>
@@ -2532,8 +2502,7 @@
         <v>10</v>
       </c>
       <c r="M35" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1012</v>
       </c>
       <c r="N35" s="2">
         <v>41</v>
@@ -2591,8 +2560,7 @@
         <v>10</v>
       </c>
       <c r="M36" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1013</v>
       </c>
       <c r="N36" s="2">
         <v>42</v>
@@ -2650,8 +2618,7 @@
         <v>10</v>
       </c>
       <c r="M37" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1014</v>
       </c>
       <c r="N37" s="2">
         <v>43</v>
@@ -2709,8 +2676,7 @@
         <v>10</v>
       </c>
       <c r="M38" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1015</v>
       </c>
       <c r="N38" s="2">
         <v>44</v>
@@ -2768,8 +2734,7 @@
         <v>10</v>
       </c>
       <c r="M39" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1016</v>
       </c>
       <c r="N39" s="2">
         <v>45</v>
@@ -2827,8 +2792,7 @@
         <v>10</v>
       </c>
       <c r="M40" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1017</v>
       </c>
       <c r="N40" s="2">
         <v>46</v>
@@ -2886,8 +2850,7 @@
         <v>10</v>
       </c>
       <c r="M41" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1018</v>
       </c>
       <c r="N41" s="2">
         <v>47</v>
@@ -2945,8 +2908,7 @@
         <v>10</v>
       </c>
       <c r="M42" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1019</v>
       </c>
       <c r="N42" s="2">
         <v>48</v>
@@ -3004,8 +2966,7 @@
         <v>10</v>
       </c>
       <c r="M43" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1020</v>
       </c>
       <c r="N43" s="2">
         <v>49</v>
@@ -3063,8 +3024,7 @@
         <v>10</v>
       </c>
       <c r="M44" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1001</v>
       </c>
       <c r="N44" s="2">
         <v>50</v>
@@ -3122,8 +3082,7 @@
         <v>10</v>
       </c>
       <c r="M45" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1002</v>
       </c>
       <c r="N45" s="2">
         <v>51</v>
@@ -3181,8 +3140,7 @@
         <v>10</v>
       </c>
       <c r="M46" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1003</v>
       </c>
       <c r="N46" s="2">
         <v>52</v>
@@ -3240,8 +3198,7 @@
         <v>10</v>
       </c>
       <c r="M47" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1004</v>
       </c>
       <c r="N47" s="2">
         <v>53</v>
@@ -3299,8 +3256,7 @@
         <v>10</v>
       </c>
       <c r="M48" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1005</v>
       </c>
       <c r="N48" s="2">
         <v>54</v>
@@ -3358,8 +3314,7 @@
         <v>10</v>
       </c>
       <c r="M49" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1006</v>
       </c>
       <c r="N49" s="2">
         <v>55</v>
@@ -3417,8 +3372,7 @@
         <v>10</v>
       </c>
       <c r="M50" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1007</v>
       </c>
       <c r="N50" s="2">
         <v>56</v>
@@ -3476,8 +3430,7 @@
         <v>10</v>
       </c>
       <c r="M51" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="N51" s="2">
         <v>57</v>
@@ -3535,8 +3488,7 @@
         <v>10</v>
       </c>
       <c r="M52" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1009</v>
       </c>
       <c r="N52" s="2">
         <v>58</v>
@@ -3594,8 +3546,7 @@
         <v>10</v>
       </c>
       <c r="M53" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1010</v>
       </c>
       <c r="N53" s="2">
         <v>59</v>
@@ -3653,8 +3604,7 @@
         <v>10</v>
       </c>
       <c r="M54" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1011</v>
       </c>
       <c r="N54" s="2">
         <v>60</v>
@@ -3712,8 +3662,7 @@
         <v>10</v>
       </c>
       <c r="M55" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1012</v>
       </c>
       <c r="N55" s="2">
         <v>61</v>
@@ -3771,8 +3720,7 @@
         <v>10</v>
       </c>
       <c r="M56" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1013</v>
       </c>
       <c r="N56" s="2">
         <v>62</v>
@@ -3830,8 +3778,7 @@
         <v>10</v>
       </c>
       <c r="M57" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1014</v>
       </c>
       <c r="N57" s="2">
         <v>63</v>
@@ -3889,8 +3836,7 @@
         <v>10</v>
       </c>
       <c r="M58" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1015</v>
       </c>
       <c r="N58" s="2">
         <v>64</v>
@@ -3948,8 +3894,7 @@
         <v>10</v>
       </c>
       <c r="M59" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1016</v>
       </c>
       <c r="N59" s="2">
         <v>65</v>
@@ -4007,8 +3952,7 @@
         <v>10</v>
       </c>
       <c r="M60" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1017</v>
       </c>
       <c r="N60" s="2">
         <v>66</v>
@@ -4066,8 +4010,7 @@
         <v>10</v>
       </c>
       <c r="M61" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1018</v>
       </c>
       <c r="N61" s="2">
         <v>67</v>
@@ -4125,8 +4068,7 @@
         <v>10</v>
       </c>
       <c r="M62" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1019</v>
       </c>
       <c r="N62" s="2">
         <v>68</v>
@@ -4184,8 +4126,7 @@
         <v>10</v>
       </c>
       <c r="M63" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1020</v>
       </c>
       <c r="N63" s="2">
         <v>69</v>
@@ -4243,8 +4184,7 @@
         <v>10</v>
       </c>
       <c r="M64" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1001</v>
       </c>
       <c r="N64" s="2">
         <v>70</v>
@@ -4302,8 +4242,7 @@
         <v>10</v>
       </c>
       <c r="M65" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1002</v>
       </c>
       <c r="N65" s="2">
         <v>71</v>
@@ -4361,8 +4300,7 @@
         <v>10</v>
       </c>
       <c r="M66" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1003</v>
       </c>
       <c r="N66" s="2">
         <v>72</v>
@@ -4420,8 +4358,7 @@
         <v>10</v>
       </c>
       <c r="M67" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1004</v>
       </c>
       <c r="N67" s="2">
         <v>73</v>
@@ -4479,8 +4416,7 @@
         <v>10</v>
       </c>
       <c r="M68" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1005</v>
       </c>
       <c r="N68" s="2">
         <v>74</v>
@@ -4538,8 +4474,7 @@
         <v>10</v>
       </c>
       <c r="M69" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1006</v>
       </c>
       <c r="N69" s="2">
         <v>75</v>
@@ -4553,52 +4488,51 @@
         <v>67</v>
       </c>
       <c r="B70" s="2">
-        <f t="shared" ref="B70:B103" si="13">B69+5</f>
+        <f t="shared" ref="B70:B103" si="12">B69+5</f>
         <v>360</v>
       </c>
       <c r="C70" s="2">
-        <f t="shared" ref="C70:C103" si="14">C69+3</f>
+        <f t="shared" ref="C70:C103" si="13">C69+3</f>
         <v>203</v>
       </c>
       <c r="D70" s="2">
-        <f t="shared" ref="D70:D103" si="15">D69+120</f>
+        <f t="shared" ref="D70:D103" si="14">D69+120</f>
         <v>9120</v>
       </c>
       <c r="E70" s="2">
-        <f t="shared" ref="E70:E103" si="16">E69+2</f>
+        <f t="shared" ref="E70:E103" si="15">E69+2</f>
         <v>142</v>
       </c>
       <c r="F70" s="2">
-        <f t="shared" ref="F70:F103" si="17">F69</f>
+        <f t="shared" ref="F70:F103" si="16">F69</f>
         <v>5</v>
       </c>
       <c r="G70" s="2">
-        <f t="shared" ref="G70:G103" si="18">G69</f>
+        <f t="shared" ref="G70:G103" si="17">G69</f>
         <v>100</v>
       </c>
       <c r="H70" s="2">
-        <f t="shared" ref="H70:H103" si="19">H69</f>
+        <f t="shared" ref="H70:H103" si="18">H69</f>
         <v>10</v>
       </c>
       <c r="I70" s="2">
-        <f t="shared" ref="I70:I103" si="20">I69</f>
+        <f t="shared" ref="I70:I103" si="19">I69</f>
         <v>10</v>
       </c>
       <c r="J70" s="2">
-        <f t="shared" ref="J70:J103" si="21">J69</f>
+        <f t="shared" ref="J70:J103" si="20">J69</f>
         <v>10</v>
       </c>
       <c r="K70" s="2">
-        <f t="shared" ref="K70:K103" si="22">K69</f>
+        <f t="shared" ref="K70:K103" si="21">K69</f>
         <v>10</v>
       </c>
       <c r="L70" s="2">
-        <f t="shared" ref="L70:L103" si="23">L69</f>
+        <f t="shared" ref="L70:L103" si="22">L69</f>
         <v>10</v>
       </c>
       <c r="M70" s="2">
-        <f t="shared" ref="M70:M103" si="24">M69</f>
-        <v>0</v>
+        <v>1007</v>
       </c>
       <c r="N70" s="2">
         <v>76</v>
@@ -4612,52 +4546,51 @@
         <v>68</v>
       </c>
       <c r="B71" s="2">
+        <f t="shared" si="12"/>
+        <v>365</v>
+      </c>
+      <c r="C71" s="2">
         <f t="shared" si="13"/>
-        <v>365</v>
-      </c>
-      <c r="C71" s="2">
+        <v>206</v>
+      </c>
+      <c r="D71" s="2">
         <f t="shared" si="14"/>
-        <v>206</v>
-      </c>
-      <c r="D71" s="2">
+        <v>9240</v>
+      </c>
+      <c r="E71" s="2">
         <f t="shared" si="15"/>
-        <v>9240</v>
-      </c>
-      <c r="E71" s="2">
+        <v>144</v>
+      </c>
+      <c r="F71" s="2">
         <f t="shared" si="16"/>
-        <v>144</v>
-      </c>
-      <c r="F71" s="2">
+        <v>5</v>
+      </c>
+      <c r="G71" s="2">
         <f t="shared" si="17"/>
-        <v>5</v>
-      </c>
-      <c r="G71" s="2">
+        <v>100</v>
+      </c>
+      <c r="H71" s="2">
         <f t="shared" si="18"/>
-        <v>100</v>
-      </c>
-      <c r="H71" s="2">
+        <v>10</v>
+      </c>
+      <c r="I71" s="2">
         <f t="shared" si="19"/>
         <v>10</v>
       </c>
-      <c r="I71" s="2">
+      <c r="J71" s="2">
         <f t="shared" si="20"/>
         <v>10</v>
       </c>
-      <c r="J71" s="2">
+      <c r="K71" s="2">
         <f t="shared" si="21"/>
         <v>10</v>
       </c>
-      <c r="K71" s="2">
+      <c r="L71" s="2">
         <f t="shared" si="22"/>
         <v>10</v>
       </c>
-      <c r="L71" s="2">
-        <f t="shared" si="23"/>
-        <v>10</v>
-      </c>
       <c r="M71" s="2">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="N71" s="2">
         <v>77</v>
@@ -4671,52 +4604,51 @@
         <v>69</v>
       </c>
       <c r="B72" s="2">
+        <f t="shared" si="12"/>
+        <v>370</v>
+      </c>
+      <c r="C72" s="2">
         <f t="shared" si="13"/>
-        <v>370</v>
-      </c>
-      <c r="C72" s="2">
+        <v>209</v>
+      </c>
+      <c r="D72" s="2">
         <f t="shared" si="14"/>
-        <v>209</v>
-      </c>
-      <c r="D72" s="2">
+        <v>9360</v>
+      </c>
+      <c r="E72" s="2">
         <f t="shared" si="15"/>
-        <v>9360</v>
-      </c>
-      <c r="E72" s="2">
+        <v>146</v>
+      </c>
+      <c r="F72" s="2">
         <f t="shared" si="16"/>
-        <v>146</v>
-      </c>
-      <c r="F72" s="2">
+        <v>5</v>
+      </c>
+      <c r="G72" s="2">
         <f t="shared" si="17"/>
-        <v>5</v>
-      </c>
-      <c r="G72" s="2">
+        <v>100</v>
+      </c>
+      <c r="H72" s="2">
         <f t="shared" si="18"/>
-        <v>100</v>
-      </c>
-      <c r="H72" s="2">
+        <v>10</v>
+      </c>
+      <c r="I72" s="2">
         <f t="shared" si="19"/>
         <v>10</v>
       </c>
-      <c r="I72" s="2">
+      <c r="J72" s="2">
         <f t="shared" si="20"/>
         <v>10</v>
       </c>
-      <c r="J72" s="2">
+      <c r="K72" s="2">
         <f t="shared" si="21"/>
         <v>10</v>
       </c>
-      <c r="K72" s="2">
+      <c r="L72" s="2">
         <f t="shared" si="22"/>
         <v>10</v>
       </c>
-      <c r="L72" s="2">
-        <f t="shared" si="23"/>
-        <v>10</v>
-      </c>
       <c r="M72" s="2">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1009</v>
       </c>
       <c r="N72" s="2">
         <v>78</v>
@@ -4730,52 +4662,51 @@
         <v>70</v>
       </c>
       <c r="B73" s="2">
+        <f t="shared" si="12"/>
+        <v>375</v>
+      </c>
+      <c r="C73" s="2">
         <f t="shared" si="13"/>
-        <v>375</v>
-      </c>
-      <c r="C73" s="2">
+        <v>212</v>
+      </c>
+      <c r="D73" s="2">
         <f t="shared" si="14"/>
-        <v>212</v>
-      </c>
-      <c r="D73" s="2">
+        <v>9480</v>
+      </c>
+      <c r="E73" s="2">
         <f t="shared" si="15"/>
-        <v>9480</v>
-      </c>
-      <c r="E73" s="2">
+        <v>148</v>
+      </c>
+      <c r="F73" s="2">
         <f t="shared" si="16"/>
-        <v>148</v>
-      </c>
-      <c r="F73" s="2">
+        <v>5</v>
+      </c>
+      <c r="G73" s="2">
         <f t="shared" si="17"/>
-        <v>5</v>
-      </c>
-      <c r="G73" s="2">
+        <v>100</v>
+      </c>
+      <c r="H73" s="2">
         <f t="shared" si="18"/>
-        <v>100</v>
-      </c>
-      <c r="H73" s="2">
+        <v>10</v>
+      </c>
+      <c r="I73" s="2">
         <f t="shared" si="19"/>
         <v>10</v>
       </c>
-      <c r="I73" s="2">
+      <c r="J73" s="2">
         <f t="shared" si="20"/>
         <v>10</v>
       </c>
-      <c r="J73" s="2">
+      <c r="K73" s="2">
         <f t="shared" si="21"/>
         <v>10</v>
       </c>
-      <c r="K73" s="2">
+      <c r="L73" s="2">
         <f t="shared" si="22"/>
         <v>10</v>
       </c>
-      <c r="L73" s="2">
-        <f t="shared" si="23"/>
-        <v>10</v>
-      </c>
       <c r="M73" s="2">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1010</v>
       </c>
       <c r="N73" s="2">
         <v>79</v>
@@ -4789,52 +4720,51 @@
         <v>71</v>
       </c>
       <c r="B74" s="2">
+        <f t="shared" si="12"/>
+        <v>380</v>
+      </c>
+      <c r="C74" s="2">
         <f t="shared" si="13"/>
-        <v>380</v>
-      </c>
-      <c r="C74" s="2">
+        <v>215</v>
+      </c>
+      <c r="D74" s="2">
         <f t="shared" si="14"/>
-        <v>215</v>
-      </c>
-      <c r="D74" s="2">
+        <v>9600</v>
+      </c>
+      <c r="E74" s="2">
         <f t="shared" si="15"/>
-        <v>9600</v>
-      </c>
-      <c r="E74" s="2">
+        <v>150</v>
+      </c>
+      <c r="F74" s="2">
         <f t="shared" si="16"/>
-        <v>150</v>
-      </c>
-      <c r="F74" s="2">
+        <v>5</v>
+      </c>
+      <c r="G74" s="2">
         <f t="shared" si="17"/>
-        <v>5</v>
-      </c>
-      <c r="G74" s="2">
+        <v>100</v>
+      </c>
+      <c r="H74" s="2">
         <f t="shared" si="18"/>
-        <v>100</v>
-      </c>
-      <c r="H74" s="2">
+        <v>10</v>
+      </c>
+      <c r="I74" s="2">
         <f t="shared" si="19"/>
         <v>10</v>
       </c>
-      <c r="I74" s="2">
+      <c r="J74" s="2">
         <f t="shared" si="20"/>
         <v>10</v>
       </c>
-      <c r="J74" s="2">
+      <c r="K74" s="2">
         <f t="shared" si="21"/>
         <v>10</v>
       </c>
-      <c r="K74" s="2">
+      <c r="L74" s="2">
         <f t="shared" si="22"/>
         <v>10</v>
       </c>
-      <c r="L74" s="2">
-        <f t="shared" si="23"/>
-        <v>10</v>
-      </c>
       <c r="M74" s="2">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1011</v>
       </c>
       <c r="N74" s="2">
         <v>80</v>
@@ -4848,52 +4778,51 @@
         <v>72</v>
       </c>
       <c r="B75" s="2">
+        <f t="shared" si="12"/>
+        <v>385</v>
+      </c>
+      <c r="C75" s="2">
         <f t="shared" si="13"/>
-        <v>385</v>
-      </c>
-      <c r="C75" s="2">
+        <v>218</v>
+      </c>
+      <c r="D75" s="2">
         <f t="shared" si="14"/>
-        <v>218</v>
-      </c>
-      <c r="D75" s="2">
+        <v>9720</v>
+      </c>
+      <c r="E75" s="2">
         <f t="shared" si="15"/>
-        <v>9720</v>
-      </c>
-      <c r="E75" s="2">
+        <v>152</v>
+      </c>
+      <c r="F75" s="2">
         <f t="shared" si="16"/>
-        <v>152</v>
-      </c>
-      <c r="F75" s="2">
+        <v>5</v>
+      </c>
+      <c r="G75" s="2">
         <f t="shared" si="17"/>
-        <v>5</v>
-      </c>
-      <c r="G75" s="2">
+        <v>100</v>
+      </c>
+      <c r="H75" s="2">
         <f t="shared" si="18"/>
-        <v>100</v>
-      </c>
-      <c r="H75" s="2">
+        <v>10</v>
+      </c>
+      <c r="I75" s="2">
         <f t="shared" si="19"/>
         <v>10</v>
       </c>
-      <c r="I75" s="2">
+      <c r="J75" s="2">
         <f t="shared" si="20"/>
         <v>10</v>
       </c>
-      <c r="J75" s="2">
+      <c r="K75" s="2">
         <f t="shared" si="21"/>
         <v>10</v>
       </c>
-      <c r="K75" s="2">
+      <c r="L75" s="2">
         <f t="shared" si="22"/>
         <v>10</v>
       </c>
-      <c r="L75" s="2">
-        <f t="shared" si="23"/>
-        <v>10</v>
-      </c>
       <c r="M75" s="2">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1012</v>
       </c>
       <c r="N75" s="2">
         <v>81</v>
@@ -4907,52 +4836,51 @@
         <v>73</v>
       </c>
       <c r="B76" s="2">
+        <f t="shared" si="12"/>
+        <v>390</v>
+      </c>
+      <c r="C76" s="2">
         <f t="shared" si="13"/>
-        <v>390</v>
-      </c>
-      <c r="C76" s="2">
+        <v>221</v>
+      </c>
+      <c r="D76" s="2">
         <f t="shared" si="14"/>
-        <v>221</v>
-      </c>
-      <c r="D76" s="2">
+        <v>9840</v>
+      </c>
+      <c r="E76" s="2">
         <f t="shared" si="15"/>
-        <v>9840</v>
-      </c>
-      <c r="E76" s="2">
+        <v>154</v>
+      </c>
+      <c r="F76" s="2">
         <f t="shared" si="16"/>
-        <v>154</v>
-      </c>
-      <c r="F76" s="2">
+        <v>5</v>
+      </c>
+      <c r="G76" s="2">
         <f t="shared" si="17"/>
-        <v>5</v>
-      </c>
-      <c r="G76" s="2">
+        <v>100</v>
+      </c>
+      <c r="H76" s="2">
         <f t="shared" si="18"/>
-        <v>100</v>
-      </c>
-      <c r="H76" s="2">
+        <v>10</v>
+      </c>
+      <c r="I76" s="2">
         <f t="shared" si="19"/>
         <v>10</v>
       </c>
-      <c r="I76" s="2">
+      <c r="J76" s="2">
         <f t="shared" si="20"/>
         <v>10</v>
       </c>
-      <c r="J76" s="2">
+      <c r="K76" s="2">
         <f t="shared" si="21"/>
         <v>10</v>
       </c>
-      <c r="K76" s="2">
+      <c r="L76" s="2">
         <f t="shared" si="22"/>
         <v>10</v>
       </c>
-      <c r="L76" s="2">
-        <f t="shared" si="23"/>
-        <v>10</v>
-      </c>
       <c r="M76" s="2">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1013</v>
       </c>
       <c r="N76" s="2">
         <v>82</v>
@@ -4966,52 +4894,51 @@
         <v>74</v>
       </c>
       <c r="B77" s="2">
+        <f t="shared" si="12"/>
+        <v>395</v>
+      </c>
+      <c r="C77" s="2">
         <f t="shared" si="13"/>
-        <v>395</v>
-      </c>
-      <c r="C77" s="2">
+        <v>224</v>
+      </c>
+      <c r="D77" s="2">
         <f t="shared" si="14"/>
-        <v>224</v>
-      </c>
-      <c r="D77" s="2">
+        <v>9960</v>
+      </c>
+      <c r="E77" s="2">
         <f t="shared" si="15"/>
-        <v>9960</v>
-      </c>
-      <c r="E77" s="2">
+        <v>156</v>
+      </c>
+      <c r="F77" s="2">
         <f t="shared" si="16"/>
-        <v>156</v>
-      </c>
-      <c r="F77" s="2">
+        <v>5</v>
+      </c>
+      <c r="G77" s="2">
         <f t="shared" si="17"/>
-        <v>5</v>
-      </c>
-      <c r="G77" s="2">
+        <v>100</v>
+      </c>
+      <c r="H77" s="2">
         <f t="shared" si="18"/>
-        <v>100</v>
-      </c>
-      <c r="H77" s="2">
+        <v>10</v>
+      </c>
+      <c r="I77" s="2">
         <f t="shared" si="19"/>
         <v>10</v>
       </c>
-      <c r="I77" s="2">
+      <c r="J77" s="2">
         <f t="shared" si="20"/>
         <v>10</v>
       </c>
-      <c r="J77" s="2">
+      <c r="K77" s="2">
         <f t="shared" si="21"/>
         <v>10</v>
       </c>
-      <c r="K77" s="2">
+      <c r="L77" s="2">
         <f t="shared" si="22"/>
         <v>10</v>
       </c>
-      <c r="L77" s="2">
-        <f t="shared" si="23"/>
-        <v>10</v>
-      </c>
       <c r="M77" s="2">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1014</v>
       </c>
       <c r="N77" s="2">
         <v>83</v>
@@ -5025,52 +4952,51 @@
         <v>75</v>
       </c>
       <c r="B78" s="2">
+        <f t="shared" si="12"/>
+        <v>400</v>
+      </c>
+      <c r="C78" s="2">
         <f t="shared" si="13"/>
-        <v>400</v>
-      </c>
-      <c r="C78" s="2">
+        <v>227</v>
+      </c>
+      <c r="D78" s="2">
         <f t="shared" si="14"/>
-        <v>227</v>
-      </c>
-      <c r="D78" s="2">
+        <v>10080</v>
+      </c>
+      <c r="E78" s="2">
         <f t="shared" si="15"/>
-        <v>10080</v>
-      </c>
-      <c r="E78" s="2">
+        <v>158</v>
+      </c>
+      <c r="F78" s="2">
         <f t="shared" si="16"/>
-        <v>158</v>
-      </c>
-      <c r="F78" s="2">
+        <v>5</v>
+      </c>
+      <c r="G78" s="2">
         <f t="shared" si="17"/>
-        <v>5</v>
-      </c>
-      <c r="G78" s="2">
+        <v>100</v>
+      </c>
+      <c r="H78" s="2">
         <f t="shared" si="18"/>
-        <v>100</v>
-      </c>
-      <c r="H78" s="2">
+        <v>10</v>
+      </c>
+      <c r="I78" s="2">
         <f t="shared" si="19"/>
         <v>10</v>
       </c>
-      <c r="I78" s="2">
+      <c r="J78" s="2">
         <f t="shared" si="20"/>
         <v>10</v>
       </c>
-      <c r="J78" s="2">
+      <c r="K78" s="2">
         <f t="shared" si="21"/>
         <v>10</v>
       </c>
-      <c r="K78" s="2">
+      <c r="L78" s="2">
         <f t="shared" si="22"/>
         <v>10</v>
       </c>
-      <c r="L78" s="2">
-        <f t="shared" si="23"/>
-        <v>10</v>
-      </c>
       <c r="M78" s="2">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1015</v>
       </c>
       <c r="N78" s="2">
         <v>84</v>
@@ -5084,52 +5010,51 @@
         <v>76</v>
       </c>
       <c r="B79" s="2">
+        <f t="shared" si="12"/>
+        <v>405</v>
+      </c>
+      <c r="C79" s="2">
         <f t="shared" si="13"/>
-        <v>405</v>
-      </c>
-      <c r="C79" s="2">
+        <v>230</v>
+      </c>
+      <c r="D79" s="2">
         <f t="shared" si="14"/>
-        <v>230</v>
-      </c>
-      <c r="D79" s="2">
+        <v>10200</v>
+      </c>
+      <c r="E79" s="2">
         <f t="shared" si="15"/>
-        <v>10200</v>
-      </c>
-      <c r="E79" s="2">
+        <v>160</v>
+      </c>
+      <c r="F79" s="2">
         <f t="shared" si="16"/>
-        <v>160</v>
-      </c>
-      <c r="F79" s="2">
+        <v>5</v>
+      </c>
+      <c r="G79" s="2">
         <f t="shared" si="17"/>
-        <v>5</v>
-      </c>
-      <c r="G79" s="2">
+        <v>100</v>
+      </c>
+      <c r="H79" s="2">
         <f t="shared" si="18"/>
-        <v>100</v>
-      </c>
-      <c r="H79" s="2">
+        <v>10</v>
+      </c>
+      <c r="I79" s="2">
         <f t="shared" si="19"/>
         <v>10</v>
       </c>
-      <c r="I79" s="2">
+      <c r="J79" s="2">
         <f t="shared" si="20"/>
         <v>10</v>
       </c>
-      <c r="J79" s="2">
+      <c r="K79" s="2">
         <f t="shared" si="21"/>
         <v>10</v>
       </c>
-      <c r="K79" s="2">
+      <c r="L79" s="2">
         <f t="shared" si="22"/>
         <v>10</v>
       </c>
-      <c r="L79" s="2">
-        <f t="shared" si="23"/>
-        <v>10</v>
-      </c>
       <c r="M79" s="2">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1016</v>
       </c>
       <c r="N79" s="2">
         <v>85</v>
@@ -5143,52 +5068,51 @@
         <v>77</v>
       </c>
       <c r="B80" s="2">
+        <f t="shared" si="12"/>
+        <v>410</v>
+      </c>
+      <c r="C80" s="2">
         <f t="shared" si="13"/>
-        <v>410</v>
-      </c>
-      <c r="C80" s="2">
+        <v>233</v>
+      </c>
+      <c r="D80" s="2">
         <f t="shared" si="14"/>
-        <v>233</v>
-      </c>
-      <c r="D80" s="2">
+        <v>10320</v>
+      </c>
+      <c r="E80" s="2">
         <f t="shared" si="15"/>
-        <v>10320</v>
-      </c>
-      <c r="E80" s="2">
+        <v>162</v>
+      </c>
+      <c r="F80" s="2">
         <f t="shared" si="16"/>
-        <v>162</v>
-      </c>
-      <c r="F80" s="2">
+        <v>5</v>
+      </c>
+      <c r="G80" s="2">
         <f t="shared" si="17"/>
-        <v>5</v>
-      </c>
-      <c r="G80" s="2">
+        <v>100</v>
+      </c>
+      <c r="H80" s="2">
         <f t="shared" si="18"/>
-        <v>100</v>
-      </c>
-      <c r="H80" s="2">
+        <v>10</v>
+      </c>
+      <c r="I80" s="2">
         <f t="shared" si="19"/>
         <v>10</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <f t="shared" si="20"/>
         <v>10</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <f t="shared" si="21"/>
         <v>10</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <f t="shared" si="22"/>
         <v>10</v>
       </c>
-      <c r="L80" s="2">
-        <f t="shared" si="23"/>
-        <v>10</v>
-      </c>
       <c r="M80" s="2">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1017</v>
       </c>
       <c r="N80" s="2">
         <v>86</v>
@@ -5202,52 +5126,51 @@
         <v>78</v>
       </c>
       <c r="B81" s="2">
+        <f t="shared" si="12"/>
+        <v>415</v>
+      </c>
+      <c r="C81" s="2">
         <f t="shared" si="13"/>
-        <v>415</v>
-      </c>
-      <c r="C81" s="2">
+        <v>236</v>
+      </c>
+      <c r="D81" s="2">
         <f t="shared" si="14"/>
-        <v>236</v>
-      </c>
-      <c r="D81" s="2">
+        <v>10440</v>
+      </c>
+      <c r="E81" s="2">
         <f t="shared" si="15"/>
-        <v>10440</v>
-      </c>
-      <c r="E81" s="2">
+        <v>164</v>
+      </c>
+      <c r="F81" s="2">
         <f t="shared" si="16"/>
-        <v>164</v>
-      </c>
-      <c r="F81" s="2">
+        <v>5</v>
+      </c>
+      <c r="G81" s="2">
         <f t="shared" si="17"/>
-        <v>5</v>
-      </c>
-      <c r="G81" s="2">
+        <v>100</v>
+      </c>
+      <c r="H81" s="2">
         <f t="shared" si="18"/>
-        <v>100</v>
-      </c>
-      <c r="H81" s="2">
+        <v>10</v>
+      </c>
+      <c r="I81" s="2">
         <f t="shared" si="19"/>
         <v>10</v>
       </c>
-      <c r="I81" s="2">
+      <c r="J81" s="2">
         <f t="shared" si="20"/>
         <v>10</v>
       </c>
-      <c r="J81" s="2">
+      <c r="K81" s="2">
         <f t="shared" si="21"/>
         <v>10</v>
       </c>
-      <c r="K81" s="2">
+      <c r="L81" s="2">
         <f t="shared" si="22"/>
         <v>10</v>
       </c>
-      <c r="L81" s="2">
-        <f t="shared" si="23"/>
-        <v>10</v>
-      </c>
       <c r="M81" s="2">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1018</v>
       </c>
       <c r="N81" s="2">
         <v>87</v>
@@ -5261,52 +5184,51 @@
         <v>79</v>
       </c>
       <c r="B82" s="2">
+        <f t="shared" si="12"/>
+        <v>420</v>
+      </c>
+      <c r="C82" s="2">
         <f t="shared" si="13"/>
-        <v>420</v>
-      </c>
-      <c r="C82" s="2">
+        <v>239</v>
+      </c>
+      <c r="D82" s="2">
         <f t="shared" si="14"/>
-        <v>239</v>
-      </c>
-      <c r="D82" s="2">
+        <v>10560</v>
+      </c>
+      <c r="E82" s="2">
         <f t="shared" si="15"/>
-        <v>10560</v>
-      </c>
-      <c r="E82" s="2">
+        <v>166</v>
+      </c>
+      <c r="F82" s="2">
         <f t="shared" si="16"/>
-        <v>166</v>
-      </c>
-      <c r="F82" s="2">
+        <v>5</v>
+      </c>
+      <c r="G82" s="2">
         <f t="shared" si="17"/>
-        <v>5</v>
-      </c>
-      <c r="G82" s="2">
+        <v>100</v>
+      </c>
+      <c r="H82" s="2">
         <f t="shared" si="18"/>
-        <v>100</v>
-      </c>
-      <c r="H82" s="2">
+        <v>10</v>
+      </c>
+      <c r="I82" s="2">
         <f t="shared" si="19"/>
         <v>10</v>
       </c>
-      <c r="I82" s="2">
+      <c r="J82" s="2">
         <f t="shared" si="20"/>
         <v>10</v>
       </c>
-      <c r="J82" s="2">
+      <c r="K82" s="2">
         <f t="shared" si="21"/>
         <v>10</v>
       </c>
-      <c r="K82" s="2">
+      <c r="L82" s="2">
         <f t="shared" si="22"/>
         <v>10</v>
       </c>
-      <c r="L82" s="2">
-        <f t="shared" si="23"/>
-        <v>10</v>
-      </c>
       <c r="M82" s="2">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1019</v>
       </c>
       <c r="N82" s="2">
         <v>88</v>
@@ -5320,52 +5242,51 @@
         <v>80</v>
       </c>
       <c r="B83" s="2">
+        <f t="shared" si="12"/>
+        <v>425</v>
+      </c>
+      <c r="C83" s="2">
         <f t="shared" si="13"/>
-        <v>425</v>
-      </c>
-      <c r="C83" s="2">
+        <v>242</v>
+      </c>
+      <c r="D83" s="2">
         <f t="shared" si="14"/>
-        <v>242</v>
-      </c>
-      <c r="D83" s="2">
+        <v>10680</v>
+      </c>
+      <c r="E83" s="2">
         <f t="shared" si="15"/>
-        <v>10680</v>
-      </c>
-      <c r="E83" s="2">
+        <v>168</v>
+      </c>
+      <c r="F83" s="2">
         <f t="shared" si="16"/>
-        <v>168</v>
-      </c>
-      <c r="F83" s="2">
+        <v>5</v>
+      </c>
+      <c r="G83" s="2">
         <f t="shared" si="17"/>
-        <v>5</v>
-      </c>
-      <c r="G83" s="2">
+        <v>100</v>
+      </c>
+      <c r="H83" s="2">
         <f t="shared" si="18"/>
-        <v>100</v>
-      </c>
-      <c r="H83" s="2">
+        <v>10</v>
+      </c>
+      <c r="I83" s="2">
         <f t="shared" si="19"/>
         <v>10</v>
       </c>
-      <c r="I83" s="2">
+      <c r="J83" s="2">
         <f t="shared" si="20"/>
         <v>10</v>
       </c>
-      <c r="J83" s="2">
+      <c r="K83" s="2">
         <f t="shared" si="21"/>
         <v>10</v>
       </c>
-      <c r="K83" s="2">
+      <c r="L83" s="2">
         <f t="shared" si="22"/>
         <v>10</v>
       </c>
-      <c r="L83" s="2">
-        <f t="shared" si="23"/>
-        <v>10</v>
-      </c>
       <c r="M83" s="2">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1020</v>
       </c>
       <c r="N83" s="2">
         <v>89</v>
@@ -5379,52 +5300,51 @@
         <v>81</v>
       </c>
       <c r="B84" s="2">
+        <f t="shared" si="12"/>
+        <v>430</v>
+      </c>
+      <c r="C84" s="2">
         <f t="shared" si="13"/>
-        <v>430</v>
-      </c>
-      <c r="C84" s="2">
+        <v>245</v>
+      </c>
+      <c r="D84" s="2">
         <f t="shared" si="14"/>
-        <v>245</v>
-      </c>
-      <c r="D84" s="2">
+        <v>10800</v>
+      </c>
+      <c r="E84" s="2">
         <f t="shared" si="15"/>
-        <v>10800</v>
-      </c>
-      <c r="E84" s="2">
+        <v>170</v>
+      </c>
+      <c r="F84" s="2">
         <f t="shared" si="16"/>
-        <v>170</v>
-      </c>
-      <c r="F84" s="2">
+        <v>5</v>
+      </c>
+      <c r="G84" s="2">
         <f t="shared" si="17"/>
-        <v>5</v>
-      </c>
-      <c r="G84" s="2">
+        <v>100</v>
+      </c>
+      <c r="H84" s="2">
         <f t="shared" si="18"/>
-        <v>100</v>
-      </c>
-      <c r="H84" s="2">
+        <v>10</v>
+      </c>
+      <c r="I84" s="2">
         <f t="shared" si="19"/>
         <v>10</v>
       </c>
-      <c r="I84" s="2">
+      <c r="J84" s="2">
         <f t="shared" si="20"/>
         <v>10</v>
       </c>
-      <c r="J84" s="2">
+      <c r="K84" s="2">
         <f t="shared" si="21"/>
         <v>10</v>
       </c>
-      <c r="K84" s="2">
+      <c r="L84" s="2">
         <f t="shared" si="22"/>
         <v>10</v>
       </c>
-      <c r="L84" s="2">
-        <f t="shared" si="23"/>
-        <v>10</v>
-      </c>
       <c r="M84" s="2">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1001</v>
       </c>
       <c r="N84" s="2">
         <v>90</v>
@@ -5438,52 +5358,51 @@
         <v>82</v>
       </c>
       <c r="B85" s="2">
+        <f t="shared" si="12"/>
+        <v>435</v>
+      </c>
+      <c r="C85" s="2">
         <f t="shared" si="13"/>
-        <v>435</v>
-      </c>
-      <c r="C85" s="2">
+        <v>248</v>
+      </c>
+      <c r="D85" s="2">
         <f t="shared" si="14"/>
-        <v>248</v>
-      </c>
-      <c r="D85" s="2">
+        <v>10920</v>
+      </c>
+      <c r="E85" s="2">
         <f t="shared" si="15"/>
-        <v>10920</v>
-      </c>
-      <c r="E85" s="2">
+        <v>172</v>
+      </c>
+      <c r="F85" s="2">
         <f t="shared" si="16"/>
-        <v>172</v>
-      </c>
-      <c r="F85" s="2">
+        <v>5</v>
+      </c>
+      <c r="G85" s="2">
         <f t="shared" si="17"/>
-        <v>5</v>
-      </c>
-      <c r="G85" s="2">
+        <v>100</v>
+      </c>
+      <c r="H85" s="2">
         <f t="shared" si="18"/>
-        <v>100</v>
-      </c>
-      <c r="H85" s="2">
+        <v>10</v>
+      </c>
+      <c r="I85" s="2">
         <f t="shared" si="19"/>
         <v>10</v>
       </c>
-      <c r="I85" s="2">
+      <c r="J85" s="2">
         <f t="shared" si="20"/>
         <v>10</v>
       </c>
-      <c r="J85" s="2">
+      <c r="K85" s="2">
         <f t="shared" si="21"/>
         <v>10</v>
       </c>
-      <c r="K85" s="2">
+      <c r="L85" s="2">
         <f t="shared" si="22"/>
         <v>10</v>
       </c>
-      <c r="L85" s="2">
-        <f t="shared" si="23"/>
-        <v>10</v>
-      </c>
       <c r="M85" s="2">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1002</v>
       </c>
       <c r="N85" s="2">
         <v>91</v>
@@ -5497,52 +5416,51 @@
         <v>83</v>
       </c>
       <c r="B86" s="2">
+        <f t="shared" si="12"/>
+        <v>440</v>
+      </c>
+      <c r="C86" s="2">
         <f t="shared" si="13"/>
-        <v>440</v>
-      </c>
-      <c r="C86" s="2">
+        <v>251</v>
+      </c>
+      <c r="D86" s="2">
         <f t="shared" si="14"/>
-        <v>251</v>
-      </c>
-      <c r="D86" s="2">
+        <v>11040</v>
+      </c>
+      <c r="E86" s="2">
         <f t="shared" si="15"/>
-        <v>11040</v>
-      </c>
-      <c r="E86" s="2">
+        <v>174</v>
+      </c>
+      <c r="F86" s="2">
         <f t="shared" si="16"/>
-        <v>174</v>
-      </c>
-      <c r="F86" s="2">
+        <v>5</v>
+      </c>
+      <c r="G86" s="2">
         <f t="shared" si="17"/>
-        <v>5</v>
-      </c>
-      <c r="G86" s="2">
+        <v>100</v>
+      </c>
+      <c r="H86" s="2">
         <f t="shared" si="18"/>
-        <v>100</v>
-      </c>
-      <c r="H86" s="2">
+        <v>10</v>
+      </c>
+      <c r="I86" s="2">
         <f t="shared" si="19"/>
         <v>10</v>
       </c>
-      <c r="I86" s="2">
+      <c r="J86" s="2">
         <f t="shared" si="20"/>
         <v>10</v>
       </c>
-      <c r="J86" s="2">
+      <c r="K86" s="2">
         <f t="shared" si="21"/>
         <v>10</v>
       </c>
-      <c r="K86" s="2">
+      <c r="L86" s="2">
         <f t="shared" si="22"/>
         <v>10</v>
       </c>
-      <c r="L86" s="2">
-        <f t="shared" si="23"/>
-        <v>10</v>
-      </c>
       <c r="M86" s="2">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1003</v>
       </c>
       <c r="N86" s="2">
         <v>92</v>
@@ -5556,52 +5474,51 @@
         <v>84</v>
       </c>
       <c r="B87" s="2">
+        <f t="shared" si="12"/>
+        <v>445</v>
+      </c>
+      <c r="C87" s="2">
         <f t="shared" si="13"/>
-        <v>445</v>
-      </c>
-      <c r="C87" s="2">
+        <v>254</v>
+      </c>
+      <c r="D87" s="2">
         <f t="shared" si="14"/>
-        <v>254</v>
-      </c>
-      <c r="D87" s="2">
+        <v>11160</v>
+      </c>
+      <c r="E87" s="2">
         <f t="shared" si="15"/>
-        <v>11160</v>
-      </c>
-      <c r="E87" s="2">
+        <v>176</v>
+      </c>
+      <c r="F87" s="2">
         <f t="shared" si="16"/>
-        <v>176</v>
-      </c>
-      <c r="F87" s="2">
+        <v>5</v>
+      </c>
+      <c r="G87" s="2">
         <f t="shared" si="17"/>
-        <v>5</v>
-      </c>
-      <c r="G87" s="2">
+        <v>100</v>
+      </c>
+      <c r="H87" s="2">
         <f t="shared" si="18"/>
-        <v>100</v>
-      </c>
-      <c r="H87" s="2">
+        <v>10</v>
+      </c>
+      <c r="I87" s="2">
         <f t="shared" si="19"/>
         <v>10</v>
       </c>
-      <c r="I87" s="2">
+      <c r="J87" s="2">
         <f t="shared" si="20"/>
         <v>10</v>
       </c>
-      <c r="J87" s="2">
+      <c r="K87" s="2">
         <f t="shared" si="21"/>
         <v>10</v>
       </c>
-      <c r="K87" s="2">
+      <c r="L87" s="2">
         <f t="shared" si="22"/>
         <v>10</v>
       </c>
-      <c r="L87" s="2">
-        <f t="shared" si="23"/>
-        <v>10</v>
-      </c>
       <c r="M87" s="2">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1004</v>
       </c>
       <c r="N87" s="2">
         <v>93</v>
@@ -5615,52 +5532,51 @@
         <v>85</v>
       </c>
       <c r="B88" s="2">
+        <f t="shared" si="12"/>
+        <v>450</v>
+      </c>
+      <c r="C88" s="2">
         <f t="shared" si="13"/>
-        <v>450</v>
-      </c>
-      <c r="C88" s="2">
+        <v>257</v>
+      </c>
+      <c r="D88" s="2">
         <f t="shared" si="14"/>
-        <v>257</v>
-      </c>
-      <c r="D88" s="2">
+        <v>11280</v>
+      </c>
+      <c r="E88" s="2">
         <f t="shared" si="15"/>
-        <v>11280</v>
-      </c>
-      <c r="E88" s="2">
+        <v>178</v>
+      </c>
+      <c r="F88" s="2">
         <f t="shared" si="16"/>
-        <v>178</v>
-      </c>
-      <c r="F88" s="2">
+        <v>5</v>
+      </c>
+      <c r="G88" s="2">
         <f t="shared" si="17"/>
-        <v>5</v>
-      </c>
-      <c r="G88" s="2">
+        <v>100</v>
+      </c>
+      <c r="H88" s="2">
         <f t="shared" si="18"/>
-        <v>100</v>
-      </c>
-      <c r="H88" s="2">
+        <v>10</v>
+      </c>
+      <c r="I88" s="2">
         <f t="shared" si="19"/>
         <v>10</v>
       </c>
-      <c r="I88" s="2">
+      <c r="J88" s="2">
         <f t="shared" si="20"/>
         <v>10</v>
       </c>
-      <c r="J88" s="2">
+      <c r="K88" s="2">
         <f t="shared" si="21"/>
         <v>10</v>
       </c>
-      <c r="K88" s="2">
+      <c r="L88" s="2">
         <f t="shared" si="22"/>
         <v>10</v>
       </c>
-      <c r="L88" s="2">
-        <f t="shared" si="23"/>
-        <v>10</v>
-      </c>
       <c r="M88" s="2">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1005</v>
       </c>
       <c r="N88" s="2">
         <v>94</v>
@@ -5674,52 +5590,51 @@
         <v>86</v>
       </c>
       <c r="B89" s="2">
+        <f t="shared" si="12"/>
+        <v>455</v>
+      </c>
+      <c r="C89" s="2">
         <f t="shared" si="13"/>
-        <v>455</v>
-      </c>
-      <c r="C89" s="2">
+        <v>260</v>
+      </c>
+      <c r="D89" s="2">
         <f t="shared" si="14"/>
-        <v>260</v>
-      </c>
-      <c r="D89" s="2">
+        <v>11400</v>
+      </c>
+      <c r="E89" s="2">
         <f t="shared" si="15"/>
-        <v>11400</v>
-      </c>
-      <c r="E89" s="2">
+        <v>180</v>
+      </c>
+      <c r="F89" s="2">
         <f t="shared" si="16"/>
-        <v>180</v>
-      </c>
-      <c r="F89" s="2">
+        <v>5</v>
+      </c>
+      <c r="G89" s="2">
         <f t="shared" si="17"/>
-        <v>5</v>
-      </c>
-      <c r="G89" s="2">
+        <v>100</v>
+      </c>
+      <c r="H89" s="2">
         <f t="shared" si="18"/>
-        <v>100</v>
-      </c>
-      <c r="H89" s="2">
+        <v>10</v>
+      </c>
+      <c r="I89" s="2">
         <f t="shared" si="19"/>
         <v>10</v>
       </c>
-      <c r="I89" s="2">
+      <c r="J89" s="2">
         <f t="shared" si="20"/>
         <v>10</v>
       </c>
-      <c r="J89" s="2">
+      <c r="K89" s="2">
         <f t="shared" si="21"/>
         <v>10</v>
       </c>
-      <c r="K89" s="2">
+      <c r="L89" s="2">
         <f t="shared" si="22"/>
         <v>10</v>
       </c>
-      <c r="L89" s="2">
-        <f t="shared" si="23"/>
-        <v>10</v>
-      </c>
       <c r="M89" s="2">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1006</v>
       </c>
       <c r="N89" s="2">
         <v>95</v>
@@ -5733,52 +5648,51 @@
         <v>87</v>
       </c>
       <c r="B90" s="2">
+        <f t="shared" si="12"/>
+        <v>460</v>
+      </c>
+      <c r="C90" s="2">
         <f t="shared" si="13"/>
-        <v>460</v>
-      </c>
-      <c r="C90" s="2">
+        <v>263</v>
+      </c>
+      <c r="D90" s="2">
         <f t="shared" si="14"/>
-        <v>263</v>
-      </c>
-      <c r="D90" s="2">
+        <v>11520</v>
+      </c>
+      <c r="E90" s="2">
         <f t="shared" si="15"/>
-        <v>11520</v>
-      </c>
-      <c r="E90" s="2">
+        <v>182</v>
+      </c>
+      <c r="F90" s="2">
         <f t="shared" si="16"/>
-        <v>182</v>
-      </c>
-      <c r="F90" s="2">
+        <v>5</v>
+      </c>
+      <c r="G90" s="2">
         <f t="shared" si="17"/>
-        <v>5</v>
-      </c>
-      <c r="G90" s="2">
+        <v>100</v>
+      </c>
+      <c r="H90" s="2">
         <f t="shared" si="18"/>
-        <v>100</v>
-      </c>
-      <c r="H90" s="2">
+        <v>10</v>
+      </c>
+      <c r="I90" s="2">
         <f t="shared" si="19"/>
         <v>10</v>
       </c>
-      <c r="I90" s="2">
+      <c r="J90" s="2">
         <f t="shared" si="20"/>
         <v>10</v>
       </c>
-      <c r="J90" s="2">
+      <c r="K90" s="2">
         <f t="shared" si="21"/>
         <v>10</v>
       </c>
-      <c r="K90" s="2">
+      <c r="L90" s="2">
         <f t="shared" si="22"/>
         <v>10</v>
       </c>
-      <c r="L90" s="2">
-        <f t="shared" si="23"/>
-        <v>10</v>
-      </c>
       <c r="M90" s="2">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1007</v>
       </c>
       <c r="N90" s="2">
         <v>96</v>
@@ -5792,52 +5706,51 @@
         <v>88</v>
       </c>
       <c r="B91" s="2">
+        <f t="shared" si="12"/>
+        <v>465</v>
+      </c>
+      <c r="C91" s="2">
         <f t="shared" si="13"/>
-        <v>465</v>
-      </c>
-      <c r="C91" s="2">
+        <v>266</v>
+      </c>
+      <c r="D91" s="2">
         <f t="shared" si="14"/>
-        <v>266</v>
-      </c>
-      <c r="D91" s="2">
+        <v>11640</v>
+      </c>
+      <c r="E91" s="2">
         <f t="shared" si="15"/>
-        <v>11640</v>
-      </c>
-      <c r="E91" s="2">
+        <v>184</v>
+      </c>
+      <c r="F91" s="2">
         <f t="shared" si="16"/>
-        <v>184</v>
-      </c>
-      <c r="F91" s="2">
+        <v>5</v>
+      </c>
+      <c r="G91" s="2">
         <f t="shared" si="17"/>
-        <v>5</v>
-      </c>
-      <c r="G91" s="2">
+        <v>100</v>
+      </c>
+      <c r="H91" s="2">
         <f t="shared" si="18"/>
-        <v>100</v>
-      </c>
-      <c r="H91" s="2">
+        <v>10</v>
+      </c>
+      <c r="I91" s="2">
         <f t="shared" si="19"/>
         <v>10</v>
       </c>
-      <c r="I91" s="2">
+      <c r="J91" s="2">
         <f t="shared" si="20"/>
         <v>10</v>
       </c>
-      <c r="J91" s="2">
+      <c r="K91" s="2">
         <f t="shared" si="21"/>
         <v>10</v>
       </c>
-      <c r="K91" s="2">
+      <c r="L91" s="2">
         <f t="shared" si="22"/>
         <v>10</v>
       </c>
-      <c r="L91" s="2">
-        <f t="shared" si="23"/>
-        <v>10</v>
-      </c>
       <c r="M91" s="2">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="N91" s="2">
         <v>97</v>
@@ -5851,52 +5764,51 @@
         <v>89</v>
       </c>
       <c r="B92" s="2">
+        <f t="shared" si="12"/>
+        <v>470</v>
+      </c>
+      <c r="C92" s="2">
         <f t="shared" si="13"/>
-        <v>470</v>
-      </c>
-      <c r="C92" s="2">
+        <v>269</v>
+      </c>
+      <c r="D92" s="2">
         <f t="shared" si="14"/>
-        <v>269</v>
-      </c>
-      <c r="D92" s="2">
+        <v>11760</v>
+      </c>
+      <c r="E92" s="2">
         <f t="shared" si="15"/>
-        <v>11760</v>
-      </c>
-      <c r="E92" s="2">
+        <v>186</v>
+      </c>
+      <c r="F92" s="2">
         <f t="shared" si="16"/>
-        <v>186</v>
-      </c>
-      <c r="F92" s="2">
+        <v>5</v>
+      </c>
+      <c r="G92" s="2">
         <f t="shared" si="17"/>
-        <v>5</v>
-      </c>
-      <c r="G92" s="2">
+        <v>100</v>
+      </c>
+      <c r="H92" s="2">
         <f t="shared" si="18"/>
-        <v>100</v>
-      </c>
-      <c r="H92" s="2">
+        <v>10</v>
+      </c>
+      <c r="I92" s="2">
         <f t="shared" si="19"/>
         <v>10</v>
       </c>
-      <c r="I92" s="2">
+      <c r="J92" s="2">
         <f t="shared" si="20"/>
         <v>10</v>
       </c>
-      <c r="J92" s="2">
+      <c r="K92" s="2">
         <f t="shared" si="21"/>
         <v>10</v>
       </c>
-      <c r="K92" s="2">
+      <c r="L92" s="2">
         <f t="shared" si="22"/>
         <v>10</v>
       </c>
-      <c r="L92" s="2">
-        <f t="shared" si="23"/>
-        <v>10</v>
-      </c>
       <c r="M92" s="2">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1009</v>
       </c>
       <c r="N92" s="2">
         <v>98</v>
@@ -5910,52 +5822,51 @@
         <v>90</v>
       </c>
       <c r="B93" s="2">
+        <f t="shared" si="12"/>
+        <v>475</v>
+      </c>
+      <c r="C93" s="2">
         <f t="shared" si="13"/>
-        <v>475</v>
-      </c>
-      <c r="C93" s="2">
+        <v>272</v>
+      </c>
+      <c r="D93" s="2">
         <f t="shared" si="14"/>
-        <v>272</v>
-      </c>
-      <c r="D93" s="2">
+        <v>11880</v>
+      </c>
+      <c r="E93" s="2">
         <f t="shared" si="15"/>
-        <v>11880</v>
-      </c>
-      <c r="E93" s="2">
+        <v>188</v>
+      </c>
+      <c r="F93" s="2">
         <f t="shared" si="16"/>
-        <v>188</v>
-      </c>
-      <c r="F93" s="2">
+        <v>5</v>
+      </c>
+      <c r="G93" s="2">
         <f t="shared" si="17"/>
-        <v>5</v>
-      </c>
-      <c r="G93" s="2">
+        <v>100</v>
+      </c>
+      <c r="H93" s="2">
         <f t="shared" si="18"/>
-        <v>100</v>
-      </c>
-      <c r="H93" s="2">
+        <v>10</v>
+      </c>
+      <c r="I93" s="2">
         <f t="shared" si="19"/>
         <v>10</v>
       </c>
-      <c r="I93" s="2">
+      <c r="J93" s="2">
         <f t="shared" si="20"/>
         <v>10</v>
       </c>
-      <c r="J93" s="2">
+      <c r="K93" s="2">
         <f t="shared" si="21"/>
         <v>10</v>
       </c>
-      <c r="K93" s="2">
+      <c r="L93" s="2">
         <f t="shared" si="22"/>
         <v>10</v>
       </c>
-      <c r="L93" s="2">
-        <f t="shared" si="23"/>
-        <v>10</v>
-      </c>
       <c r="M93" s="2">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1010</v>
       </c>
       <c r="N93" s="2">
         <v>99</v>
@@ -5969,52 +5880,51 @@
         <v>91</v>
       </c>
       <c r="B94" s="2">
+        <f t="shared" si="12"/>
+        <v>480</v>
+      </c>
+      <c r="C94" s="2">
         <f t="shared" si="13"/>
-        <v>480</v>
-      </c>
-      <c r="C94" s="2">
+        <v>275</v>
+      </c>
+      <c r="D94" s="2">
         <f t="shared" si="14"/>
-        <v>275</v>
-      </c>
-      <c r="D94" s="2">
+        <v>12000</v>
+      </c>
+      <c r="E94" s="2">
         <f t="shared" si="15"/>
-        <v>12000</v>
-      </c>
-      <c r="E94" s="2">
+        <v>190</v>
+      </c>
+      <c r="F94" s="2">
         <f t="shared" si="16"/>
-        <v>190</v>
-      </c>
-      <c r="F94" s="2">
+        <v>5</v>
+      </c>
+      <c r="G94" s="2">
         <f t="shared" si="17"/>
-        <v>5</v>
-      </c>
-      <c r="G94" s="2">
+        <v>100</v>
+      </c>
+      <c r="H94" s="2">
         <f t="shared" si="18"/>
-        <v>100</v>
-      </c>
-      <c r="H94" s="2">
+        <v>10</v>
+      </c>
+      <c r="I94" s="2">
         <f t="shared" si="19"/>
         <v>10</v>
       </c>
-      <c r="I94" s="2">
+      <c r="J94" s="2">
         <f t="shared" si="20"/>
         <v>10</v>
       </c>
-      <c r="J94" s="2">
+      <c r="K94" s="2">
         <f t="shared" si="21"/>
         <v>10</v>
       </c>
-      <c r="K94" s="2">
+      <c r="L94" s="2">
         <f t="shared" si="22"/>
         <v>10</v>
       </c>
-      <c r="L94" s="2">
-        <f t="shared" si="23"/>
-        <v>10</v>
-      </c>
       <c r="M94" s="2">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1011</v>
       </c>
       <c r="N94" s="2">
         <v>100</v>
@@ -6028,52 +5938,51 @@
         <v>92</v>
       </c>
       <c r="B95" s="2">
+        <f t="shared" si="12"/>
+        <v>485</v>
+      </c>
+      <c r="C95" s="2">
         <f t="shared" si="13"/>
-        <v>485</v>
-      </c>
-      <c r="C95" s="2">
+        <v>278</v>
+      </c>
+      <c r="D95" s="2">
         <f t="shared" si="14"/>
-        <v>278</v>
-      </c>
-      <c r="D95" s="2">
+        <v>12120</v>
+      </c>
+      <c r="E95" s="2">
         <f t="shared" si="15"/>
-        <v>12120</v>
-      </c>
-      <c r="E95" s="2">
+        <v>192</v>
+      </c>
+      <c r="F95" s="2">
         <f t="shared" si="16"/>
-        <v>192</v>
-      </c>
-      <c r="F95" s="2">
+        <v>5</v>
+      </c>
+      <c r="G95" s="2">
         <f t="shared" si="17"/>
-        <v>5</v>
-      </c>
-      <c r="G95" s="2">
+        <v>100</v>
+      </c>
+      <c r="H95" s="2">
         <f t="shared" si="18"/>
-        <v>100</v>
-      </c>
-      <c r="H95" s="2">
+        <v>10</v>
+      </c>
+      <c r="I95" s="2">
         <f t="shared" si="19"/>
         <v>10</v>
       </c>
-      <c r="I95" s="2">
+      <c r="J95" s="2">
         <f t="shared" si="20"/>
         <v>10</v>
       </c>
-      <c r="J95" s="2">
+      <c r="K95" s="2">
         <f t="shared" si="21"/>
         <v>10</v>
       </c>
-      <c r="K95" s="2">
+      <c r="L95" s="2">
         <f t="shared" si="22"/>
         <v>10</v>
       </c>
-      <c r="L95" s="2">
-        <f t="shared" si="23"/>
-        <v>10</v>
-      </c>
       <c r="M95" s="2">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1012</v>
       </c>
       <c r="N95" s="2">
         <v>101</v>
@@ -6087,52 +5996,51 @@
         <v>93</v>
       </c>
       <c r="B96" s="2">
+        <f t="shared" si="12"/>
+        <v>490</v>
+      </c>
+      <c r="C96" s="2">
         <f t="shared" si="13"/>
-        <v>490</v>
-      </c>
-      <c r="C96" s="2">
+        <v>281</v>
+      </c>
+      <c r="D96" s="2">
         <f t="shared" si="14"/>
-        <v>281</v>
-      </c>
-      <c r="D96" s="2">
+        <v>12240</v>
+      </c>
+      <c r="E96" s="2">
         <f t="shared" si="15"/>
-        <v>12240</v>
-      </c>
-      <c r="E96" s="2">
+        <v>194</v>
+      </c>
+      <c r="F96" s="2">
         <f t="shared" si="16"/>
-        <v>194</v>
-      </c>
-      <c r="F96" s="2">
+        <v>5</v>
+      </c>
+      <c r="G96" s="2">
         <f t="shared" si="17"/>
-        <v>5</v>
-      </c>
-      <c r="G96" s="2">
+        <v>100</v>
+      </c>
+      <c r="H96" s="2">
         <f t="shared" si="18"/>
-        <v>100</v>
-      </c>
-      <c r="H96" s="2">
+        <v>10</v>
+      </c>
+      <c r="I96" s="2">
         <f t="shared" si="19"/>
         <v>10</v>
       </c>
-      <c r="I96" s="2">
+      <c r="J96" s="2">
         <f t="shared" si="20"/>
         <v>10</v>
       </c>
-      <c r="J96" s="2">
+      <c r="K96" s="2">
         <f t="shared" si="21"/>
         <v>10</v>
       </c>
-      <c r="K96" s="2">
+      <c r="L96" s="2">
         <f t="shared" si="22"/>
         <v>10</v>
       </c>
-      <c r="L96" s="2">
-        <f t="shared" si="23"/>
-        <v>10</v>
-      </c>
       <c r="M96" s="2">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1013</v>
       </c>
       <c r="N96" s="2">
         <v>102</v>
@@ -6146,52 +6054,51 @@
         <v>94</v>
       </c>
       <c r="B97" s="2">
+        <f t="shared" si="12"/>
+        <v>495</v>
+      </c>
+      <c r="C97" s="2">
         <f t="shared" si="13"/>
-        <v>495</v>
-      </c>
-      <c r="C97" s="2">
+        <v>284</v>
+      </c>
+      <c r="D97" s="2">
         <f t="shared" si="14"/>
-        <v>284</v>
-      </c>
-      <c r="D97" s="2">
+        <v>12360</v>
+      </c>
+      <c r="E97" s="2">
         <f t="shared" si="15"/>
-        <v>12360</v>
-      </c>
-      <c r="E97" s="2">
+        <v>196</v>
+      </c>
+      <c r="F97" s="2">
         <f t="shared" si="16"/>
-        <v>196</v>
-      </c>
-      <c r="F97" s="2">
+        <v>5</v>
+      </c>
+      <c r="G97" s="2">
         <f t="shared" si="17"/>
-        <v>5</v>
-      </c>
-      <c r="G97" s="2">
+        <v>100</v>
+      </c>
+      <c r="H97" s="2">
         <f t="shared" si="18"/>
-        <v>100</v>
-      </c>
-      <c r="H97" s="2">
+        <v>10</v>
+      </c>
+      <c r="I97" s="2">
         <f t="shared" si="19"/>
         <v>10</v>
       </c>
-      <c r="I97" s="2">
+      <c r="J97" s="2">
         <f t="shared" si="20"/>
         <v>10</v>
       </c>
-      <c r="J97" s="2">
+      <c r="K97" s="2">
         <f t="shared" si="21"/>
         <v>10</v>
       </c>
-      <c r="K97" s="2">
+      <c r="L97" s="2">
         <f t="shared" si="22"/>
         <v>10</v>
       </c>
-      <c r="L97" s="2">
-        <f t="shared" si="23"/>
-        <v>10</v>
-      </c>
       <c r="M97" s="2">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1014</v>
       </c>
       <c r="N97" s="2">
         <v>103</v>
@@ -6205,52 +6112,51 @@
         <v>95</v>
       </c>
       <c r="B98" s="2">
+        <f t="shared" si="12"/>
+        <v>500</v>
+      </c>
+      <c r="C98" s="2">
         <f t="shared" si="13"/>
-        <v>500</v>
-      </c>
-      <c r="C98" s="2">
+        <v>287</v>
+      </c>
+      <c r="D98" s="2">
         <f t="shared" si="14"/>
-        <v>287</v>
-      </c>
-      <c r="D98" s="2">
+        <v>12480</v>
+      </c>
+      <c r="E98" s="2">
         <f t="shared" si="15"/>
-        <v>12480</v>
-      </c>
-      <c r="E98" s="2">
+        <v>198</v>
+      </c>
+      <c r="F98" s="2">
         <f t="shared" si="16"/>
-        <v>198</v>
-      </c>
-      <c r="F98" s="2">
+        <v>5</v>
+      </c>
+      <c r="G98" s="2">
         <f t="shared" si="17"/>
-        <v>5</v>
-      </c>
-      <c r="G98" s="2">
+        <v>100</v>
+      </c>
+      <c r="H98" s="2">
         <f t="shared" si="18"/>
-        <v>100</v>
-      </c>
-      <c r="H98" s="2">
+        <v>10</v>
+      </c>
+      <c r="I98" s="2">
         <f t="shared" si="19"/>
         <v>10</v>
       </c>
-      <c r="I98" s="2">
+      <c r="J98" s="2">
         <f t="shared" si="20"/>
         <v>10</v>
       </c>
-      <c r="J98" s="2">
+      <c r="K98" s="2">
         <f t="shared" si="21"/>
         <v>10</v>
       </c>
-      <c r="K98" s="2">
+      <c r="L98" s="2">
         <f t="shared" si="22"/>
         <v>10</v>
       </c>
-      <c r="L98" s="2">
-        <f t="shared" si="23"/>
-        <v>10</v>
-      </c>
       <c r="M98" s="2">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1015</v>
       </c>
       <c r="N98" s="2">
         <v>104</v>
@@ -6264,52 +6170,51 @@
         <v>96</v>
       </c>
       <c r="B99" s="2">
+        <f t="shared" si="12"/>
+        <v>505</v>
+      </c>
+      <c r="C99" s="2">
         <f t="shared" si="13"/>
-        <v>505</v>
-      </c>
-      <c r="C99" s="2">
+        <v>290</v>
+      </c>
+      <c r="D99" s="2">
         <f t="shared" si="14"/>
-        <v>290</v>
-      </c>
-      <c r="D99" s="2">
+        <v>12600</v>
+      </c>
+      <c r="E99" s="2">
         <f t="shared" si="15"/>
-        <v>12600</v>
-      </c>
-      <c r="E99" s="2">
+        <v>200</v>
+      </c>
+      <c r="F99" s="2">
         <f t="shared" si="16"/>
-        <v>200</v>
-      </c>
-      <c r="F99" s="2">
+        <v>5</v>
+      </c>
+      <c r="G99" s="2">
         <f t="shared" si="17"/>
-        <v>5</v>
-      </c>
-      <c r="G99" s="2">
+        <v>100</v>
+      </c>
+      <c r="H99" s="2">
         <f t="shared" si="18"/>
-        <v>100</v>
-      </c>
-      <c r="H99" s="2">
+        <v>10</v>
+      </c>
+      <c r="I99" s="2">
         <f t="shared" si="19"/>
         <v>10</v>
       </c>
-      <c r="I99" s="2">
+      <c r="J99" s="2">
         <f t="shared" si="20"/>
         <v>10</v>
       </c>
-      <c r="J99" s="2">
+      <c r="K99" s="2">
         <f t="shared" si="21"/>
         <v>10</v>
       </c>
-      <c r="K99" s="2">
+      <c r="L99" s="2">
         <f t="shared" si="22"/>
         <v>10</v>
       </c>
-      <c r="L99" s="2">
-        <f t="shared" si="23"/>
-        <v>10</v>
-      </c>
       <c r="M99" s="2">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1016</v>
       </c>
       <c r="N99" s="2">
         <v>105</v>
@@ -6323,52 +6228,51 @@
         <v>97</v>
       </c>
       <c r="B100" s="2">
+        <f t="shared" si="12"/>
+        <v>510</v>
+      </c>
+      <c r="C100" s="2">
         <f t="shared" si="13"/>
-        <v>510</v>
-      </c>
-      <c r="C100" s="2">
+        <v>293</v>
+      </c>
+      <c r="D100" s="2">
         <f t="shared" si="14"/>
-        <v>293</v>
-      </c>
-      <c r="D100" s="2">
+        <v>12720</v>
+      </c>
+      <c r="E100" s="2">
         <f t="shared" si="15"/>
-        <v>12720</v>
-      </c>
-      <c r="E100" s="2">
+        <v>202</v>
+      </c>
+      <c r="F100" s="2">
         <f t="shared" si="16"/>
-        <v>202</v>
-      </c>
-      <c r="F100" s="2">
+        <v>5</v>
+      </c>
+      <c r="G100" s="2">
         <f t="shared" si="17"/>
-        <v>5</v>
-      </c>
-      <c r="G100" s="2">
+        <v>100</v>
+      </c>
+      <c r="H100" s="2">
         <f t="shared" si="18"/>
-        <v>100</v>
-      </c>
-      <c r="H100" s="2">
+        <v>10</v>
+      </c>
+      <c r="I100" s="2">
         <f t="shared" si="19"/>
         <v>10</v>
       </c>
-      <c r="I100" s="2">
+      <c r="J100" s="2">
         <f t="shared" si="20"/>
         <v>10</v>
       </c>
-      <c r="J100" s="2">
+      <c r="K100" s="2">
         <f t="shared" si="21"/>
         <v>10</v>
       </c>
-      <c r="K100" s="2">
+      <c r="L100" s="2">
         <f t="shared" si="22"/>
         <v>10</v>
       </c>
-      <c r="L100" s="2">
-        <f t="shared" si="23"/>
-        <v>10</v>
-      </c>
       <c r="M100" s="2">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1017</v>
       </c>
       <c r="N100" s="2">
         <v>106</v>
@@ -6382,52 +6286,51 @@
         <v>98</v>
       </c>
       <c r="B101" s="2">
+        <f t="shared" si="12"/>
+        <v>515</v>
+      </c>
+      <c r="C101" s="2">
         <f t="shared" si="13"/>
-        <v>515</v>
-      </c>
-      <c r="C101" s="2">
+        <v>296</v>
+      </c>
+      <c r="D101" s="2">
         <f t="shared" si="14"/>
-        <v>296</v>
-      </c>
-      <c r="D101" s="2">
+        <v>12840</v>
+      </c>
+      <c r="E101" s="2">
         <f t="shared" si="15"/>
-        <v>12840</v>
-      </c>
-      <c r="E101" s="2">
+        <v>204</v>
+      </c>
+      <c r="F101" s="2">
         <f t="shared" si="16"/>
-        <v>204</v>
-      </c>
-      <c r="F101" s="2">
+        <v>5</v>
+      </c>
+      <c r="G101" s="2">
         <f t="shared" si="17"/>
-        <v>5</v>
-      </c>
-      <c r="G101" s="2">
+        <v>100</v>
+      </c>
+      <c r="H101" s="2">
         <f t="shared" si="18"/>
-        <v>100</v>
-      </c>
-      <c r="H101" s="2">
+        <v>10</v>
+      </c>
+      <c r="I101" s="2">
         <f t="shared" si="19"/>
         <v>10</v>
       </c>
-      <c r="I101" s="2">
+      <c r="J101" s="2">
         <f t="shared" si="20"/>
         <v>10</v>
       </c>
-      <c r="J101" s="2">
+      <c r="K101" s="2">
         <f t="shared" si="21"/>
         <v>10</v>
       </c>
-      <c r="K101" s="2">
+      <c r="L101" s="2">
         <f t="shared" si="22"/>
         <v>10</v>
       </c>
-      <c r="L101" s="2">
-        <f t="shared" si="23"/>
-        <v>10</v>
-      </c>
       <c r="M101" s="2">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1018</v>
       </c>
       <c r="N101" s="2">
         <v>107</v>
@@ -6441,52 +6344,51 @@
         <v>99</v>
       </c>
       <c r="B102" s="2">
+        <f t="shared" si="12"/>
+        <v>520</v>
+      </c>
+      <c r="C102" s="2">
         <f t="shared" si="13"/>
-        <v>520</v>
-      </c>
-      <c r="C102" s="2">
+        <v>299</v>
+      </c>
+      <c r="D102" s="2">
         <f t="shared" si="14"/>
-        <v>299</v>
-      </c>
-      <c r="D102" s="2">
+        <v>12960</v>
+      </c>
+      <c r="E102" s="2">
         <f t="shared" si="15"/>
-        <v>12960</v>
-      </c>
-      <c r="E102" s="2">
+        <v>206</v>
+      </c>
+      <c r="F102" s="2">
         <f t="shared" si="16"/>
-        <v>206</v>
-      </c>
-      <c r="F102" s="2">
+        <v>5</v>
+      </c>
+      <c r="G102" s="2">
         <f t="shared" si="17"/>
-        <v>5</v>
-      </c>
-      <c r="G102" s="2">
+        <v>100</v>
+      </c>
+      <c r="H102" s="2">
         <f t="shared" si="18"/>
-        <v>100</v>
-      </c>
-      <c r="H102" s="2">
+        <v>10</v>
+      </c>
+      <c r="I102" s="2">
         <f t="shared" si="19"/>
         <v>10</v>
       </c>
-      <c r="I102" s="2">
+      <c r="J102" s="2">
         <f t="shared" si="20"/>
         <v>10</v>
       </c>
-      <c r="J102" s="2">
+      <c r="K102" s="2">
         <f t="shared" si="21"/>
         <v>10</v>
       </c>
-      <c r="K102" s="2">
+      <c r="L102" s="2">
         <f t="shared" si="22"/>
         <v>10</v>
       </c>
-      <c r="L102" s="2">
-        <f t="shared" si="23"/>
-        <v>10</v>
-      </c>
       <c r="M102" s="2">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1019</v>
       </c>
       <c r="N102" s="2">
         <v>108</v>
@@ -6500,52 +6402,51 @@
         <v>100</v>
       </c>
       <c r="B103" s="2">
+        <f t="shared" si="12"/>
+        <v>525</v>
+      </c>
+      <c r="C103" s="2">
         <f t="shared" si="13"/>
-        <v>525</v>
-      </c>
-      <c r="C103" s="2">
+        <v>302</v>
+      </c>
+      <c r="D103" s="2">
         <f t="shared" si="14"/>
-        <v>302</v>
-      </c>
-      <c r="D103" s="2">
+        <v>13080</v>
+      </c>
+      <c r="E103" s="2">
         <f t="shared" si="15"/>
-        <v>13080</v>
-      </c>
-      <c r="E103" s="2">
+        <v>208</v>
+      </c>
+      <c r="F103" s="2">
         <f t="shared" si="16"/>
-        <v>208</v>
-      </c>
-      <c r="F103" s="2">
+        <v>5</v>
+      </c>
+      <c r="G103" s="2">
         <f t="shared" si="17"/>
-        <v>5</v>
-      </c>
-      <c r="G103" s="2">
+        <v>100</v>
+      </c>
+      <c r="H103" s="2">
         <f t="shared" si="18"/>
-        <v>100</v>
-      </c>
-      <c r="H103" s="2">
+        <v>10</v>
+      </c>
+      <c r="I103" s="2">
         <f t="shared" si="19"/>
         <v>10</v>
       </c>
-      <c r="I103" s="2">
+      <c r="J103" s="2">
         <f t="shared" si="20"/>
         <v>10</v>
       </c>
-      <c r="J103" s="2">
+      <c r="K103" s="2">
         <f t="shared" si="21"/>
         <v>10</v>
       </c>
-      <c r="K103" s="2">
+      <c r="L103" s="2">
         <f t="shared" si="22"/>
         <v>10</v>
       </c>
-      <c r="L103" s="2">
-        <f t="shared" si="23"/>
-        <v>10</v>
-      </c>
       <c r="M103" s="2">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1020</v>
       </c>
       <c r="N103" s="2">
         <v>109</v>

--- a/Assets/Excel/Stage.xlsx
+++ b/Assets/Excel/Stage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenBox\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{819691D6-694C-4A34-8934-22069BE15743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69699C5B-E4DB-456D-BC68-96310EC4FEE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipment" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="46">
   <si>
     <t>Int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -111,14 +111,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>暴击率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>爆伤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>反击</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -166,6 +158,66 @@
     <t>RewardSpeedUp</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>暴击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>强化爆伤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弱化爆伤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最终增伤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最终减伤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>强化治疗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弱化治疗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>强化宠物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弱化宠物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageIncrease</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageDecrease</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Healing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AntiHealing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PetIncrease</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PetDecrease</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -196,12 +248,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -216,12 +274,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -504,7 +565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O103"/>
+  <dimension ref="A1:AB103"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.25" style="2" customWidth="1"/>
@@ -513,19 +574,31 @@
     <col min="4" max="4" width="7.125" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.5" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="2"/>
+    <col min="7" max="7" width="11.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.875" customWidth="1"/>
+    <col min="23" max="24" width="11" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="17.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -542,37 +615,82 @@
         <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="str">
+        <f>"抗"&amp;F1</f>
+        <v>抗暴击</v>
+      </c>
+      <c r="M1" s="1" t="str">
+        <f>"抗"&amp;G1</f>
+        <v>抗反击</v>
+      </c>
+      <c r="N1" s="1" t="str">
+        <f>"抗"&amp;H1</f>
+        <v>抗连击</v>
+      </c>
+      <c r="O1" s="1" t="str">
+        <f>"抗"&amp;I1</f>
+        <v>抗闪避</v>
+      </c>
+      <c r="P1" s="1" t="str">
+        <f>"抗"&amp;J1</f>
+        <v>抗击晕</v>
+      </c>
+      <c r="Q1" s="1" t="str">
+        <f>"抗"&amp;K1</f>
+        <v>抗吸血</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>30</v>
+      <c r="AA1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -610,16 +728,55 @@
         <v>14</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -639,34 +796,80 @@
         <v>7</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L3" s="3" t="str">
+        <f>"Anti"&amp;F3</f>
+        <v>AntiCritRate</v>
+      </c>
+      <c r="M3" s="3" t="str">
+        <f>"Anti"&amp;G3</f>
+        <v>AntiCounterRate</v>
+      </c>
+      <c r="N3" s="3" t="str">
+        <f>"Anti"&amp;H3</f>
+        <v>AntiComboRate</v>
+      </c>
+      <c r="O3" s="3" t="str">
+        <f>"Anti"&amp;I3</f>
+        <v>AntiDodgeRate</v>
+      </c>
+      <c r="P3" s="3" t="str">
+        <f>"Anti"&amp;J3</f>
+        <v>AntiStunRate</v>
+      </c>
+      <c r="Q3" s="3" t="str">
+        <f>"Anti"&amp;K3</f>
+        <v>AntiLifeStealRate</v>
+      </c>
+      <c r="R3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>32</v>
+      <c r="S3" s="2" t="str">
+        <f>"Anti"&amp;R3</f>
+        <v>AntiCritDmg</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -686,34 +889,73 @@
         <v>5</v>
       </c>
       <c r="G4" s="2">
+        <v>10</v>
+      </c>
+      <c r="H4" s="2">
+        <v>10</v>
+      </c>
+      <c r="I4" s="2">
+        <v>10</v>
+      </c>
+      <c r="J4" s="2">
+        <v>10</v>
+      </c>
+      <c r="K4" s="2">
+        <v>10</v>
+      </c>
+      <c r="L4" s="2">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2">
+        <v>0</v>
+      </c>
+      <c r="N4" s="2">
+        <v>0</v>
+      </c>
+      <c r="O4" s="2">
+        <v>0</v>
+      </c>
+      <c r="P4" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>0</v>
+      </c>
+      <c r="R4" s="2">
         <v>100</v>
       </c>
-      <c r="H4" s="2">
-        <v>10</v>
-      </c>
-      <c r="I4" s="2">
-        <v>10</v>
-      </c>
-      <c r="J4" s="2">
-        <v>10</v>
-      </c>
-      <c r="K4" s="2">
-        <v>10</v>
-      </c>
-      <c r="L4" s="2">
-        <v>10</v>
-      </c>
-      <c r="M4" s="2">
+      <c r="S4" s="2">
+        <v>0</v>
+      </c>
+      <c r="T4" s="2">
+        <v>0</v>
+      </c>
+      <c r="U4" s="2">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2">
+        <v>0</v>
+      </c>
+      <c r="W4" s="2">
+        <v>0</v>
+      </c>
+      <c r="X4" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="2">
         <v>1001</v>
       </c>
-      <c r="N4" s="2">
-        <v>10</v>
-      </c>
-      <c r="O4" s="2">
+      <c r="AA4" s="2">
+        <v>10</v>
+      </c>
+      <c r="AB4" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -738,8 +980,8 @@
         <v>5</v>
       </c>
       <c r="G5" s="2">
-        <f t="shared" ref="G5:M5" si="0">G4</f>
-        <v>100</v>
+        <f t="shared" ref="G5:K5" si="0">G4</f>
+        <v>10</v>
       </c>
       <c r="H5" s="2">
         <f t="shared" si="0"/>
@@ -758,20 +1000,59 @@
         <v>10</v>
       </c>
       <c r="L5" s="2">
-        <f t="shared" si="0"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M5" s="2">
+        <v>0</v>
+      </c>
+      <c r="N5" s="2">
+        <v>0</v>
+      </c>
+      <c r="O5" s="2">
+        <v>0</v>
+      </c>
+      <c r="P5" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>0</v>
+      </c>
+      <c r="R5" s="2">
+        <f>R4</f>
+        <v>100</v>
+      </c>
+      <c r="S5" s="2">
+        <v>0</v>
+      </c>
+      <c r="T5" s="2">
+        <v>0</v>
+      </c>
+      <c r="U5" s="2">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2">
+        <v>0</v>
+      </c>
+      <c r="W5" s="2">
+        <v>0</v>
+      </c>
+      <c r="X5" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="2">
         <v>1002</v>
       </c>
-      <c r="N5" s="2">
+      <c r="AA5" s="2">
         <v>11</v>
       </c>
-      <c r="O5" s="2">
+      <c r="AB5" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -797,7 +1078,7 @@
       </c>
       <c r="G6" s="2">
         <f t="shared" ref="G6:G69" si="6">G5</f>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H6" s="2">
         <f t="shared" ref="H6:H69" si="7">H5</f>
@@ -816,20 +1097,59 @@
         <v>10</v>
       </c>
       <c r="L6" s="2">
-        <f t="shared" ref="L6:L69" si="11">L5</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2">
+        <v>0</v>
+      </c>
+      <c r="N6" s="2">
+        <v>0</v>
+      </c>
+      <c r="O6" s="2">
+        <v>0</v>
+      </c>
+      <c r="P6" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2">
+        <f t="shared" ref="R6:R69" si="11">R5</f>
+        <v>100</v>
+      </c>
+      <c r="S6" s="2">
+        <v>0</v>
+      </c>
+      <c r="T6" s="2">
+        <v>0</v>
+      </c>
+      <c r="U6" s="2">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2">
+        <v>0</v>
+      </c>
+      <c r="W6" s="2">
+        <v>0</v>
+      </c>
+      <c r="X6" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="2">
         <v>1003</v>
       </c>
-      <c r="N6" s="2">
+      <c r="AA6" s="2">
         <v>12</v>
       </c>
-      <c r="O6" s="2">
+      <c r="AB6" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -855,7 +1175,7 @@
       </c>
       <c r="G7" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H7" s="2">
         <f t="shared" si="7"/>
@@ -874,20 +1194,59 @@
         <v>10</v>
       </c>
       <c r="L7" s="2">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2">
+        <v>0</v>
+      </c>
+      <c r="N7" s="2">
+        <v>0</v>
+      </c>
+      <c r="O7" s="2">
+        <v>0</v>
+      </c>
+      <c r="P7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>0</v>
+      </c>
+      <c r="R7" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M7" s="2">
+        <v>100</v>
+      </c>
+      <c r="S7" s="2">
+        <v>0</v>
+      </c>
+      <c r="T7" s="2">
+        <v>0</v>
+      </c>
+      <c r="U7" s="2">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2">
+        <v>0</v>
+      </c>
+      <c r="W7" s="2">
+        <v>0</v>
+      </c>
+      <c r="X7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="2">
         <v>1004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="AA7" s="2">
         <v>13</v>
       </c>
-      <c r="O7" s="2">
+      <c r="AB7" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -913,7 +1272,7 @@
       </c>
       <c r="G8" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H8" s="2">
         <f t="shared" si="7"/>
@@ -932,20 +1291,59 @@
         <v>10</v>
       </c>
       <c r="L8" s="2">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2">
+        <v>0</v>
+      </c>
+      <c r="O8" s="2">
+        <v>0</v>
+      </c>
+      <c r="P8" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>0</v>
+      </c>
+      <c r="R8" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M8" s="2">
+        <v>100</v>
+      </c>
+      <c r="S8" s="2">
+        <v>0</v>
+      </c>
+      <c r="T8" s="2">
+        <v>0</v>
+      </c>
+      <c r="U8" s="2">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2">
+        <v>0</v>
+      </c>
+      <c r="W8" s="2">
+        <v>0</v>
+      </c>
+      <c r="X8" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="2">
         <v>1005</v>
       </c>
-      <c r="N8" s="2">
+      <c r="AA8" s="2">
         <v>14</v>
       </c>
-      <c r="O8" s="2">
+      <c r="AB8" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>6</v>
       </c>
@@ -971,7 +1369,7 @@
       </c>
       <c r="G9" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H9" s="2">
         <f t="shared" si="7"/>
@@ -990,20 +1388,59 @@
         <v>10</v>
       </c>
       <c r="L9" s="2">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2">
+        <v>0</v>
+      </c>
+      <c r="N9" s="2">
+        <v>0</v>
+      </c>
+      <c r="O9" s="2">
+        <v>0</v>
+      </c>
+      <c r="P9" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>0</v>
+      </c>
+      <c r="R9" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M9" s="2">
+        <v>100</v>
+      </c>
+      <c r="S9" s="2">
+        <v>0</v>
+      </c>
+      <c r="T9" s="2">
+        <v>0</v>
+      </c>
+      <c r="U9" s="2">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2">
+        <v>0</v>
+      </c>
+      <c r="W9" s="2">
+        <v>0</v>
+      </c>
+      <c r="X9" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="2">
         <v>1006</v>
       </c>
-      <c r="N9" s="2">
+      <c r="AA9" s="2">
         <v>15</v>
       </c>
-      <c r="O9" s="2">
+      <c r="AB9" s="2">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>7</v>
       </c>
@@ -1029,7 +1466,7 @@
       </c>
       <c r="G10" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H10" s="2">
         <f t="shared" si="7"/>
@@ -1048,20 +1485,59 @@
         <v>10</v>
       </c>
       <c r="L10" s="2">
+        <v>0</v>
+      </c>
+      <c r="M10" s="2">
+        <v>0</v>
+      </c>
+      <c r="N10" s="2">
+        <v>0</v>
+      </c>
+      <c r="O10" s="2">
+        <v>0</v>
+      </c>
+      <c r="P10" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>0</v>
+      </c>
+      <c r="R10" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M10" s="2">
+        <v>100</v>
+      </c>
+      <c r="S10" s="2">
+        <v>0</v>
+      </c>
+      <c r="T10" s="2">
+        <v>0</v>
+      </c>
+      <c r="U10" s="2">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2">
+        <v>0</v>
+      </c>
+      <c r="W10" s="2">
+        <v>0</v>
+      </c>
+      <c r="X10" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="2">
         <v>1007</v>
       </c>
-      <c r="N10" s="2">
+      <c r="AA10" s="2">
         <v>16</v>
       </c>
-      <c r="O10" s="2">
+      <c r="AB10" s="2">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>8</v>
       </c>
@@ -1087,7 +1563,7 @@
       </c>
       <c r="G11" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H11" s="2">
         <f t="shared" si="7"/>
@@ -1106,20 +1582,59 @@
         <v>10</v>
       </c>
       <c r="L11" s="2">
+        <v>0</v>
+      </c>
+      <c r="M11" s="2">
+        <v>0</v>
+      </c>
+      <c r="N11" s="2">
+        <v>0</v>
+      </c>
+      <c r="O11" s="2">
+        <v>0</v>
+      </c>
+      <c r="P11" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>0</v>
+      </c>
+      <c r="R11" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M11" s="2">
+        <v>100</v>
+      </c>
+      <c r="S11" s="2">
+        <v>0</v>
+      </c>
+      <c r="T11" s="2">
+        <v>0</v>
+      </c>
+      <c r="U11" s="2">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2">
+        <v>0</v>
+      </c>
+      <c r="W11" s="2">
+        <v>0</v>
+      </c>
+      <c r="X11" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="2">
         <v>1008</v>
       </c>
-      <c r="N11" s="2">
+      <c r="AA11" s="2">
         <v>17</v>
       </c>
-      <c r="O11" s="2">
+      <c r="AB11" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>9</v>
       </c>
@@ -1145,7 +1660,7 @@
       </c>
       <c r="G12" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H12" s="2">
         <f t="shared" si="7"/>
@@ -1164,20 +1679,59 @@
         <v>10</v>
       </c>
       <c r="L12" s="2">
+        <v>0</v>
+      </c>
+      <c r="M12" s="2">
+        <v>0</v>
+      </c>
+      <c r="N12" s="2">
+        <v>0</v>
+      </c>
+      <c r="O12" s="2">
+        <v>0</v>
+      </c>
+      <c r="P12" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>0</v>
+      </c>
+      <c r="R12" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M12" s="2">
+        <v>100</v>
+      </c>
+      <c r="S12" s="2">
+        <v>0</v>
+      </c>
+      <c r="T12" s="2">
+        <v>0</v>
+      </c>
+      <c r="U12" s="2">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2">
+        <v>0</v>
+      </c>
+      <c r="W12" s="2">
+        <v>0</v>
+      </c>
+      <c r="X12" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="2">
         <v>1009</v>
       </c>
-      <c r="N12" s="2">
+      <c r="AA12" s="2">
         <v>18</v>
       </c>
-      <c r="O12" s="2">
+      <c r="AB12" s="2">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>10</v>
       </c>
@@ -1203,7 +1757,7 @@
       </c>
       <c r="G13" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H13" s="2">
         <f t="shared" si="7"/>
@@ -1222,20 +1776,59 @@
         <v>10</v>
       </c>
       <c r="L13" s="2">
+        <v>0</v>
+      </c>
+      <c r="M13" s="2">
+        <v>0</v>
+      </c>
+      <c r="N13" s="2">
+        <v>0</v>
+      </c>
+      <c r="O13" s="2">
+        <v>0</v>
+      </c>
+      <c r="P13" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>0</v>
+      </c>
+      <c r="R13" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M13" s="2">
+        <v>100</v>
+      </c>
+      <c r="S13" s="2">
+        <v>0</v>
+      </c>
+      <c r="T13" s="2">
+        <v>0</v>
+      </c>
+      <c r="U13" s="2">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2">
+        <v>0</v>
+      </c>
+      <c r="W13" s="2">
+        <v>0</v>
+      </c>
+      <c r="X13" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="2">
         <v>1010</v>
       </c>
-      <c r="N13" s="2">
+      <c r="AA13" s="2">
         <v>19</v>
       </c>
-      <c r="O13" s="2">
+      <c r="AB13" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>11</v>
       </c>
@@ -1261,7 +1854,7 @@
       </c>
       <c r="G14" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H14" s="2">
         <f t="shared" si="7"/>
@@ -1280,20 +1873,59 @@
         <v>10</v>
       </c>
       <c r="L14" s="2">
+        <v>0</v>
+      </c>
+      <c r="M14" s="2">
+        <v>0</v>
+      </c>
+      <c r="N14" s="2">
+        <v>0</v>
+      </c>
+      <c r="O14" s="2">
+        <v>0</v>
+      </c>
+      <c r="P14" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>0</v>
+      </c>
+      <c r="R14" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M14" s="2">
+        <v>100</v>
+      </c>
+      <c r="S14" s="2">
+        <v>0</v>
+      </c>
+      <c r="T14" s="2">
+        <v>0</v>
+      </c>
+      <c r="U14" s="2">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2">
+        <v>0</v>
+      </c>
+      <c r="W14" s="2">
+        <v>0</v>
+      </c>
+      <c r="X14" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="2">
         <v>1011</v>
       </c>
-      <c r="N14" s="2">
+      <c r="AA14" s="2">
         <v>20</v>
       </c>
-      <c r="O14" s="2">
+      <c r="AB14" s="2">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>12</v>
       </c>
@@ -1319,7 +1951,7 @@
       </c>
       <c r="G15" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H15" s="2">
         <f t="shared" si="7"/>
@@ -1338,20 +1970,59 @@
         <v>10</v>
       </c>
       <c r="L15" s="2">
+        <v>0</v>
+      </c>
+      <c r="M15" s="2">
+        <v>0</v>
+      </c>
+      <c r="N15" s="2">
+        <v>0</v>
+      </c>
+      <c r="O15" s="2">
+        <v>0</v>
+      </c>
+      <c r="P15" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>0</v>
+      </c>
+      <c r="R15" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M15" s="2">
+        <v>100</v>
+      </c>
+      <c r="S15" s="2">
+        <v>0</v>
+      </c>
+      <c r="T15" s="2">
+        <v>0</v>
+      </c>
+      <c r="U15" s="2">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2">
+        <v>0</v>
+      </c>
+      <c r="W15" s="2">
+        <v>0</v>
+      </c>
+      <c r="X15" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="2">
         <v>1012</v>
       </c>
-      <c r="N15" s="2">
+      <c r="AA15" s="2">
         <v>21</v>
       </c>
-      <c r="O15" s="2">
+      <c r="AB15" s="2">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>13</v>
       </c>
@@ -1377,7 +2048,7 @@
       </c>
       <c r="G16" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H16" s="2">
         <f t="shared" si="7"/>
@@ -1396,20 +2067,59 @@
         <v>10</v>
       </c>
       <c r="L16" s="2">
+        <v>0</v>
+      </c>
+      <c r="M16" s="2">
+        <v>0</v>
+      </c>
+      <c r="N16" s="2">
+        <v>0</v>
+      </c>
+      <c r="O16" s="2">
+        <v>0</v>
+      </c>
+      <c r="P16" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>0</v>
+      </c>
+      <c r="R16" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M16" s="2">
+        <v>100</v>
+      </c>
+      <c r="S16" s="2">
+        <v>0</v>
+      </c>
+      <c r="T16" s="2">
+        <v>0</v>
+      </c>
+      <c r="U16" s="2">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2">
+        <v>0</v>
+      </c>
+      <c r="W16" s="2">
+        <v>0</v>
+      </c>
+      <c r="X16" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="2">
         <v>1013</v>
       </c>
-      <c r="N16" s="2">
+      <c r="AA16" s="2">
         <v>22</v>
       </c>
-      <c r="O16" s="2">
+      <c r="AB16" s="2">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>14</v>
       </c>
@@ -1435,7 +2145,7 @@
       </c>
       <c r="G17" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H17" s="2">
         <f t="shared" si="7"/>
@@ -1454,20 +2164,59 @@
         <v>10</v>
       </c>
       <c r="L17" s="2">
+        <v>0</v>
+      </c>
+      <c r="M17" s="2">
+        <v>0</v>
+      </c>
+      <c r="N17" s="2">
+        <v>0</v>
+      </c>
+      <c r="O17" s="2">
+        <v>0</v>
+      </c>
+      <c r="P17" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>0</v>
+      </c>
+      <c r="R17" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M17" s="2">
+        <v>100</v>
+      </c>
+      <c r="S17" s="2">
+        <v>0</v>
+      </c>
+      <c r="T17" s="2">
+        <v>0</v>
+      </c>
+      <c r="U17" s="2">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2">
+        <v>0</v>
+      </c>
+      <c r="W17" s="2">
+        <v>0</v>
+      </c>
+      <c r="X17" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="2">
         <v>1014</v>
       </c>
-      <c r="N17" s="2">
+      <c r="AA17" s="2">
         <v>23</v>
       </c>
-      <c r="O17" s="2">
+      <c r="AB17" s="2">
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>15</v>
       </c>
@@ -1493,7 +2242,7 @@
       </c>
       <c r="G18" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H18" s="2">
         <f t="shared" si="7"/>
@@ -1512,20 +2261,59 @@
         <v>10</v>
       </c>
       <c r="L18" s="2">
+        <v>0</v>
+      </c>
+      <c r="M18" s="2">
+        <v>0</v>
+      </c>
+      <c r="N18" s="2">
+        <v>0</v>
+      </c>
+      <c r="O18" s="2">
+        <v>0</v>
+      </c>
+      <c r="P18" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="2">
+        <v>0</v>
+      </c>
+      <c r="R18" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M18" s="2">
+        <v>100</v>
+      </c>
+      <c r="S18" s="2">
+        <v>0</v>
+      </c>
+      <c r="T18" s="2">
+        <v>0</v>
+      </c>
+      <c r="U18" s="2">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2">
+        <v>0</v>
+      </c>
+      <c r="W18" s="2">
+        <v>0</v>
+      </c>
+      <c r="X18" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="2">
         <v>1015</v>
       </c>
-      <c r="N18" s="2">
+      <c r="AA18" s="2">
         <v>24</v>
       </c>
-      <c r="O18" s="2">
+      <c r="AB18" s="2">
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>16</v>
       </c>
@@ -1551,7 +2339,7 @@
       </c>
       <c r="G19" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H19" s="2">
         <f t="shared" si="7"/>
@@ -1570,20 +2358,59 @@
         <v>10</v>
       </c>
       <c r="L19" s="2">
+        <v>0</v>
+      </c>
+      <c r="M19" s="2">
+        <v>0</v>
+      </c>
+      <c r="N19" s="2">
+        <v>0</v>
+      </c>
+      <c r="O19" s="2">
+        <v>0</v>
+      </c>
+      <c r="P19" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="2">
+        <v>0</v>
+      </c>
+      <c r="R19" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M19" s="2">
+        <v>100</v>
+      </c>
+      <c r="S19" s="2">
+        <v>0</v>
+      </c>
+      <c r="T19" s="2">
+        <v>0</v>
+      </c>
+      <c r="U19" s="2">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2">
+        <v>0</v>
+      </c>
+      <c r="W19" s="2">
+        <v>0</v>
+      </c>
+      <c r="X19" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="2">
         <v>1016</v>
       </c>
-      <c r="N19" s="2">
+      <c r="AA19" s="2">
         <v>25</v>
       </c>
-      <c r="O19" s="2">
+      <c r="AB19" s="2">
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>17</v>
       </c>
@@ -1609,7 +2436,7 @@
       </c>
       <c r="G20" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H20" s="2">
         <f t="shared" si="7"/>
@@ -1628,20 +2455,59 @@
         <v>10</v>
       </c>
       <c r="L20" s="2">
+        <v>0</v>
+      </c>
+      <c r="M20" s="2">
+        <v>0</v>
+      </c>
+      <c r="N20" s="2">
+        <v>0</v>
+      </c>
+      <c r="O20" s="2">
+        <v>0</v>
+      </c>
+      <c r="P20" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="2">
+        <v>0</v>
+      </c>
+      <c r="R20" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M20" s="2">
+        <v>100</v>
+      </c>
+      <c r="S20" s="2">
+        <v>0</v>
+      </c>
+      <c r="T20" s="2">
+        <v>0</v>
+      </c>
+      <c r="U20" s="2">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2">
+        <v>0</v>
+      </c>
+      <c r="W20" s="2">
+        <v>0</v>
+      </c>
+      <c r="X20" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="2">
         <v>1017</v>
       </c>
-      <c r="N20" s="2">
+      <c r="AA20" s="2">
         <v>26</v>
       </c>
-      <c r="O20" s="2">
+      <c r="AB20" s="2">
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>18</v>
       </c>
@@ -1667,7 +2533,7 @@
       </c>
       <c r="G21" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H21" s="2">
         <f t="shared" si="7"/>
@@ -1686,20 +2552,59 @@
         <v>10</v>
       </c>
       <c r="L21" s="2">
+        <v>0</v>
+      </c>
+      <c r="M21" s="2">
+        <v>0</v>
+      </c>
+      <c r="N21" s="2">
+        <v>0</v>
+      </c>
+      <c r="O21" s="2">
+        <v>0</v>
+      </c>
+      <c r="P21" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="2">
+        <v>0</v>
+      </c>
+      <c r="R21" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M21" s="2">
+        <v>100</v>
+      </c>
+      <c r="S21" s="2">
+        <v>0</v>
+      </c>
+      <c r="T21" s="2">
+        <v>0</v>
+      </c>
+      <c r="U21" s="2">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2">
+        <v>0</v>
+      </c>
+      <c r="W21" s="2">
+        <v>0</v>
+      </c>
+      <c r="X21" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="2">
         <v>1018</v>
       </c>
-      <c r="N21" s="2">
+      <c r="AA21" s="2">
         <v>27</v>
       </c>
-      <c r="O21" s="2">
+      <c r="AB21" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>19</v>
       </c>
@@ -1725,7 +2630,7 @@
       </c>
       <c r="G22" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H22" s="2">
         <f t="shared" si="7"/>
@@ -1744,20 +2649,59 @@
         <v>10</v>
       </c>
       <c r="L22" s="2">
+        <v>0</v>
+      </c>
+      <c r="M22" s="2">
+        <v>0</v>
+      </c>
+      <c r="N22" s="2">
+        <v>0</v>
+      </c>
+      <c r="O22" s="2">
+        <v>0</v>
+      </c>
+      <c r="P22" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="2">
+        <v>0</v>
+      </c>
+      <c r="R22" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M22" s="2">
+        <v>100</v>
+      </c>
+      <c r="S22" s="2">
+        <v>0</v>
+      </c>
+      <c r="T22" s="2">
+        <v>0</v>
+      </c>
+      <c r="U22" s="2">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2">
+        <v>0</v>
+      </c>
+      <c r="W22" s="2">
+        <v>0</v>
+      </c>
+      <c r="X22" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="2">
         <v>1019</v>
       </c>
-      <c r="N22" s="2">
+      <c r="AA22" s="2">
         <v>28</v>
       </c>
-      <c r="O22" s="2">
+      <c r="AB22" s="2">
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>20</v>
       </c>
@@ -1783,7 +2727,7 @@
       </c>
       <c r="G23" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H23" s="2">
         <f t="shared" si="7"/>
@@ -1802,20 +2746,59 @@
         <v>10</v>
       </c>
       <c r="L23" s="2">
+        <v>0</v>
+      </c>
+      <c r="M23" s="2">
+        <v>0</v>
+      </c>
+      <c r="N23" s="2">
+        <v>0</v>
+      </c>
+      <c r="O23" s="2">
+        <v>0</v>
+      </c>
+      <c r="P23" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="2">
+        <v>0</v>
+      </c>
+      <c r="R23" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M23" s="2">
+        <v>100</v>
+      </c>
+      <c r="S23" s="2">
+        <v>0</v>
+      </c>
+      <c r="T23" s="2">
+        <v>0</v>
+      </c>
+      <c r="U23" s="2">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2">
+        <v>0</v>
+      </c>
+      <c r="W23" s="2">
+        <v>0</v>
+      </c>
+      <c r="X23" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="2">
         <v>1020</v>
       </c>
-      <c r="N23" s="2">
+      <c r="AA23" s="2">
         <v>29</v>
       </c>
-      <c r="O23" s="2">
+      <c r="AB23" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>21</v>
       </c>
@@ -1841,7 +2824,7 @@
       </c>
       <c r="G24" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H24" s="2">
         <f t="shared" si="7"/>
@@ -1860,20 +2843,59 @@
         <v>10</v>
       </c>
       <c r="L24" s="2">
+        <v>0</v>
+      </c>
+      <c r="M24" s="2">
+        <v>0</v>
+      </c>
+      <c r="N24" s="2">
+        <v>0</v>
+      </c>
+      <c r="O24" s="2">
+        <v>0</v>
+      </c>
+      <c r="P24" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="2">
+        <v>0</v>
+      </c>
+      <c r="R24" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M24" s="2">
+        <v>100</v>
+      </c>
+      <c r="S24" s="2">
+        <v>0</v>
+      </c>
+      <c r="T24" s="2">
+        <v>0</v>
+      </c>
+      <c r="U24" s="2">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2">
+        <v>0</v>
+      </c>
+      <c r="W24" s="2">
+        <v>0</v>
+      </c>
+      <c r="X24" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="2">
         <v>1001</v>
       </c>
-      <c r="N24" s="2">
+      <c r="AA24" s="2">
         <v>30</v>
       </c>
-      <c r="O24" s="2">
+      <c r="AB24" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>22</v>
       </c>
@@ -1899,7 +2921,7 @@
       </c>
       <c r="G25" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H25" s="2">
         <f t="shared" si="7"/>
@@ -1918,20 +2940,59 @@
         <v>10</v>
       </c>
       <c r="L25" s="2">
+        <v>0</v>
+      </c>
+      <c r="M25" s="2">
+        <v>0</v>
+      </c>
+      <c r="N25" s="2">
+        <v>0</v>
+      </c>
+      <c r="O25" s="2">
+        <v>0</v>
+      </c>
+      <c r="P25" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="2">
+        <v>0</v>
+      </c>
+      <c r="R25" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M25" s="2">
+        <v>100</v>
+      </c>
+      <c r="S25" s="2">
+        <v>0</v>
+      </c>
+      <c r="T25" s="2">
+        <v>0</v>
+      </c>
+      <c r="U25" s="2">
+        <v>0</v>
+      </c>
+      <c r="V25" s="2">
+        <v>0</v>
+      </c>
+      <c r="W25" s="2">
+        <v>0</v>
+      </c>
+      <c r="X25" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="2">
         <v>1002</v>
       </c>
-      <c r="N25" s="2">
+      <c r="AA25" s="2">
         <v>31</v>
       </c>
-      <c r="O25" s="2">
+      <c r="AB25" s="2">
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>23</v>
       </c>
@@ -1957,7 +3018,7 @@
       </c>
       <c r="G26" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H26" s="2">
         <f t="shared" si="7"/>
@@ -1976,20 +3037,59 @@
         <v>10</v>
       </c>
       <c r="L26" s="2">
+        <v>0</v>
+      </c>
+      <c r="M26" s="2">
+        <v>0</v>
+      </c>
+      <c r="N26" s="2">
+        <v>0</v>
+      </c>
+      <c r="O26" s="2">
+        <v>0</v>
+      </c>
+      <c r="P26" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="2">
+        <v>0</v>
+      </c>
+      <c r="R26" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M26" s="2">
+        <v>100</v>
+      </c>
+      <c r="S26" s="2">
+        <v>0</v>
+      </c>
+      <c r="T26" s="2">
+        <v>0</v>
+      </c>
+      <c r="U26" s="2">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2">
+        <v>0</v>
+      </c>
+      <c r="W26" s="2">
+        <v>0</v>
+      </c>
+      <c r="X26" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="2">
         <v>1003</v>
       </c>
-      <c r="N26" s="2">
+      <c r="AA26" s="2">
         <v>32</v>
       </c>
-      <c r="O26" s="2">
+      <c r="AB26" s="2">
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>24</v>
       </c>
@@ -2015,7 +3115,7 @@
       </c>
       <c r="G27" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H27" s="2">
         <f t="shared" si="7"/>
@@ -2034,20 +3134,59 @@
         <v>10</v>
       </c>
       <c r="L27" s="2">
+        <v>0</v>
+      </c>
+      <c r="M27" s="2">
+        <v>0</v>
+      </c>
+      <c r="N27" s="2">
+        <v>0</v>
+      </c>
+      <c r="O27" s="2">
+        <v>0</v>
+      </c>
+      <c r="P27" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="2">
+        <v>0</v>
+      </c>
+      <c r="R27" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M27" s="2">
+        <v>100</v>
+      </c>
+      <c r="S27" s="2">
+        <v>0</v>
+      </c>
+      <c r="T27" s="2">
+        <v>0</v>
+      </c>
+      <c r="U27" s="2">
+        <v>0</v>
+      </c>
+      <c r="V27" s="2">
+        <v>0</v>
+      </c>
+      <c r="W27" s="2">
+        <v>0</v>
+      </c>
+      <c r="X27" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="2">
         <v>1004</v>
       </c>
-      <c r="N27" s="2">
+      <c r="AA27" s="2">
         <v>33</v>
       </c>
-      <c r="O27" s="2">
+      <c r="AB27" s="2">
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>25</v>
       </c>
@@ -2073,7 +3212,7 @@
       </c>
       <c r="G28" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H28" s="2">
         <f t="shared" si="7"/>
@@ -2092,20 +3231,59 @@
         <v>10</v>
       </c>
       <c r="L28" s="2">
+        <v>0</v>
+      </c>
+      <c r="M28" s="2">
+        <v>0</v>
+      </c>
+      <c r="N28" s="2">
+        <v>0</v>
+      </c>
+      <c r="O28" s="2">
+        <v>0</v>
+      </c>
+      <c r="P28" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="2">
+        <v>0</v>
+      </c>
+      <c r="R28" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M28" s="2">
+        <v>100</v>
+      </c>
+      <c r="S28" s="2">
+        <v>0</v>
+      </c>
+      <c r="T28" s="2">
+        <v>0</v>
+      </c>
+      <c r="U28" s="2">
+        <v>0</v>
+      </c>
+      <c r="V28" s="2">
+        <v>0</v>
+      </c>
+      <c r="W28" s="2">
+        <v>0</v>
+      </c>
+      <c r="X28" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="2">
         <v>1005</v>
       </c>
-      <c r="N28" s="2">
+      <c r="AA28" s="2">
         <v>34</v>
       </c>
-      <c r="O28" s="2">
+      <c r="AB28" s="2">
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>26</v>
       </c>
@@ -2131,7 +3309,7 @@
       </c>
       <c r="G29" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H29" s="2">
         <f t="shared" si="7"/>
@@ -2150,20 +3328,59 @@
         <v>10</v>
       </c>
       <c r="L29" s="2">
+        <v>0</v>
+      </c>
+      <c r="M29" s="2">
+        <v>0</v>
+      </c>
+      <c r="N29" s="2">
+        <v>0</v>
+      </c>
+      <c r="O29" s="2">
+        <v>0</v>
+      </c>
+      <c r="P29" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="2">
+        <v>0</v>
+      </c>
+      <c r="R29" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M29" s="2">
+        <v>100</v>
+      </c>
+      <c r="S29" s="2">
+        <v>0</v>
+      </c>
+      <c r="T29" s="2">
+        <v>0</v>
+      </c>
+      <c r="U29" s="2">
+        <v>0</v>
+      </c>
+      <c r="V29" s="2">
+        <v>0</v>
+      </c>
+      <c r="W29" s="2">
+        <v>0</v>
+      </c>
+      <c r="X29" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="2">
         <v>1006</v>
       </c>
-      <c r="N29" s="2">
+      <c r="AA29" s="2">
         <v>35</v>
       </c>
-      <c r="O29" s="2">
+      <c r="AB29" s="2">
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>27</v>
       </c>
@@ -2189,7 +3406,7 @@
       </c>
       <c r="G30" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H30" s="2">
         <f t="shared" si="7"/>
@@ -2208,20 +3425,59 @@
         <v>10</v>
       </c>
       <c r="L30" s="2">
+        <v>0</v>
+      </c>
+      <c r="M30" s="2">
+        <v>0</v>
+      </c>
+      <c r="N30" s="2">
+        <v>0</v>
+      </c>
+      <c r="O30" s="2">
+        <v>0</v>
+      </c>
+      <c r="P30" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="2">
+        <v>0</v>
+      </c>
+      <c r="R30" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M30" s="2">
+        <v>100</v>
+      </c>
+      <c r="S30" s="2">
+        <v>0</v>
+      </c>
+      <c r="T30" s="2">
+        <v>0</v>
+      </c>
+      <c r="U30" s="2">
+        <v>0</v>
+      </c>
+      <c r="V30" s="2">
+        <v>0</v>
+      </c>
+      <c r="W30" s="2">
+        <v>0</v>
+      </c>
+      <c r="X30" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="2">
         <v>1007</v>
       </c>
-      <c r="N30" s="2">
+      <c r="AA30" s="2">
         <v>36</v>
       </c>
-      <c r="O30" s="2">
+      <c r="AB30" s="2">
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>28</v>
       </c>
@@ -2247,7 +3503,7 @@
       </c>
       <c r="G31" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H31" s="2">
         <f t="shared" si="7"/>
@@ -2266,20 +3522,59 @@
         <v>10</v>
       </c>
       <c r="L31" s="2">
+        <v>0</v>
+      </c>
+      <c r="M31" s="2">
+        <v>0</v>
+      </c>
+      <c r="N31" s="2">
+        <v>0</v>
+      </c>
+      <c r="O31" s="2">
+        <v>0</v>
+      </c>
+      <c r="P31" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="2">
+        <v>0</v>
+      </c>
+      <c r="R31" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M31" s="2">
+        <v>100</v>
+      </c>
+      <c r="S31" s="2">
+        <v>0</v>
+      </c>
+      <c r="T31" s="2">
+        <v>0</v>
+      </c>
+      <c r="U31" s="2">
+        <v>0</v>
+      </c>
+      <c r="V31" s="2">
+        <v>0</v>
+      </c>
+      <c r="W31" s="2">
+        <v>0</v>
+      </c>
+      <c r="X31" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="2">
         <v>1008</v>
       </c>
-      <c r="N31" s="2">
+      <c r="AA31" s="2">
         <v>37</v>
       </c>
-      <c r="O31" s="2">
+      <c r="AB31" s="2">
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>29</v>
       </c>
@@ -2305,7 +3600,7 @@
       </c>
       <c r="G32" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H32" s="2">
         <f t="shared" si="7"/>
@@ -2324,20 +3619,59 @@
         <v>10</v>
       </c>
       <c r="L32" s="2">
+        <v>0</v>
+      </c>
+      <c r="M32" s="2">
+        <v>0</v>
+      </c>
+      <c r="N32" s="2">
+        <v>0</v>
+      </c>
+      <c r="O32" s="2">
+        <v>0</v>
+      </c>
+      <c r="P32" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="2">
+        <v>0</v>
+      </c>
+      <c r="R32" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M32" s="2">
+        <v>100</v>
+      </c>
+      <c r="S32" s="2">
+        <v>0</v>
+      </c>
+      <c r="T32" s="2">
+        <v>0</v>
+      </c>
+      <c r="U32" s="2">
+        <v>0</v>
+      </c>
+      <c r="V32" s="2">
+        <v>0</v>
+      </c>
+      <c r="W32" s="2">
+        <v>0</v>
+      </c>
+      <c r="X32" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="2">
         <v>1009</v>
       </c>
-      <c r="N32" s="2">
+      <c r="AA32" s="2">
         <v>38</v>
       </c>
-      <c r="O32" s="2">
+      <c r="AB32" s="2">
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>30</v>
       </c>
@@ -2363,7 +3697,7 @@
       </c>
       <c r="G33" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H33" s="2">
         <f t="shared" si="7"/>
@@ -2382,20 +3716,59 @@
         <v>10</v>
       </c>
       <c r="L33" s="2">
+        <v>0</v>
+      </c>
+      <c r="M33" s="2">
+        <v>0</v>
+      </c>
+      <c r="N33" s="2">
+        <v>0</v>
+      </c>
+      <c r="O33" s="2">
+        <v>0</v>
+      </c>
+      <c r="P33" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="2">
+        <v>0</v>
+      </c>
+      <c r="R33" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M33" s="2">
+        <v>100</v>
+      </c>
+      <c r="S33" s="2">
+        <v>0</v>
+      </c>
+      <c r="T33" s="2">
+        <v>0</v>
+      </c>
+      <c r="U33" s="2">
+        <v>0</v>
+      </c>
+      <c r="V33" s="2">
+        <v>0</v>
+      </c>
+      <c r="W33" s="2">
+        <v>0</v>
+      </c>
+      <c r="X33" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="2">
         <v>1010</v>
       </c>
-      <c r="N33" s="2">
+      <c r="AA33" s="2">
         <v>39</v>
       </c>
-      <c r="O33" s="2">
+      <c r="AB33" s="2">
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>31</v>
       </c>
@@ -2421,7 +3794,7 @@
       </c>
       <c r="G34" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H34" s="2">
         <f t="shared" si="7"/>
@@ -2440,20 +3813,59 @@
         <v>10</v>
       </c>
       <c r="L34" s="2">
+        <v>0</v>
+      </c>
+      <c r="M34" s="2">
+        <v>0</v>
+      </c>
+      <c r="N34" s="2">
+        <v>0</v>
+      </c>
+      <c r="O34" s="2">
+        <v>0</v>
+      </c>
+      <c r="P34" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="2">
+        <v>0</v>
+      </c>
+      <c r="R34" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M34" s="2">
+        <v>100</v>
+      </c>
+      <c r="S34" s="2">
+        <v>0</v>
+      </c>
+      <c r="T34" s="2">
+        <v>0</v>
+      </c>
+      <c r="U34" s="2">
+        <v>0</v>
+      </c>
+      <c r="V34" s="2">
+        <v>0</v>
+      </c>
+      <c r="W34" s="2">
+        <v>0</v>
+      </c>
+      <c r="X34" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="2">
         <v>1011</v>
       </c>
-      <c r="N34" s="2">
+      <c r="AA34" s="2">
         <v>40</v>
       </c>
-      <c r="O34" s="2">
+      <c r="AB34" s="2">
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>32</v>
       </c>
@@ -2479,7 +3891,7 @@
       </c>
       <c r="G35" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H35" s="2">
         <f t="shared" si="7"/>
@@ -2498,20 +3910,59 @@
         <v>10</v>
       </c>
       <c r="L35" s="2">
+        <v>0</v>
+      </c>
+      <c r="M35" s="2">
+        <v>0</v>
+      </c>
+      <c r="N35" s="2">
+        <v>0</v>
+      </c>
+      <c r="O35" s="2">
+        <v>0</v>
+      </c>
+      <c r="P35" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="2">
+        <v>0</v>
+      </c>
+      <c r="R35" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M35" s="2">
+        <v>100</v>
+      </c>
+      <c r="S35" s="2">
+        <v>0</v>
+      </c>
+      <c r="T35" s="2">
+        <v>0</v>
+      </c>
+      <c r="U35" s="2">
+        <v>0</v>
+      </c>
+      <c r="V35" s="2">
+        <v>0</v>
+      </c>
+      <c r="W35" s="2">
+        <v>0</v>
+      </c>
+      <c r="X35" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="2">
         <v>1012</v>
       </c>
-      <c r="N35" s="2">
+      <c r="AA35" s="2">
         <v>41</v>
       </c>
-      <c r="O35" s="2">
+      <c r="AB35" s="2">
         <v>32</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>33</v>
       </c>
@@ -2537,7 +3988,7 @@
       </c>
       <c r="G36" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H36" s="2">
         <f t="shared" si="7"/>
@@ -2556,20 +4007,59 @@
         <v>10</v>
       </c>
       <c r="L36" s="2">
+        <v>0</v>
+      </c>
+      <c r="M36" s="2">
+        <v>0</v>
+      </c>
+      <c r="N36" s="2">
+        <v>0</v>
+      </c>
+      <c r="O36" s="2">
+        <v>0</v>
+      </c>
+      <c r="P36" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="2">
+        <v>0</v>
+      </c>
+      <c r="R36" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M36" s="2">
+        <v>100</v>
+      </c>
+      <c r="S36" s="2">
+        <v>0</v>
+      </c>
+      <c r="T36" s="2">
+        <v>0</v>
+      </c>
+      <c r="U36" s="2">
+        <v>0</v>
+      </c>
+      <c r="V36" s="2">
+        <v>0</v>
+      </c>
+      <c r="W36" s="2">
+        <v>0</v>
+      </c>
+      <c r="X36" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="2">
         <v>1013</v>
       </c>
-      <c r="N36" s="2">
+      <c r="AA36" s="2">
         <v>42</v>
       </c>
-      <c r="O36" s="2">
+      <c r="AB36" s="2">
         <v>33</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>34</v>
       </c>
@@ -2595,7 +4085,7 @@
       </c>
       <c r="G37" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H37" s="2">
         <f t="shared" si="7"/>
@@ -2614,20 +4104,59 @@
         <v>10</v>
       </c>
       <c r="L37" s="2">
+        <v>0</v>
+      </c>
+      <c r="M37" s="2">
+        <v>0</v>
+      </c>
+      <c r="N37" s="2">
+        <v>0</v>
+      </c>
+      <c r="O37" s="2">
+        <v>0</v>
+      </c>
+      <c r="P37" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="2">
+        <v>0</v>
+      </c>
+      <c r="R37" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M37" s="2">
+        <v>100</v>
+      </c>
+      <c r="S37" s="2">
+        <v>0</v>
+      </c>
+      <c r="T37" s="2">
+        <v>0</v>
+      </c>
+      <c r="U37" s="2">
+        <v>0</v>
+      </c>
+      <c r="V37" s="2">
+        <v>0</v>
+      </c>
+      <c r="W37" s="2">
+        <v>0</v>
+      </c>
+      <c r="X37" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="2">
         <v>1014</v>
       </c>
-      <c r="N37" s="2">
+      <c r="AA37" s="2">
         <v>43</v>
       </c>
-      <c r="O37" s="2">
+      <c r="AB37" s="2">
         <v>34</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>35</v>
       </c>
@@ -2653,7 +4182,7 @@
       </c>
       <c r="G38" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H38" s="2">
         <f t="shared" si="7"/>
@@ -2672,20 +4201,59 @@
         <v>10</v>
       </c>
       <c r="L38" s="2">
+        <v>0</v>
+      </c>
+      <c r="M38" s="2">
+        <v>0</v>
+      </c>
+      <c r="N38" s="2">
+        <v>0</v>
+      </c>
+      <c r="O38" s="2">
+        <v>0</v>
+      </c>
+      <c r="P38" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="2">
+        <v>0</v>
+      </c>
+      <c r="R38" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M38" s="2">
+        <v>100</v>
+      </c>
+      <c r="S38" s="2">
+        <v>0</v>
+      </c>
+      <c r="T38" s="2">
+        <v>0</v>
+      </c>
+      <c r="U38" s="2">
+        <v>0</v>
+      </c>
+      <c r="V38" s="2">
+        <v>0</v>
+      </c>
+      <c r="W38" s="2">
+        <v>0</v>
+      </c>
+      <c r="X38" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="2">
         <v>1015</v>
       </c>
-      <c r="N38" s="2">
+      <c r="AA38" s="2">
         <v>44</v>
       </c>
-      <c r="O38" s="2">
+      <c r="AB38" s="2">
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>36</v>
       </c>
@@ -2711,7 +4279,7 @@
       </c>
       <c r="G39" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H39" s="2">
         <f t="shared" si="7"/>
@@ -2730,20 +4298,59 @@
         <v>10</v>
       </c>
       <c r="L39" s="2">
+        <v>0</v>
+      </c>
+      <c r="M39" s="2">
+        <v>0</v>
+      </c>
+      <c r="N39" s="2">
+        <v>0</v>
+      </c>
+      <c r="O39" s="2">
+        <v>0</v>
+      </c>
+      <c r="P39" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="2">
+        <v>0</v>
+      </c>
+      <c r="R39" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M39" s="2">
+        <v>100</v>
+      </c>
+      <c r="S39" s="2">
+        <v>0</v>
+      </c>
+      <c r="T39" s="2">
+        <v>0</v>
+      </c>
+      <c r="U39" s="2">
+        <v>0</v>
+      </c>
+      <c r="V39" s="2">
+        <v>0</v>
+      </c>
+      <c r="W39" s="2">
+        <v>0</v>
+      </c>
+      <c r="X39" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y39" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z39" s="2">
         <v>1016</v>
       </c>
-      <c r="N39" s="2">
+      <c r="AA39" s="2">
         <v>45</v>
       </c>
-      <c r="O39" s="2">
+      <c r="AB39" s="2">
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>37</v>
       </c>
@@ -2769,7 +4376,7 @@
       </c>
       <c r="G40" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H40" s="2">
         <f t="shared" si="7"/>
@@ -2788,20 +4395,59 @@
         <v>10</v>
       </c>
       <c r="L40" s="2">
+        <v>0</v>
+      </c>
+      <c r="M40" s="2">
+        <v>0</v>
+      </c>
+      <c r="N40" s="2">
+        <v>0</v>
+      </c>
+      <c r="O40" s="2">
+        <v>0</v>
+      </c>
+      <c r="P40" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="2">
+        <v>0</v>
+      </c>
+      <c r="R40" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M40" s="2">
+        <v>100</v>
+      </c>
+      <c r="S40" s="2">
+        <v>0</v>
+      </c>
+      <c r="T40" s="2">
+        <v>0</v>
+      </c>
+      <c r="U40" s="2">
+        <v>0</v>
+      </c>
+      <c r="V40" s="2">
+        <v>0</v>
+      </c>
+      <c r="W40" s="2">
+        <v>0</v>
+      </c>
+      <c r="X40" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y40" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z40" s="2">
         <v>1017</v>
       </c>
-      <c r="N40" s="2">
+      <c r="AA40" s="2">
         <v>46</v>
       </c>
-      <c r="O40" s="2">
+      <c r="AB40" s="2">
         <v>37</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>38</v>
       </c>
@@ -2827,7 +4473,7 @@
       </c>
       <c r="G41" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H41" s="2">
         <f t="shared" si="7"/>
@@ -2846,20 +4492,59 @@
         <v>10</v>
       </c>
       <c r="L41" s="2">
+        <v>0</v>
+      </c>
+      <c r="M41" s="2">
+        <v>0</v>
+      </c>
+      <c r="N41" s="2">
+        <v>0</v>
+      </c>
+      <c r="O41" s="2">
+        <v>0</v>
+      </c>
+      <c r="P41" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="2">
+        <v>0</v>
+      </c>
+      <c r="R41" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M41" s="2">
+        <v>100</v>
+      </c>
+      <c r="S41" s="2">
+        <v>0</v>
+      </c>
+      <c r="T41" s="2">
+        <v>0</v>
+      </c>
+      <c r="U41" s="2">
+        <v>0</v>
+      </c>
+      <c r="V41" s="2">
+        <v>0</v>
+      </c>
+      <c r="W41" s="2">
+        <v>0</v>
+      </c>
+      <c r="X41" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="2">
         <v>1018</v>
       </c>
-      <c r="N41" s="2">
+      <c r="AA41" s="2">
         <v>47</v>
       </c>
-      <c r="O41" s="2">
+      <c r="AB41" s="2">
         <v>38</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>39</v>
       </c>
@@ -2885,7 +4570,7 @@
       </c>
       <c r="G42" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H42" s="2">
         <f t="shared" si="7"/>
@@ -2904,20 +4589,59 @@
         <v>10</v>
       </c>
       <c r="L42" s="2">
+        <v>0</v>
+      </c>
+      <c r="M42" s="2">
+        <v>0</v>
+      </c>
+      <c r="N42" s="2">
+        <v>0</v>
+      </c>
+      <c r="O42" s="2">
+        <v>0</v>
+      </c>
+      <c r="P42" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="2">
+        <v>0</v>
+      </c>
+      <c r="R42" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M42" s="2">
+        <v>100</v>
+      </c>
+      <c r="S42" s="2">
+        <v>0</v>
+      </c>
+      <c r="T42" s="2">
+        <v>0</v>
+      </c>
+      <c r="U42" s="2">
+        <v>0</v>
+      </c>
+      <c r="V42" s="2">
+        <v>0</v>
+      </c>
+      <c r="W42" s="2">
+        <v>0</v>
+      </c>
+      <c r="X42" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="2">
         <v>1019</v>
       </c>
-      <c r="N42" s="2">
+      <c r="AA42" s="2">
         <v>48</v>
       </c>
-      <c r="O42" s="2">
+      <c r="AB42" s="2">
         <v>39</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>40</v>
       </c>
@@ -2943,7 +4667,7 @@
       </c>
       <c r="G43" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H43" s="2">
         <f t="shared" si="7"/>
@@ -2962,20 +4686,59 @@
         <v>10</v>
       </c>
       <c r="L43" s="2">
+        <v>0</v>
+      </c>
+      <c r="M43" s="2">
+        <v>0</v>
+      </c>
+      <c r="N43" s="2">
+        <v>0</v>
+      </c>
+      <c r="O43" s="2">
+        <v>0</v>
+      </c>
+      <c r="P43" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="2">
+        <v>0</v>
+      </c>
+      <c r="R43" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M43" s="2">
+        <v>100</v>
+      </c>
+      <c r="S43" s="2">
+        <v>0</v>
+      </c>
+      <c r="T43" s="2">
+        <v>0</v>
+      </c>
+      <c r="U43" s="2">
+        <v>0</v>
+      </c>
+      <c r="V43" s="2">
+        <v>0</v>
+      </c>
+      <c r="W43" s="2">
+        <v>0</v>
+      </c>
+      <c r="X43" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="2">
         <v>1020</v>
       </c>
-      <c r="N43" s="2">
+      <c r="AA43" s="2">
         <v>49</v>
       </c>
-      <c r="O43" s="2">
+      <c r="AB43" s="2">
         <v>40</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>41</v>
       </c>
@@ -3001,7 +4764,7 @@
       </c>
       <c r="G44" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H44" s="2">
         <f t="shared" si="7"/>
@@ -3020,20 +4783,59 @@
         <v>10</v>
       </c>
       <c r="L44" s="2">
+        <v>0</v>
+      </c>
+      <c r="M44" s="2">
+        <v>0</v>
+      </c>
+      <c r="N44" s="2">
+        <v>0</v>
+      </c>
+      <c r="O44" s="2">
+        <v>0</v>
+      </c>
+      <c r="P44" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="2">
+        <v>0</v>
+      </c>
+      <c r="R44" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M44" s="2">
+        <v>100</v>
+      </c>
+      <c r="S44" s="2">
+        <v>0</v>
+      </c>
+      <c r="T44" s="2">
+        <v>0</v>
+      </c>
+      <c r="U44" s="2">
+        <v>0</v>
+      </c>
+      <c r="V44" s="2">
+        <v>0</v>
+      </c>
+      <c r="W44" s="2">
+        <v>0</v>
+      </c>
+      <c r="X44" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="2">
         <v>1001</v>
       </c>
-      <c r="N44" s="2">
+      <c r="AA44" s="2">
         <v>50</v>
       </c>
-      <c r="O44" s="2">
+      <c r="AB44" s="2">
         <v>41</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>42</v>
       </c>
@@ -3059,7 +4861,7 @@
       </c>
       <c r="G45" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H45" s="2">
         <f t="shared" si="7"/>
@@ -3078,20 +4880,59 @@
         <v>10</v>
       </c>
       <c r="L45" s="2">
+        <v>0</v>
+      </c>
+      <c r="M45" s="2">
+        <v>0</v>
+      </c>
+      <c r="N45" s="2">
+        <v>0</v>
+      </c>
+      <c r="O45" s="2">
+        <v>0</v>
+      </c>
+      <c r="P45" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="2">
+        <v>0</v>
+      </c>
+      <c r="R45" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M45" s="2">
+        <v>100</v>
+      </c>
+      <c r="S45" s="2">
+        <v>0</v>
+      </c>
+      <c r="T45" s="2">
+        <v>0</v>
+      </c>
+      <c r="U45" s="2">
+        <v>0</v>
+      </c>
+      <c r="V45" s="2">
+        <v>0</v>
+      </c>
+      <c r="W45" s="2">
+        <v>0</v>
+      </c>
+      <c r="X45" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="2">
         <v>1002</v>
       </c>
-      <c r="N45" s="2">
+      <c r="AA45" s="2">
         <v>51</v>
       </c>
-      <c r="O45" s="2">
+      <c r="AB45" s="2">
         <v>42</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>43</v>
       </c>
@@ -3117,7 +4958,7 @@
       </c>
       <c r="G46" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H46" s="2">
         <f t="shared" si="7"/>
@@ -3136,20 +4977,59 @@
         <v>10</v>
       </c>
       <c r="L46" s="2">
+        <v>0</v>
+      </c>
+      <c r="M46" s="2">
+        <v>0</v>
+      </c>
+      <c r="N46" s="2">
+        <v>0</v>
+      </c>
+      <c r="O46" s="2">
+        <v>0</v>
+      </c>
+      <c r="P46" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="2">
+        <v>0</v>
+      </c>
+      <c r="R46" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M46" s="2">
+        <v>100</v>
+      </c>
+      <c r="S46" s="2">
+        <v>0</v>
+      </c>
+      <c r="T46" s="2">
+        <v>0</v>
+      </c>
+      <c r="U46" s="2">
+        <v>0</v>
+      </c>
+      <c r="V46" s="2">
+        <v>0</v>
+      </c>
+      <c r="W46" s="2">
+        <v>0</v>
+      </c>
+      <c r="X46" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y46" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z46" s="2">
         <v>1003</v>
       </c>
-      <c r="N46" s="2">
+      <c r="AA46" s="2">
         <v>52</v>
       </c>
-      <c r="O46" s="2">
+      <c r="AB46" s="2">
         <v>43</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>44</v>
       </c>
@@ -3175,7 +5055,7 @@
       </c>
       <c r="G47" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H47" s="2">
         <f t="shared" si="7"/>
@@ -3194,20 +5074,59 @@
         <v>10</v>
       </c>
       <c r="L47" s="2">
+        <v>0</v>
+      </c>
+      <c r="M47" s="2">
+        <v>0</v>
+      </c>
+      <c r="N47" s="2">
+        <v>0</v>
+      </c>
+      <c r="O47" s="2">
+        <v>0</v>
+      </c>
+      <c r="P47" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="2">
+        <v>0</v>
+      </c>
+      <c r="R47" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M47" s="2">
+        <v>100</v>
+      </c>
+      <c r="S47" s="2">
+        <v>0</v>
+      </c>
+      <c r="T47" s="2">
+        <v>0</v>
+      </c>
+      <c r="U47" s="2">
+        <v>0</v>
+      </c>
+      <c r="V47" s="2">
+        <v>0</v>
+      </c>
+      <c r="W47" s="2">
+        <v>0</v>
+      </c>
+      <c r="X47" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="2">
         <v>1004</v>
       </c>
-      <c r="N47" s="2">
+      <c r="AA47" s="2">
         <v>53</v>
       </c>
-      <c r="O47" s="2">
+      <c r="AB47" s="2">
         <v>44</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <v>45</v>
       </c>
@@ -3233,7 +5152,7 @@
       </c>
       <c r="G48" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H48" s="2">
         <f t="shared" si="7"/>
@@ -3252,20 +5171,59 @@
         <v>10</v>
       </c>
       <c r="L48" s="2">
+        <v>0</v>
+      </c>
+      <c r="M48" s="2">
+        <v>0</v>
+      </c>
+      <c r="N48" s="2">
+        <v>0</v>
+      </c>
+      <c r="O48" s="2">
+        <v>0</v>
+      </c>
+      <c r="P48" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="2">
+        <v>0</v>
+      </c>
+      <c r="R48" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M48" s="2">
+        <v>100</v>
+      </c>
+      <c r="S48" s="2">
+        <v>0</v>
+      </c>
+      <c r="T48" s="2">
+        <v>0</v>
+      </c>
+      <c r="U48" s="2">
+        <v>0</v>
+      </c>
+      <c r="V48" s="2">
+        <v>0</v>
+      </c>
+      <c r="W48" s="2">
+        <v>0</v>
+      </c>
+      <c r="X48" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y48" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z48" s="2">
         <v>1005</v>
       </c>
-      <c r="N48" s="2">
+      <c r="AA48" s="2">
         <v>54</v>
       </c>
-      <c r="O48" s="2">
+      <c r="AB48" s="2">
         <v>45</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <v>46</v>
       </c>
@@ -3291,7 +5249,7 @@
       </c>
       <c r="G49" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H49" s="2">
         <f t="shared" si="7"/>
@@ -3310,20 +5268,59 @@
         <v>10</v>
       </c>
       <c r="L49" s="2">
+        <v>0</v>
+      </c>
+      <c r="M49" s="2">
+        <v>0</v>
+      </c>
+      <c r="N49" s="2">
+        <v>0</v>
+      </c>
+      <c r="O49" s="2">
+        <v>0</v>
+      </c>
+      <c r="P49" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="2">
+        <v>0</v>
+      </c>
+      <c r="R49" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M49" s="2">
+        <v>100</v>
+      </c>
+      <c r="S49" s="2">
+        <v>0</v>
+      </c>
+      <c r="T49" s="2">
+        <v>0</v>
+      </c>
+      <c r="U49" s="2">
+        <v>0</v>
+      </c>
+      <c r="V49" s="2">
+        <v>0</v>
+      </c>
+      <c r="W49" s="2">
+        <v>0</v>
+      </c>
+      <c r="X49" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y49" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z49" s="2">
         <v>1006</v>
       </c>
-      <c r="N49" s="2">
+      <c r="AA49" s="2">
         <v>55</v>
       </c>
-      <c r="O49" s="2">
+      <c r="AB49" s="2">
         <v>46</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
         <v>47</v>
       </c>
@@ -3349,7 +5346,7 @@
       </c>
       <c r="G50" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H50" s="2">
         <f t="shared" si="7"/>
@@ -3368,20 +5365,59 @@
         <v>10</v>
       </c>
       <c r="L50" s="2">
+        <v>0</v>
+      </c>
+      <c r="M50" s="2">
+        <v>0</v>
+      </c>
+      <c r="N50" s="2">
+        <v>0</v>
+      </c>
+      <c r="O50" s="2">
+        <v>0</v>
+      </c>
+      <c r="P50" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="2">
+        <v>0</v>
+      </c>
+      <c r="R50" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M50" s="2">
+        <v>100</v>
+      </c>
+      <c r="S50" s="2">
+        <v>0</v>
+      </c>
+      <c r="T50" s="2">
+        <v>0</v>
+      </c>
+      <c r="U50" s="2">
+        <v>0</v>
+      </c>
+      <c r="V50" s="2">
+        <v>0</v>
+      </c>
+      <c r="W50" s="2">
+        <v>0</v>
+      </c>
+      <c r="X50" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="2">
         <v>1007</v>
       </c>
-      <c r="N50" s="2">
+      <c r="AA50" s="2">
         <v>56</v>
       </c>
-      <c r="O50" s="2">
+      <c r="AB50" s="2">
         <v>47</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
         <v>48</v>
       </c>
@@ -3407,7 +5443,7 @@
       </c>
       <c r="G51" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H51" s="2">
         <f t="shared" si="7"/>
@@ -3426,20 +5462,59 @@
         <v>10</v>
       </c>
       <c r="L51" s="2">
+        <v>0</v>
+      </c>
+      <c r="M51" s="2">
+        <v>0</v>
+      </c>
+      <c r="N51" s="2">
+        <v>0</v>
+      </c>
+      <c r="O51" s="2">
+        <v>0</v>
+      </c>
+      <c r="P51" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="2">
+        <v>0</v>
+      </c>
+      <c r="R51" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M51" s="2">
+        <v>100</v>
+      </c>
+      <c r="S51" s="2">
+        <v>0</v>
+      </c>
+      <c r="T51" s="2">
+        <v>0</v>
+      </c>
+      <c r="U51" s="2">
+        <v>0</v>
+      </c>
+      <c r="V51" s="2">
+        <v>0</v>
+      </c>
+      <c r="W51" s="2">
+        <v>0</v>
+      </c>
+      <c r="X51" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="2">
         <v>1008</v>
       </c>
-      <c r="N51" s="2">
+      <c r="AA51" s="2">
         <v>57</v>
       </c>
-      <c r="O51" s="2">
+      <c r="AB51" s="2">
         <v>48</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
         <v>49</v>
       </c>
@@ -3465,7 +5540,7 @@
       </c>
       <c r="G52" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H52" s="2">
         <f t="shared" si="7"/>
@@ -3484,20 +5559,59 @@
         <v>10</v>
       </c>
       <c r="L52" s="2">
+        <v>0</v>
+      </c>
+      <c r="M52" s="2">
+        <v>0</v>
+      </c>
+      <c r="N52" s="2">
+        <v>0</v>
+      </c>
+      <c r="O52" s="2">
+        <v>0</v>
+      </c>
+      <c r="P52" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="2">
+        <v>0</v>
+      </c>
+      <c r="R52" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M52" s="2">
+        <v>100</v>
+      </c>
+      <c r="S52" s="2">
+        <v>0</v>
+      </c>
+      <c r="T52" s="2">
+        <v>0</v>
+      </c>
+      <c r="U52" s="2">
+        <v>0</v>
+      </c>
+      <c r="V52" s="2">
+        <v>0</v>
+      </c>
+      <c r="W52" s="2">
+        <v>0</v>
+      </c>
+      <c r="X52" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="2">
         <v>1009</v>
       </c>
-      <c r="N52" s="2">
+      <c r="AA52" s="2">
         <v>58</v>
       </c>
-      <c r="O52" s="2">
+      <c r="AB52" s="2">
         <v>49</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
         <v>50</v>
       </c>
@@ -3523,7 +5637,7 @@
       </c>
       <c r="G53" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H53" s="2">
         <f t="shared" si="7"/>
@@ -3542,20 +5656,59 @@
         <v>10</v>
       </c>
       <c r="L53" s="2">
+        <v>0</v>
+      </c>
+      <c r="M53" s="2">
+        <v>0</v>
+      </c>
+      <c r="N53" s="2">
+        <v>0</v>
+      </c>
+      <c r="O53" s="2">
+        <v>0</v>
+      </c>
+      <c r="P53" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="2">
+        <v>0</v>
+      </c>
+      <c r="R53" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M53" s="2">
+        <v>100</v>
+      </c>
+      <c r="S53" s="2">
+        <v>0</v>
+      </c>
+      <c r="T53" s="2">
+        <v>0</v>
+      </c>
+      <c r="U53" s="2">
+        <v>0</v>
+      </c>
+      <c r="V53" s="2">
+        <v>0</v>
+      </c>
+      <c r="W53" s="2">
+        <v>0</v>
+      </c>
+      <c r="X53" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="2">
         <v>1010</v>
       </c>
-      <c r="N53" s="2">
+      <c r="AA53" s="2">
         <v>59</v>
       </c>
-      <c r="O53" s="2">
+      <c r="AB53" s="2">
         <v>50</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
         <v>51</v>
       </c>
@@ -3581,7 +5734,7 @@
       </c>
       <c r="G54" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H54" s="2">
         <f t="shared" si="7"/>
@@ -3600,20 +5753,59 @@
         <v>10</v>
       </c>
       <c r="L54" s="2">
+        <v>0</v>
+      </c>
+      <c r="M54" s="2">
+        <v>0</v>
+      </c>
+      <c r="N54" s="2">
+        <v>0</v>
+      </c>
+      <c r="O54" s="2">
+        <v>0</v>
+      </c>
+      <c r="P54" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="2">
+        <v>0</v>
+      </c>
+      <c r="R54" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M54" s="2">
+        <v>100</v>
+      </c>
+      <c r="S54" s="2">
+        <v>0</v>
+      </c>
+      <c r="T54" s="2">
+        <v>0</v>
+      </c>
+      <c r="U54" s="2">
+        <v>0</v>
+      </c>
+      <c r="V54" s="2">
+        <v>0</v>
+      </c>
+      <c r="W54" s="2">
+        <v>0</v>
+      </c>
+      <c r="X54" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y54" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z54" s="2">
         <v>1011</v>
       </c>
-      <c r="N54" s="2">
+      <c r="AA54" s="2">
         <v>60</v>
       </c>
-      <c r="O54" s="2">
+      <c r="AB54" s="2">
         <v>51</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
         <v>52</v>
       </c>
@@ -3639,7 +5831,7 @@
       </c>
       <c r="G55" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H55" s="2">
         <f t="shared" si="7"/>
@@ -3658,20 +5850,59 @@
         <v>10</v>
       </c>
       <c r="L55" s="2">
+        <v>0</v>
+      </c>
+      <c r="M55" s="2">
+        <v>0</v>
+      </c>
+      <c r="N55" s="2">
+        <v>0</v>
+      </c>
+      <c r="O55" s="2">
+        <v>0</v>
+      </c>
+      <c r="P55" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="2">
+        <v>0</v>
+      </c>
+      <c r="R55" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M55" s="2">
+        <v>100</v>
+      </c>
+      <c r="S55" s="2">
+        <v>0</v>
+      </c>
+      <c r="T55" s="2">
+        <v>0</v>
+      </c>
+      <c r="U55" s="2">
+        <v>0</v>
+      </c>
+      <c r="V55" s="2">
+        <v>0</v>
+      </c>
+      <c r="W55" s="2">
+        <v>0</v>
+      </c>
+      <c r="X55" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y55" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z55" s="2">
         <v>1012</v>
       </c>
-      <c r="N55" s="2">
+      <c r="AA55" s="2">
         <v>61</v>
       </c>
-      <c r="O55" s="2">
+      <c r="AB55" s="2">
         <v>52</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
         <v>53</v>
       </c>
@@ -3697,7 +5928,7 @@
       </c>
       <c r="G56" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H56" s="2">
         <f t="shared" si="7"/>
@@ -3716,20 +5947,59 @@
         <v>10</v>
       </c>
       <c r="L56" s="2">
+        <v>0</v>
+      </c>
+      <c r="M56" s="2">
+        <v>0</v>
+      </c>
+      <c r="N56" s="2">
+        <v>0</v>
+      </c>
+      <c r="O56" s="2">
+        <v>0</v>
+      </c>
+      <c r="P56" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="2">
+        <v>0</v>
+      </c>
+      <c r="R56" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M56" s="2">
+        <v>100</v>
+      </c>
+      <c r="S56" s="2">
+        <v>0</v>
+      </c>
+      <c r="T56" s="2">
+        <v>0</v>
+      </c>
+      <c r="U56" s="2">
+        <v>0</v>
+      </c>
+      <c r="V56" s="2">
+        <v>0</v>
+      </c>
+      <c r="W56" s="2">
+        <v>0</v>
+      </c>
+      <c r="X56" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y56" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z56" s="2">
         <v>1013</v>
       </c>
-      <c r="N56" s="2">
+      <c r="AA56" s="2">
         <v>62</v>
       </c>
-      <c r="O56" s="2">
+      <c r="AB56" s="2">
         <v>53</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
         <v>54</v>
       </c>
@@ -3755,7 +6025,7 @@
       </c>
       <c r="G57" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H57" s="2">
         <f t="shared" si="7"/>
@@ -3774,20 +6044,59 @@
         <v>10</v>
       </c>
       <c r="L57" s="2">
+        <v>0</v>
+      </c>
+      <c r="M57" s="2">
+        <v>0</v>
+      </c>
+      <c r="N57" s="2">
+        <v>0</v>
+      </c>
+      <c r="O57" s="2">
+        <v>0</v>
+      </c>
+      <c r="P57" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="2">
+        <v>0</v>
+      </c>
+      <c r="R57" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M57" s="2">
+        <v>100</v>
+      </c>
+      <c r="S57" s="2">
+        <v>0</v>
+      </c>
+      <c r="T57" s="2">
+        <v>0</v>
+      </c>
+      <c r="U57" s="2">
+        <v>0</v>
+      </c>
+      <c r="V57" s="2">
+        <v>0</v>
+      </c>
+      <c r="W57" s="2">
+        <v>0</v>
+      </c>
+      <c r="X57" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y57" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="2">
         <v>1014</v>
       </c>
-      <c r="N57" s="2">
+      <c r="AA57" s="2">
         <v>63</v>
       </c>
-      <c r="O57" s="2">
+      <c r="AB57" s="2">
         <v>54</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
         <v>55</v>
       </c>
@@ -3813,7 +6122,7 @@
       </c>
       <c r="G58" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H58" s="2">
         <f t="shared" si="7"/>
@@ -3832,20 +6141,59 @@
         <v>10</v>
       </c>
       <c r="L58" s="2">
+        <v>0</v>
+      </c>
+      <c r="M58" s="2">
+        <v>0</v>
+      </c>
+      <c r="N58" s="2">
+        <v>0</v>
+      </c>
+      <c r="O58" s="2">
+        <v>0</v>
+      </c>
+      <c r="P58" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="2">
+        <v>0</v>
+      </c>
+      <c r="R58" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M58" s="2">
+        <v>100</v>
+      </c>
+      <c r="S58" s="2">
+        <v>0</v>
+      </c>
+      <c r="T58" s="2">
+        <v>0</v>
+      </c>
+      <c r="U58" s="2">
+        <v>0</v>
+      </c>
+      <c r="V58" s="2">
+        <v>0</v>
+      </c>
+      <c r="W58" s="2">
+        <v>0</v>
+      </c>
+      <c r="X58" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="2">
         <v>1015</v>
       </c>
-      <c r="N58" s="2">
+      <c r="AA58" s="2">
         <v>64</v>
       </c>
-      <c r="O58" s="2">
+      <c r="AB58" s="2">
         <v>55</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
         <v>56</v>
       </c>
@@ -3871,7 +6219,7 @@
       </c>
       <c r="G59" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H59" s="2">
         <f t="shared" si="7"/>
@@ -3890,20 +6238,59 @@
         <v>10</v>
       </c>
       <c r="L59" s="2">
+        <v>0</v>
+      </c>
+      <c r="M59" s="2">
+        <v>0</v>
+      </c>
+      <c r="N59" s="2">
+        <v>0</v>
+      </c>
+      <c r="O59" s="2">
+        <v>0</v>
+      </c>
+      <c r="P59" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="2">
+        <v>0</v>
+      </c>
+      <c r="R59" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M59" s="2">
+        <v>100</v>
+      </c>
+      <c r="S59" s="2">
+        <v>0</v>
+      </c>
+      <c r="T59" s="2">
+        <v>0</v>
+      </c>
+      <c r="U59" s="2">
+        <v>0</v>
+      </c>
+      <c r="V59" s="2">
+        <v>0</v>
+      </c>
+      <c r="W59" s="2">
+        <v>0</v>
+      </c>
+      <c r="X59" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y59" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="2">
         <v>1016</v>
       </c>
-      <c r="N59" s="2">
+      <c r="AA59" s="2">
         <v>65</v>
       </c>
-      <c r="O59" s="2">
+      <c r="AB59" s="2">
         <v>56</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
         <v>57</v>
       </c>
@@ -3929,7 +6316,7 @@
       </c>
       <c r="G60" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H60" s="2">
         <f t="shared" si="7"/>
@@ -3948,20 +6335,59 @@
         <v>10</v>
       </c>
       <c r="L60" s="2">
+        <v>0</v>
+      </c>
+      <c r="M60" s="2">
+        <v>0</v>
+      </c>
+      <c r="N60" s="2">
+        <v>0</v>
+      </c>
+      <c r="O60" s="2">
+        <v>0</v>
+      </c>
+      <c r="P60" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="2">
+        <v>0</v>
+      </c>
+      <c r="R60" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M60" s="2">
+        <v>100</v>
+      </c>
+      <c r="S60" s="2">
+        <v>0</v>
+      </c>
+      <c r="T60" s="2">
+        <v>0</v>
+      </c>
+      <c r="U60" s="2">
+        <v>0</v>
+      </c>
+      <c r="V60" s="2">
+        <v>0</v>
+      </c>
+      <c r="W60" s="2">
+        <v>0</v>
+      </c>
+      <c r="X60" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y60" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z60" s="2">
         <v>1017</v>
       </c>
-      <c r="N60" s="2">
+      <c r="AA60" s="2">
         <v>66</v>
       </c>
-      <c r="O60" s="2">
+      <c r="AB60" s="2">
         <v>57</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
         <v>58</v>
       </c>
@@ -3987,7 +6413,7 @@
       </c>
       <c r="G61" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H61" s="2">
         <f t="shared" si="7"/>
@@ -4006,20 +6432,59 @@
         <v>10</v>
       </c>
       <c r="L61" s="2">
+        <v>0</v>
+      </c>
+      <c r="M61" s="2">
+        <v>0</v>
+      </c>
+      <c r="N61" s="2">
+        <v>0</v>
+      </c>
+      <c r="O61" s="2">
+        <v>0</v>
+      </c>
+      <c r="P61" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="2">
+        <v>0</v>
+      </c>
+      <c r="R61" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M61" s="2">
+        <v>100</v>
+      </c>
+      <c r="S61" s="2">
+        <v>0</v>
+      </c>
+      <c r="T61" s="2">
+        <v>0</v>
+      </c>
+      <c r="U61" s="2">
+        <v>0</v>
+      </c>
+      <c r="V61" s="2">
+        <v>0</v>
+      </c>
+      <c r="W61" s="2">
+        <v>0</v>
+      </c>
+      <c r="X61" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="2">
         <v>1018</v>
       </c>
-      <c r="N61" s="2">
+      <c r="AA61" s="2">
         <v>67</v>
       </c>
-      <c r="O61" s="2">
+      <c r="AB61" s="2">
         <v>58</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
         <v>59</v>
       </c>
@@ -4045,7 +6510,7 @@
       </c>
       <c r="G62" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H62" s="2">
         <f t="shared" si="7"/>
@@ -4064,20 +6529,59 @@
         <v>10</v>
       </c>
       <c r="L62" s="2">
+        <v>0</v>
+      </c>
+      <c r="M62" s="2">
+        <v>0</v>
+      </c>
+      <c r="N62" s="2">
+        <v>0</v>
+      </c>
+      <c r="O62" s="2">
+        <v>0</v>
+      </c>
+      <c r="P62" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="2">
+        <v>0</v>
+      </c>
+      <c r="R62" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M62" s="2">
+        <v>100</v>
+      </c>
+      <c r="S62" s="2">
+        <v>0</v>
+      </c>
+      <c r="T62" s="2">
+        <v>0</v>
+      </c>
+      <c r="U62" s="2">
+        <v>0</v>
+      </c>
+      <c r="V62" s="2">
+        <v>0</v>
+      </c>
+      <c r="W62" s="2">
+        <v>0</v>
+      </c>
+      <c r="X62" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="2">
         <v>1019</v>
       </c>
-      <c r="N62" s="2">
+      <c r="AA62" s="2">
         <v>68</v>
       </c>
-      <c r="O62" s="2">
+      <c r="AB62" s="2">
         <v>59</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
         <v>60</v>
       </c>
@@ -4103,7 +6607,7 @@
       </c>
       <c r="G63" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H63" s="2">
         <f t="shared" si="7"/>
@@ -4122,20 +6626,59 @@
         <v>10</v>
       </c>
       <c r="L63" s="2">
+        <v>0</v>
+      </c>
+      <c r="M63" s="2">
+        <v>0</v>
+      </c>
+      <c r="N63" s="2">
+        <v>0</v>
+      </c>
+      <c r="O63" s="2">
+        <v>0</v>
+      </c>
+      <c r="P63" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="2">
+        <v>0</v>
+      </c>
+      <c r="R63" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M63" s="2">
+        <v>100</v>
+      </c>
+      <c r="S63" s="2">
+        <v>0</v>
+      </c>
+      <c r="T63" s="2">
+        <v>0</v>
+      </c>
+      <c r="U63" s="2">
+        <v>0</v>
+      </c>
+      <c r="V63" s="2">
+        <v>0</v>
+      </c>
+      <c r="W63" s="2">
+        <v>0</v>
+      </c>
+      <c r="X63" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="2">
         <v>1020</v>
       </c>
-      <c r="N63" s="2">
+      <c r="AA63" s="2">
         <v>69</v>
       </c>
-      <c r="O63" s="2">
+      <c r="AB63" s="2">
         <v>60</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
         <v>61</v>
       </c>
@@ -4161,7 +6704,7 @@
       </c>
       <c r="G64" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H64" s="2">
         <f t="shared" si="7"/>
@@ -4180,20 +6723,59 @@
         <v>10</v>
       </c>
       <c r="L64" s="2">
+        <v>0</v>
+      </c>
+      <c r="M64" s="2">
+        <v>0</v>
+      </c>
+      <c r="N64" s="2">
+        <v>0</v>
+      </c>
+      <c r="O64" s="2">
+        <v>0</v>
+      </c>
+      <c r="P64" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="2">
+        <v>0</v>
+      </c>
+      <c r="R64" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M64" s="2">
+        <v>100</v>
+      </c>
+      <c r="S64" s="2">
+        <v>0</v>
+      </c>
+      <c r="T64" s="2">
+        <v>0</v>
+      </c>
+      <c r="U64" s="2">
+        <v>0</v>
+      </c>
+      <c r="V64" s="2">
+        <v>0</v>
+      </c>
+      <c r="W64" s="2">
+        <v>0</v>
+      </c>
+      <c r="X64" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="2">
         <v>1001</v>
       </c>
-      <c r="N64" s="2">
+      <c r="AA64" s="2">
         <v>70</v>
       </c>
-      <c r="O64" s="2">
+      <c r="AB64" s="2">
         <v>61</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
         <v>62</v>
       </c>
@@ -4219,7 +6801,7 @@
       </c>
       <c r="G65" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H65" s="2">
         <f t="shared" si="7"/>
@@ -4238,20 +6820,59 @@
         <v>10</v>
       </c>
       <c r="L65" s="2">
+        <v>0</v>
+      </c>
+      <c r="M65" s="2">
+        <v>0</v>
+      </c>
+      <c r="N65" s="2">
+        <v>0</v>
+      </c>
+      <c r="O65" s="2">
+        <v>0</v>
+      </c>
+      <c r="P65" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="2">
+        <v>0</v>
+      </c>
+      <c r="R65" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M65" s="2">
+        <v>100</v>
+      </c>
+      <c r="S65" s="2">
+        <v>0</v>
+      </c>
+      <c r="T65" s="2">
+        <v>0</v>
+      </c>
+      <c r="U65" s="2">
+        <v>0</v>
+      </c>
+      <c r="V65" s="2">
+        <v>0</v>
+      </c>
+      <c r="W65" s="2">
+        <v>0</v>
+      </c>
+      <c r="X65" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="2">
         <v>1002</v>
       </c>
-      <c r="N65" s="2">
+      <c r="AA65" s="2">
         <v>71</v>
       </c>
-      <c r="O65" s="2">
+      <c r="AB65" s="2">
         <v>62</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
         <v>63</v>
       </c>
@@ -4277,7 +6898,7 @@
       </c>
       <c r="G66" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H66" s="2">
         <f t="shared" si="7"/>
@@ -4296,20 +6917,59 @@
         <v>10</v>
       </c>
       <c r="L66" s="2">
+        <v>0</v>
+      </c>
+      <c r="M66" s="2">
+        <v>0</v>
+      </c>
+      <c r="N66" s="2">
+        <v>0</v>
+      </c>
+      <c r="O66" s="2">
+        <v>0</v>
+      </c>
+      <c r="P66" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="2">
+        <v>0</v>
+      </c>
+      <c r="R66" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M66" s="2">
+        <v>100</v>
+      </c>
+      <c r="S66" s="2">
+        <v>0</v>
+      </c>
+      <c r="T66" s="2">
+        <v>0</v>
+      </c>
+      <c r="U66" s="2">
+        <v>0</v>
+      </c>
+      <c r="V66" s="2">
+        <v>0</v>
+      </c>
+      <c r="W66" s="2">
+        <v>0</v>
+      </c>
+      <c r="X66" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y66" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z66" s="2">
         <v>1003</v>
       </c>
-      <c r="N66" s="2">
+      <c r="AA66" s="2">
         <v>72</v>
       </c>
-      <c r="O66" s="2">
+      <c r="AB66" s="2">
         <v>63</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
         <v>64</v>
       </c>
@@ -4335,7 +6995,7 @@
       </c>
       <c r="G67" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H67" s="2">
         <f t="shared" si="7"/>
@@ -4354,20 +7014,59 @@
         <v>10</v>
       </c>
       <c r="L67" s="2">
+        <v>0</v>
+      </c>
+      <c r="M67" s="2">
+        <v>0</v>
+      </c>
+      <c r="N67" s="2">
+        <v>0</v>
+      </c>
+      <c r="O67" s="2">
+        <v>0</v>
+      </c>
+      <c r="P67" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="2">
+        <v>0</v>
+      </c>
+      <c r="R67" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M67" s="2">
+        <v>100</v>
+      </c>
+      <c r="S67" s="2">
+        <v>0</v>
+      </c>
+      <c r="T67" s="2">
+        <v>0</v>
+      </c>
+      <c r="U67" s="2">
+        <v>0</v>
+      </c>
+      <c r="V67" s="2">
+        <v>0</v>
+      </c>
+      <c r="W67" s="2">
+        <v>0</v>
+      </c>
+      <c r="X67" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y67" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z67" s="2">
         <v>1004</v>
       </c>
-      <c r="N67" s="2">
+      <c r="AA67" s="2">
         <v>73</v>
       </c>
-      <c r="O67" s="2">
+      <c r="AB67" s="2">
         <v>64</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
         <v>65</v>
       </c>
@@ -4393,7 +7092,7 @@
       </c>
       <c r="G68" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H68" s="2">
         <f t="shared" si="7"/>
@@ -4412,20 +7111,59 @@
         <v>10</v>
       </c>
       <c r="L68" s="2">
+        <v>0</v>
+      </c>
+      <c r="M68" s="2">
+        <v>0</v>
+      </c>
+      <c r="N68" s="2">
+        <v>0</v>
+      </c>
+      <c r="O68" s="2">
+        <v>0</v>
+      </c>
+      <c r="P68" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="2">
+        <v>0</v>
+      </c>
+      <c r="R68" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M68" s="2">
+        <v>100</v>
+      </c>
+      <c r="S68" s="2">
+        <v>0</v>
+      </c>
+      <c r="T68" s="2">
+        <v>0</v>
+      </c>
+      <c r="U68" s="2">
+        <v>0</v>
+      </c>
+      <c r="V68" s="2">
+        <v>0</v>
+      </c>
+      <c r="W68" s="2">
+        <v>0</v>
+      </c>
+      <c r="X68" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="2">
         <v>1005</v>
       </c>
-      <c r="N68" s="2">
+      <c r="AA68" s="2">
         <v>74</v>
       </c>
-      <c r="O68" s="2">
+      <c r="AB68" s="2">
         <v>65</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
         <v>66</v>
       </c>
@@ -4451,7 +7189,7 @@
       </c>
       <c r="G69" s="2">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H69" s="2">
         <f t="shared" si="7"/>
@@ -4470,20 +7208,59 @@
         <v>10</v>
       </c>
       <c r="L69" s="2">
+        <v>0</v>
+      </c>
+      <c r="M69" s="2">
+        <v>0</v>
+      </c>
+      <c r="N69" s="2">
+        <v>0</v>
+      </c>
+      <c r="O69" s="2">
+        <v>0</v>
+      </c>
+      <c r="P69" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="2">
+        <v>0</v>
+      </c>
+      <c r="R69" s="2">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="M69" s="2">
+        <v>100</v>
+      </c>
+      <c r="S69" s="2">
+        <v>0</v>
+      </c>
+      <c r="T69" s="2">
+        <v>0</v>
+      </c>
+      <c r="U69" s="2">
+        <v>0</v>
+      </c>
+      <c r="V69" s="2">
+        <v>0</v>
+      </c>
+      <c r="W69" s="2">
+        <v>0</v>
+      </c>
+      <c r="X69" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="2">
         <v>1006</v>
       </c>
-      <c r="N69" s="2">
+      <c r="AA69" s="2">
         <v>75</v>
       </c>
-      <c r="O69" s="2">
+      <c r="AB69" s="2">
         <v>66</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
         <v>67</v>
       </c>
@@ -4509,7 +7286,7 @@
       </c>
       <c r="G70" s="2">
         <f t="shared" ref="G70:G103" si="17">G69</f>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H70" s="2">
         <f t="shared" ref="H70:H103" si="18">H69</f>
@@ -4528,20 +7305,59 @@
         <v>10</v>
       </c>
       <c r="L70" s="2">
-        <f t="shared" ref="L70:L103" si="22">L69</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M70" s="2">
+        <v>0</v>
+      </c>
+      <c r="N70" s="2">
+        <v>0</v>
+      </c>
+      <c r="O70" s="2">
+        <v>0</v>
+      </c>
+      <c r="P70" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="2">
+        <v>0</v>
+      </c>
+      <c r="R70" s="2">
+        <f t="shared" ref="R70:R103" si="22">R69</f>
+        <v>100</v>
+      </c>
+      <c r="S70" s="2">
+        <v>0</v>
+      </c>
+      <c r="T70" s="2">
+        <v>0</v>
+      </c>
+      <c r="U70" s="2">
+        <v>0</v>
+      </c>
+      <c r="V70" s="2">
+        <v>0</v>
+      </c>
+      <c r="W70" s="2">
+        <v>0</v>
+      </c>
+      <c r="X70" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="2">
         <v>1007</v>
       </c>
-      <c r="N70" s="2">
+      <c r="AA70" s="2">
         <v>76</v>
       </c>
-      <c r="O70" s="2">
+      <c r="AB70" s="2">
         <v>67</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
         <v>68</v>
       </c>
@@ -4567,7 +7383,7 @@
       </c>
       <c r="G71" s="2">
         <f t="shared" si="17"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H71" s="2">
         <f t="shared" si="18"/>
@@ -4586,20 +7402,59 @@
         <v>10</v>
       </c>
       <c r="L71" s="2">
+        <v>0</v>
+      </c>
+      <c r="M71" s="2">
+        <v>0</v>
+      </c>
+      <c r="N71" s="2">
+        <v>0</v>
+      </c>
+      <c r="O71" s="2">
+        <v>0</v>
+      </c>
+      <c r="P71" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="2">
+        <v>0</v>
+      </c>
+      <c r="R71" s="2">
         <f t="shared" si="22"/>
-        <v>10</v>
-      </c>
-      <c r="M71" s="2">
+        <v>100</v>
+      </c>
+      <c r="S71" s="2">
+        <v>0</v>
+      </c>
+      <c r="T71" s="2">
+        <v>0</v>
+      </c>
+      <c r="U71" s="2">
+        <v>0</v>
+      </c>
+      <c r="V71" s="2">
+        <v>0</v>
+      </c>
+      <c r="W71" s="2">
+        <v>0</v>
+      </c>
+      <c r="X71" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="2">
         <v>1008</v>
       </c>
-      <c r="N71" s="2">
+      <c r="AA71" s="2">
         <v>77</v>
       </c>
-      <c r="O71" s="2">
+      <c r="AB71" s="2">
         <v>68</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
         <v>69</v>
       </c>
@@ -4625,7 +7480,7 @@
       </c>
       <c r="G72" s="2">
         <f t="shared" si="17"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H72" s="2">
         <f t="shared" si="18"/>
@@ -4644,20 +7499,59 @@
         <v>10</v>
       </c>
       <c r="L72" s="2">
+        <v>0</v>
+      </c>
+      <c r="M72" s="2">
+        <v>0</v>
+      </c>
+      <c r="N72" s="2">
+        <v>0</v>
+      </c>
+      <c r="O72" s="2">
+        <v>0</v>
+      </c>
+      <c r="P72" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="2">
+        <v>0</v>
+      </c>
+      <c r="R72" s="2">
         <f t="shared" si="22"/>
-        <v>10</v>
-      </c>
-      <c r="M72" s="2">
+        <v>100</v>
+      </c>
+      <c r="S72" s="2">
+        <v>0</v>
+      </c>
+      <c r="T72" s="2">
+        <v>0</v>
+      </c>
+      <c r="U72" s="2">
+        <v>0</v>
+      </c>
+      <c r="V72" s="2">
+        <v>0</v>
+      </c>
+      <c r="W72" s="2">
+        <v>0</v>
+      </c>
+      <c r="X72" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y72" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z72" s="2">
         <v>1009</v>
       </c>
-      <c r="N72" s="2">
+      <c r="AA72" s="2">
         <v>78</v>
       </c>
-      <c r="O72" s="2">
+      <c r="AB72" s="2">
         <v>69</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
         <v>70</v>
       </c>
@@ -4683,7 +7577,7 @@
       </c>
       <c r="G73" s="2">
         <f t="shared" si="17"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H73" s="2">
         <f t="shared" si="18"/>
@@ -4702,20 +7596,59 @@
         <v>10</v>
       </c>
       <c r="L73" s="2">
+        <v>0</v>
+      </c>
+      <c r="M73" s="2">
+        <v>0</v>
+      </c>
+      <c r="N73" s="2">
+        <v>0</v>
+      </c>
+      <c r="O73" s="2">
+        <v>0</v>
+      </c>
+      <c r="P73" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="2">
+        <v>0</v>
+      </c>
+      <c r="R73" s="2">
         <f t="shared" si="22"/>
-        <v>10</v>
-      </c>
-      <c r="M73" s="2">
+        <v>100</v>
+      </c>
+      <c r="S73" s="2">
+        <v>0</v>
+      </c>
+      <c r="T73" s="2">
+        <v>0</v>
+      </c>
+      <c r="U73" s="2">
+        <v>0</v>
+      </c>
+      <c r="V73" s="2">
+        <v>0</v>
+      </c>
+      <c r="W73" s="2">
+        <v>0</v>
+      </c>
+      <c r="X73" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z73" s="2">
         <v>1010</v>
       </c>
-      <c r="N73" s="2">
+      <c r="AA73" s="2">
         <v>79</v>
       </c>
-      <c r="O73" s="2">
+      <c r="AB73" s="2">
         <v>70</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
         <v>71</v>
       </c>
@@ -4741,7 +7674,7 @@
       </c>
       <c r="G74" s="2">
         <f t="shared" si="17"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H74" s="2">
         <f t="shared" si="18"/>
@@ -4760,20 +7693,59 @@
         <v>10</v>
       </c>
       <c r="L74" s="2">
+        <v>0</v>
+      </c>
+      <c r="M74" s="2">
+        <v>0</v>
+      </c>
+      <c r="N74" s="2">
+        <v>0</v>
+      </c>
+      <c r="O74" s="2">
+        <v>0</v>
+      </c>
+      <c r="P74" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="2">
+        <v>0</v>
+      </c>
+      <c r="R74" s="2">
         <f t="shared" si="22"/>
-        <v>10</v>
-      </c>
-      <c r="M74" s="2">
+        <v>100</v>
+      </c>
+      <c r="S74" s="2">
+        <v>0</v>
+      </c>
+      <c r="T74" s="2">
+        <v>0</v>
+      </c>
+      <c r="U74" s="2">
+        <v>0</v>
+      </c>
+      <c r="V74" s="2">
+        <v>0</v>
+      </c>
+      <c r="W74" s="2">
+        <v>0</v>
+      </c>
+      <c r="X74" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="2">
         <v>1011</v>
       </c>
-      <c r="N74" s="2">
+      <c r="AA74" s="2">
         <v>80</v>
       </c>
-      <c r="O74" s="2">
+      <c r="AB74" s="2">
         <v>71</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
         <v>72</v>
       </c>
@@ -4799,7 +7771,7 @@
       </c>
       <c r="G75" s="2">
         <f t="shared" si="17"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H75" s="2">
         <f t="shared" si="18"/>
@@ -4818,20 +7790,59 @@
         <v>10</v>
       </c>
       <c r="L75" s="2">
+        <v>0</v>
+      </c>
+      <c r="M75" s="2">
+        <v>0</v>
+      </c>
+      <c r="N75" s="2">
+        <v>0</v>
+      </c>
+      <c r="O75" s="2">
+        <v>0</v>
+      </c>
+      <c r="P75" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="2">
+        <v>0</v>
+      </c>
+      <c r="R75" s="2">
         <f t="shared" si="22"/>
-        <v>10</v>
-      </c>
-      <c r="M75" s="2">
+        <v>100</v>
+      </c>
+      <c r="S75" s="2">
+        <v>0</v>
+      </c>
+      <c r="T75" s="2">
+        <v>0</v>
+      </c>
+      <c r="U75" s="2">
+        <v>0</v>
+      </c>
+      <c r="V75" s="2">
+        <v>0</v>
+      </c>
+      <c r="W75" s="2">
+        <v>0</v>
+      </c>
+      <c r="X75" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="2">
         <v>1012</v>
       </c>
-      <c r="N75" s="2">
+      <c r="AA75" s="2">
         <v>81</v>
       </c>
-      <c r="O75" s="2">
+      <c r="AB75" s="2">
         <v>72</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
         <v>73</v>
       </c>
@@ -4857,7 +7868,7 @@
       </c>
       <c r="G76" s="2">
         <f t="shared" si="17"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H76" s="2">
         <f t="shared" si="18"/>
@@ -4876,20 +7887,59 @@
         <v>10</v>
       </c>
       <c r="L76" s="2">
+        <v>0</v>
+      </c>
+      <c r="M76" s="2">
+        <v>0</v>
+      </c>
+      <c r="N76" s="2">
+        <v>0</v>
+      </c>
+      <c r="O76" s="2">
+        <v>0</v>
+      </c>
+      <c r="P76" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="2">
+        <v>0</v>
+      </c>
+      <c r="R76" s="2">
         <f t="shared" si="22"/>
-        <v>10</v>
-      </c>
-      <c r="M76" s="2">
+        <v>100</v>
+      </c>
+      <c r="S76" s="2">
+        <v>0</v>
+      </c>
+      <c r="T76" s="2">
+        <v>0</v>
+      </c>
+      <c r="U76" s="2">
+        <v>0</v>
+      </c>
+      <c r="V76" s="2">
+        <v>0</v>
+      </c>
+      <c r="W76" s="2">
+        <v>0</v>
+      </c>
+      <c r="X76" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y76" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="2">
         <v>1013</v>
       </c>
-      <c r="N76" s="2">
+      <c r="AA76" s="2">
         <v>82</v>
       </c>
-      <c r="O76" s="2">
+      <c r="AB76" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
         <v>74</v>
       </c>
@@ -4915,7 +7965,7 @@
       </c>
       <c r="G77" s="2">
         <f t="shared" si="17"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H77" s="2">
         <f t="shared" si="18"/>
@@ -4934,20 +7984,59 @@
         <v>10</v>
       </c>
       <c r="L77" s="2">
+        <v>0</v>
+      </c>
+      <c r="M77" s="2">
+        <v>0</v>
+      </c>
+      <c r="N77" s="2">
+        <v>0</v>
+      </c>
+      <c r="O77" s="2">
+        <v>0</v>
+      </c>
+      <c r="P77" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="2">
+        <v>0</v>
+      </c>
+      <c r="R77" s="2">
         <f t="shared" si="22"/>
-        <v>10</v>
-      </c>
-      <c r="M77" s="2">
+        <v>100</v>
+      </c>
+      <c r="S77" s="2">
+        <v>0</v>
+      </c>
+      <c r="T77" s="2">
+        <v>0</v>
+      </c>
+      <c r="U77" s="2">
+        <v>0</v>
+      </c>
+      <c r="V77" s="2">
+        <v>0</v>
+      </c>
+      <c r="W77" s="2">
+        <v>0</v>
+      </c>
+      <c r="X77" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="2">
         <v>1014</v>
       </c>
-      <c r="N77" s="2">
+      <c r="AA77" s="2">
         <v>83</v>
       </c>
-      <c r="O77" s="2">
+      <c r="AB77" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
         <v>75</v>
       </c>
@@ -4973,7 +8062,7 @@
       </c>
       <c r="G78" s="2">
         <f t="shared" si="17"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H78" s="2">
         <f t="shared" si="18"/>
@@ -4992,20 +8081,59 @@
         <v>10</v>
       </c>
       <c r="L78" s="2">
+        <v>0</v>
+      </c>
+      <c r="M78" s="2">
+        <v>0</v>
+      </c>
+      <c r="N78" s="2">
+        <v>0</v>
+      </c>
+      <c r="O78" s="2">
+        <v>0</v>
+      </c>
+      <c r="P78" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="2">
+        <v>0</v>
+      </c>
+      <c r="R78" s="2">
         <f t="shared" si="22"/>
-        <v>10</v>
-      </c>
-      <c r="M78" s="2">
+        <v>100</v>
+      </c>
+      <c r="S78" s="2">
+        <v>0</v>
+      </c>
+      <c r="T78" s="2">
+        <v>0</v>
+      </c>
+      <c r="U78" s="2">
+        <v>0</v>
+      </c>
+      <c r="V78" s="2">
+        <v>0</v>
+      </c>
+      <c r="W78" s="2">
+        <v>0</v>
+      </c>
+      <c r="X78" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y78" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z78" s="2">
         <v>1015</v>
       </c>
-      <c r="N78" s="2">
+      <c r="AA78" s="2">
         <v>84</v>
       </c>
-      <c r="O78" s="2">
+      <c r="AB78" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
         <v>76</v>
       </c>
@@ -5031,7 +8159,7 @@
       </c>
       <c r="G79" s="2">
         <f t="shared" si="17"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H79" s="2">
         <f t="shared" si="18"/>
@@ -5050,20 +8178,59 @@
         <v>10</v>
       </c>
       <c r="L79" s="2">
+        <v>0</v>
+      </c>
+      <c r="M79" s="2">
+        <v>0</v>
+      </c>
+      <c r="N79" s="2">
+        <v>0</v>
+      </c>
+      <c r="O79" s="2">
+        <v>0</v>
+      </c>
+      <c r="P79" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="2">
+        <v>0</v>
+      </c>
+      <c r="R79" s="2">
         <f t="shared" si="22"/>
-        <v>10</v>
-      </c>
-      <c r="M79" s="2">
+        <v>100</v>
+      </c>
+      <c r="S79" s="2">
+        <v>0</v>
+      </c>
+      <c r="T79" s="2">
+        <v>0</v>
+      </c>
+      <c r="U79" s="2">
+        <v>0</v>
+      </c>
+      <c r="V79" s="2">
+        <v>0</v>
+      </c>
+      <c r="W79" s="2">
+        <v>0</v>
+      </c>
+      <c r="X79" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y79" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z79" s="2">
         <v>1016</v>
       </c>
-      <c r="N79" s="2">
+      <c r="AA79" s="2">
         <v>85</v>
       </c>
-      <c r="O79" s="2">
+      <c r="AB79" s="2">
         <v>76</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
         <v>77</v>
       </c>
@@ -5089,7 +8256,7 @@
       </c>
       <c r="G80" s="2">
         <f t="shared" si="17"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H80" s="2">
         <f t="shared" si="18"/>
@@ -5108,20 +8275,59 @@
         <v>10</v>
       </c>
       <c r="L80" s="2">
+        <v>0</v>
+      </c>
+      <c r="M80" s="2">
+        <v>0</v>
+      </c>
+      <c r="N80" s="2">
+        <v>0</v>
+      </c>
+      <c r="O80" s="2">
+        <v>0</v>
+      </c>
+      <c r="P80" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="2">
+        <v>0</v>
+      </c>
+      <c r="R80" s="2">
         <f t="shared" si="22"/>
-        <v>10</v>
-      </c>
-      <c r="M80" s="2">
+        <v>100</v>
+      </c>
+      <c r="S80" s="2">
+        <v>0</v>
+      </c>
+      <c r="T80" s="2">
+        <v>0</v>
+      </c>
+      <c r="U80" s="2">
+        <v>0</v>
+      </c>
+      <c r="V80" s="2">
+        <v>0</v>
+      </c>
+      <c r="W80" s="2">
+        <v>0</v>
+      </c>
+      <c r="X80" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y80" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z80" s="2">
         <v>1017</v>
       </c>
-      <c r="N80" s="2">
+      <c r="AA80" s="2">
         <v>86</v>
       </c>
-      <c r="O80" s="2">
+      <c r="AB80" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
         <v>78</v>
       </c>
@@ -5147,7 +8353,7 @@
       </c>
       <c r="G81" s="2">
         <f t="shared" si="17"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H81" s="2">
         <f t="shared" si="18"/>
@@ -5166,20 +8372,59 @@
         <v>10</v>
       </c>
       <c r="L81" s="2">
+        <v>0</v>
+      </c>
+      <c r="M81" s="2">
+        <v>0</v>
+      </c>
+      <c r="N81" s="2">
+        <v>0</v>
+      </c>
+      <c r="O81" s="2">
+        <v>0</v>
+      </c>
+      <c r="P81" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="2">
+        <v>0</v>
+      </c>
+      <c r="R81" s="2">
         <f t="shared" si="22"/>
-        <v>10</v>
-      </c>
-      <c r="M81" s="2">
+        <v>100</v>
+      </c>
+      <c r="S81" s="2">
+        <v>0</v>
+      </c>
+      <c r="T81" s="2">
+        <v>0</v>
+      </c>
+      <c r="U81" s="2">
+        <v>0</v>
+      </c>
+      <c r="V81" s="2">
+        <v>0</v>
+      </c>
+      <c r="W81" s="2">
+        <v>0</v>
+      </c>
+      <c r="X81" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y81" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z81" s="2">
         <v>1018</v>
       </c>
-      <c r="N81" s="2">
+      <c r="AA81" s="2">
         <v>87</v>
       </c>
-      <c r="O81" s="2">
+      <c r="AB81" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
         <v>79</v>
       </c>
@@ -5205,7 +8450,7 @@
       </c>
       <c r="G82" s="2">
         <f t="shared" si="17"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H82" s="2">
         <f t="shared" si="18"/>
@@ -5224,20 +8469,59 @@
         <v>10</v>
       </c>
       <c r="L82" s="2">
+        <v>0</v>
+      </c>
+      <c r="M82" s="2">
+        <v>0</v>
+      </c>
+      <c r="N82" s="2">
+        <v>0</v>
+      </c>
+      <c r="O82" s="2">
+        <v>0</v>
+      </c>
+      <c r="P82" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="2">
+        <v>0</v>
+      </c>
+      <c r="R82" s="2">
         <f t="shared" si="22"/>
-        <v>10</v>
-      </c>
-      <c r="M82" s="2">
+        <v>100</v>
+      </c>
+      <c r="S82" s="2">
+        <v>0</v>
+      </c>
+      <c r="T82" s="2">
+        <v>0</v>
+      </c>
+      <c r="U82" s="2">
+        <v>0</v>
+      </c>
+      <c r="V82" s="2">
+        <v>0</v>
+      </c>
+      <c r="W82" s="2">
+        <v>0</v>
+      </c>
+      <c r="X82" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y82" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z82" s="2">
         <v>1019</v>
       </c>
-      <c r="N82" s="2">
+      <c r="AA82" s="2">
         <v>88</v>
       </c>
-      <c r="O82" s="2">
+      <c r="AB82" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
         <v>80</v>
       </c>
@@ -5263,7 +8547,7 @@
       </c>
       <c r="G83" s="2">
         <f t="shared" si="17"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H83" s="2">
         <f t="shared" si="18"/>
@@ -5282,20 +8566,59 @@
         <v>10</v>
       </c>
       <c r="L83" s="2">
+        <v>0</v>
+      </c>
+      <c r="M83" s="2">
+        <v>0</v>
+      </c>
+      <c r="N83" s="2">
+        <v>0</v>
+      </c>
+      <c r="O83" s="2">
+        <v>0</v>
+      </c>
+      <c r="P83" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="2">
+        <v>0</v>
+      </c>
+      <c r="R83" s="2">
         <f t="shared" si="22"/>
-        <v>10</v>
-      </c>
-      <c r="M83" s="2">
+        <v>100</v>
+      </c>
+      <c r="S83" s="2">
+        <v>0</v>
+      </c>
+      <c r="T83" s="2">
+        <v>0</v>
+      </c>
+      <c r="U83" s="2">
+        <v>0</v>
+      </c>
+      <c r="V83" s="2">
+        <v>0</v>
+      </c>
+      <c r="W83" s="2">
+        <v>0</v>
+      </c>
+      <c r="X83" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="2">
         <v>1020</v>
       </c>
-      <c r="N83" s="2">
+      <c r="AA83" s="2">
         <v>89</v>
       </c>
-      <c r="O83" s="2">
+      <c r="AB83" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
         <v>81</v>
       </c>
@@ -5321,7 +8644,7 @@
       </c>
       <c r="G84" s="2">
         <f t="shared" si="17"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H84" s="2">
         <f t="shared" si="18"/>
@@ -5340,20 +8663,59 @@
         <v>10</v>
       </c>
       <c r="L84" s="2">
+        <v>0</v>
+      </c>
+      <c r="M84" s="2">
+        <v>0</v>
+      </c>
+      <c r="N84" s="2">
+        <v>0</v>
+      </c>
+      <c r="O84" s="2">
+        <v>0</v>
+      </c>
+      <c r="P84" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="2">
+        <v>0</v>
+      </c>
+      <c r="R84" s="2">
         <f t="shared" si="22"/>
-        <v>10</v>
-      </c>
-      <c r="M84" s="2">
+        <v>100</v>
+      </c>
+      <c r="S84" s="2">
+        <v>0</v>
+      </c>
+      <c r="T84" s="2">
+        <v>0</v>
+      </c>
+      <c r="U84" s="2">
+        <v>0</v>
+      </c>
+      <c r="V84" s="2">
+        <v>0</v>
+      </c>
+      <c r="W84" s="2">
+        <v>0</v>
+      </c>
+      <c r="X84" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="2">
         <v>1001</v>
       </c>
-      <c r="N84" s="2">
+      <c r="AA84" s="2">
         <v>90</v>
       </c>
-      <c r="O84" s="2">
+      <c r="AB84" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
         <v>82</v>
       </c>
@@ -5379,7 +8741,7 @@
       </c>
       <c r="G85" s="2">
         <f t="shared" si="17"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H85" s="2">
         <f t="shared" si="18"/>
@@ -5398,20 +8760,59 @@
         <v>10</v>
       </c>
       <c r="L85" s="2">
+        <v>0</v>
+      </c>
+      <c r="M85" s="2">
+        <v>0</v>
+      </c>
+      <c r="N85" s="2">
+        <v>0</v>
+      </c>
+      <c r="O85" s="2">
+        <v>0</v>
+      </c>
+      <c r="P85" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="2">
+        <v>0</v>
+      </c>
+      <c r="R85" s="2">
         <f t="shared" si="22"/>
-        <v>10</v>
-      </c>
-      <c r="M85" s="2">
+        <v>100</v>
+      </c>
+      <c r="S85" s="2">
+        <v>0</v>
+      </c>
+      <c r="T85" s="2">
+        <v>0</v>
+      </c>
+      <c r="U85" s="2">
+        <v>0</v>
+      </c>
+      <c r="V85" s="2">
+        <v>0</v>
+      </c>
+      <c r="W85" s="2">
+        <v>0</v>
+      </c>
+      <c r="X85" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z85" s="2">
         <v>1002</v>
       </c>
-      <c r="N85" s="2">
+      <c r="AA85" s="2">
         <v>91</v>
       </c>
-      <c r="O85" s="2">
+      <c r="AB85" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
         <v>83</v>
       </c>
@@ -5437,7 +8838,7 @@
       </c>
       <c r="G86" s="2">
         <f t="shared" si="17"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H86" s="2">
         <f t="shared" si="18"/>
@@ -5456,20 +8857,59 @@
         <v>10</v>
       </c>
       <c r="L86" s="2">
+        <v>0</v>
+      </c>
+      <c r="M86" s="2">
+        <v>0</v>
+      </c>
+      <c r="N86" s="2">
+        <v>0</v>
+      </c>
+      <c r="O86" s="2">
+        <v>0</v>
+      </c>
+      <c r="P86" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="2">
+        <v>0</v>
+      </c>
+      <c r="R86" s="2">
         <f t="shared" si="22"/>
-        <v>10</v>
-      </c>
-      <c r="M86" s="2">
+        <v>100</v>
+      </c>
+      <c r="S86" s="2">
+        <v>0</v>
+      </c>
+      <c r="T86" s="2">
+        <v>0</v>
+      </c>
+      <c r="U86" s="2">
+        <v>0</v>
+      </c>
+      <c r="V86" s="2">
+        <v>0</v>
+      </c>
+      <c r="W86" s="2">
+        <v>0</v>
+      </c>
+      <c r="X86" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z86" s="2">
         <v>1003</v>
       </c>
-      <c r="N86" s="2">
+      <c r="AA86" s="2">
         <v>92</v>
       </c>
-      <c r="O86" s="2">
+      <c r="AB86" s="2">
         <v>83</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
         <v>84</v>
       </c>
@@ -5495,7 +8935,7 @@
       </c>
       <c r="G87" s="2">
         <f t="shared" si="17"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H87" s="2">
         <f t="shared" si="18"/>
@@ -5514,20 +8954,59 @@
         <v>10</v>
       </c>
       <c r="L87" s="2">
+        <v>0</v>
+      </c>
+      <c r="M87" s="2">
+        <v>0</v>
+      </c>
+      <c r="N87" s="2">
+        <v>0</v>
+      </c>
+      <c r="O87" s="2">
+        <v>0</v>
+      </c>
+      <c r="P87" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="2">
+        <v>0</v>
+      </c>
+      <c r="R87" s="2">
         <f t="shared" si="22"/>
-        <v>10</v>
-      </c>
-      <c r="M87" s="2">
+        <v>100</v>
+      </c>
+      <c r="S87" s="2">
+        <v>0</v>
+      </c>
+      <c r="T87" s="2">
+        <v>0</v>
+      </c>
+      <c r="U87" s="2">
+        <v>0</v>
+      </c>
+      <c r="V87" s="2">
+        <v>0</v>
+      </c>
+      <c r="W87" s="2">
+        <v>0</v>
+      </c>
+      <c r="X87" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z87" s="2">
         <v>1004</v>
       </c>
-      <c r="N87" s="2">
+      <c r="AA87" s="2">
         <v>93</v>
       </c>
-      <c r="O87" s="2">
+      <c r="AB87" s="2">
         <v>84</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
         <v>85</v>
       </c>
@@ -5553,7 +9032,7 @@
       </c>
       <c r="G88" s="2">
         <f t="shared" si="17"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H88" s="2">
         <f t="shared" si="18"/>
@@ -5572,20 +9051,59 @@
         <v>10</v>
       </c>
       <c r="L88" s="2">
+        <v>0</v>
+      </c>
+      <c r="M88" s="2">
+        <v>0</v>
+      </c>
+      <c r="N88" s="2">
+        <v>0</v>
+      </c>
+      <c r="O88" s="2">
+        <v>0</v>
+      </c>
+      <c r="P88" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="2">
+        <v>0</v>
+      </c>
+      <c r="R88" s="2">
         <f t="shared" si="22"/>
-        <v>10</v>
-      </c>
-      <c r="M88" s="2">
+        <v>100</v>
+      </c>
+      <c r="S88" s="2">
+        <v>0</v>
+      </c>
+      <c r="T88" s="2">
+        <v>0</v>
+      </c>
+      <c r="U88" s="2">
+        <v>0</v>
+      </c>
+      <c r="V88" s="2">
+        <v>0</v>
+      </c>
+      <c r="W88" s="2">
+        <v>0</v>
+      </c>
+      <c r="X88" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z88" s="2">
         <v>1005</v>
       </c>
-      <c r="N88" s="2">
+      <c r="AA88" s="2">
         <v>94</v>
       </c>
-      <c r="O88" s="2">
+      <c r="AB88" s="2">
         <v>85</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
         <v>86</v>
       </c>
@@ -5611,7 +9129,7 @@
       </c>
       <c r="G89" s="2">
         <f t="shared" si="17"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H89" s="2">
         <f t="shared" si="18"/>
@@ -5630,20 +9148,59 @@
         <v>10</v>
       </c>
       <c r="L89" s="2">
+        <v>0</v>
+      </c>
+      <c r="M89" s="2">
+        <v>0</v>
+      </c>
+      <c r="N89" s="2">
+        <v>0</v>
+      </c>
+      <c r="O89" s="2">
+        <v>0</v>
+      </c>
+      <c r="P89" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="2">
+        <v>0</v>
+      </c>
+      <c r="R89" s="2">
         <f t="shared" si="22"/>
-        <v>10</v>
-      </c>
-      <c r="M89" s="2">
+        <v>100</v>
+      </c>
+      <c r="S89" s="2">
+        <v>0</v>
+      </c>
+      <c r="T89" s="2">
+        <v>0</v>
+      </c>
+      <c r="U89" s="2">
+        <v>0</v>
+      </c>
+      <c r="V89" s="2">
+        <v>0</v>
+      </c>
+      <c r="W89" s="2">
+        <v>0</v>
+      </c>
+      <c r="X89" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="2">
         <v>1006</v>
       </c>
-      <c r="N89" s="2">
+      <c r="AA89" s="2">
         <v>95</v>
       </c>
-      <c r="O89" s="2">
+      <c r="AB89" s="2">
         <v>86</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
         <v>87</v>
       </c>
@@ -5669,7 +9226,7 @@
       </c>
       <c r="G90" s="2">
         <f t="shared" si="17"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H90" s="2">
         <f t="shared" si="18"/>
@@ -5688,20 +9245,59 @@
         <v>10</v>
       </c>
       <c r="L90" s="2">
+        <v>0</v>
+      </c>
+      <c r="M90" s="2">
+        <v>0</v>
+      </c>
+      <c r="N90" s="2">
+        <v>0</v>
+      </c>
+      <c r="O90" s="2">
+        <v>0</v>
+      </c>
+      <c r="P90" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="2">
+        <v>0</v>
+      </c>
+      <c r="R90" s="2">
         <f t="shared" si="22"/>
-        <v>10</v>
-      </c>
-      <c r="M90" s="2">
+        <v>100</v>
+      </c>
+      <c r="S90" s="2">
+        <v>0</v>
+      </c>
+      <c r="T90" s="2">
+        <v>0</v>
+      </c>
+      <c r="U90" s="2">
+        <v>0</v>
+      </c>
+      <c r="V90" s="2">
+        <v>0</v>
+      </c>
+      <c r="W90" s="2">
+        <v>0</v>
+      </c>
+      <c r="X90" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y90" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z90" s="2">
         <v>1007</v>
       </c>
-      <c r="N90" s="2">
+      <c r="AA90" s="2">
         <v>96</v>
       </c>
-      <c r="O90" s="2">
+      <c r="AB90" s="2">
         <v>87</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
         <v>88</v>
       </c>
@@ -5727,7 +9323,7 @@
       </c>
       <c r="G91" s="2">
         <f t="shared" si="17"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H91" s="2">
         <f t="shared" si="18"/>
@@ -5746,20 +9342,59 @@
         <v>10</v>
       </c>
       <c r="L91" s="2">
+        <v>0</v>
+      </c>
+      <c r="M91" s="2">
+        <v>0</v>
+      </c>
+      <c r="N91" s="2">
+        <v>0</v>
+      </c>
+      <c r="O91" s="2">
+        <v>0</v>
+      </c>
+      <c r="P91" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="2">
+        <v>0</v>
+      </c>
+      <c r="R91" s="2">
         <f t="shared" si="22"/>
-        <v>10</v>
-      </c>
-      <c r="M91" s="2">
+        <v>100</v>
+      </c>
+      <c r="S91" s="2">
+        <v>0</v>
+      </c>
+      <c r="T91" s="2">
+        <v>0</v>
+      </c>
+      <c r="U91" s="2">
+        <v>0</v>
+      </c>
+      <c r="V91" s="2">
+        <v>0</v>
+      </c>
+      <c r="W91" s="2">
+        <v>0</v>
+      </c>
+      <c r="X91" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="2">
         <v>1008</v>
       </c>
-      <c r="N91" s="2">
+      <c r="AA91" s="2">
         <v>97</v>
       </c>
-      <c r="O91" s="2">
+      <c r="AB91" s="2">
         <v>88</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
         <v>89</v>
       </c>
@@ -5785,7 +9420,7 @@
       </c>
       <c r="G92" s="2">
         <f t="shared" si="17"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H92" s="2">
         <f t="shared" si="18"/>
@@ -5804,20 +9439,59 @@
         <v>10</v>
       </c>
       <c r="L92" s="2">
+        <v>0</v>
+      </c>
+      <c r="M92" s="2">
+        <v>0</v>
+      </c>
+      <c r="N92" s="2">
+        <v>0</v>
+      </c>
+      <c r="O92" s="2">
+        <v>0</v>
+      </c>
+      <c r="P92" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="2">
+        <v>0</v>
+      </c>
+      <c r="R92" s="2">
         <f t="shared" si="22"/>
-        <v>10</v>
-      </c>
-      <c r="M92" s="2">
+        <v>100</v>
+      </c>
+      <c r="S92" s="2">
+        <v>0</v>
+      </c>
+      <c r="T92" s="2">
+        <v>0</v>
+      </c>
+      <c r="U92" s="2">
+        <v>0</v>
+      </c>
+      <c r="V92" s="2">
+        <v>0</v>
+      </c>
+      <c r="W92" s="2">
+        <v>0</v>
+      </c>
+      <c r="X92" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z92" s="2">
         <v>1009</v>
       </c>
-      <c r="N92" s="2">
+      <c r="AA92" s="2">
         <v>98</v>
       </c>
-      <c r="O92" s="2">
+      <c r="AB92" s="2">
         <v>89</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
         <v>90</v>
       </c>
@@ -5843,7 +9517,7 @@
       </c>
       <c r="G93" s="2">
         <f t="shared" si="17"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H93" s="2">
         <f t="shared" si="18"/>
@@ -5862,20 +9536,59 @@
         <v>10</v>
       </c>
       <c r="L93" s="2">
+        <v>0</v>
+      </c>
+      <c r="M93" s="2">
+        <v>0</v>
+      </c>
+      <c r="N93" s="2">
+        <v>0</v>
+      </c>
+      <c r="O93" s="2">
+        <v>0</v>
+      </c>
+      <c r="P93" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="2">
+        <v>0</v>
+      </c>
+      <c r="R93" s="2">
         <f t="shared" si="22"/>
-        <v>10</v>
-      </c>
-      <c r="M93" s="2">
+        <v>100</v>
+      </c>
+      <c r="S93" s="2">
+        <v>0</v>
+      </c>
+      <c r="T93" s="2">
+        <v>0</v>
+      </c>
+      <c r="U93" s="2">
+        <v>0</v>
+      </c>
+      <c r="V93" s="2">
+        <v>0</v>
+      </c>
+      <c r="W93" s="2">
+        <v>0</v>
+      </c>
+      <c r="X93" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z93" s="2">
         <v>1010</v>
       </c>
-      <c r="N93" s="2">
+      <c r="AA93" s="2">
         <v>99</v>
       </c>
-      <c r="O93" s="2">
+      <c r="AB93" s="2">
         <v>90</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
         <v>91</v>
       </c>
@@ -5901,7 +9614,7 @@
       </c>
       <c r="G94" s="2">
         <f t="shared" si="17"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H94" s="2">
         <f t="shared" si="18"/>
@@ -5920,20 +9633,59 @@
         <v>10</v>
       </c>
       <c r="L94" s="2">
+        <v>0</v>
+      </c>
+      <c r="M94" s="2">
+        <v>0</v>
+      </c>
+      <c r="N94" s="2">
+        <v>0</v>
+      </c>
+      <c r="O94" s="2">
+        <v>0</v>
+      </c>
+      <c r="P94" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="2">
+        <v>0</v>
+      </c>
+      <c r="R94" s="2">
         <f t="shared" si="22"/>
-        <v>10</v>
-      </c>
-      <c r="M94" s="2">
+        <v>100</v>
+      </c>
+      <c r="S94" s="2">
+        <v>0</v>
+      </c>
+      <c r="T94" s="2">
+        <v>0</v>
+      </c>
+      <c r="U94" s="2">
+        <v>0</v>
+      </c>
+      <c r="V94" s="2">
+        <v>0</v>
+      </c>
+      <c r="W94" s="2">
+        <v>0</v>
+      </c>
+      <c r="X94" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="2">
         <v>1011</v>
       </c>
-      <c r="N94" s="2">
+      <c r="AA94" s="2">
         <v>100</v>
       </c>
-      <c r="O94" s="2">
+      <c r="AB94" s="2">
         <v>91</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
         <v>92</v>
       </c>
@@ -5959,7 +9711,7 @@
       </c>
       <c r="G95" s="2">
         <f t="shared" si="17"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H95" s="2">
         <f t="shared" si="18"/>
@@ -5978,20 +9730,59 @@
         <v>10</v>
       </c>
       <c r="L95" s="2">
+        <v>0</v>
+      </c>
+      <c r="M95" s="2">
+        <v>0</v>
+      </c>
+      <c r="N95" s="2">
+        <v>0</v>
+      </c>
+      <c r="O95" s="2">
+        <v>0</v>
+      </c>
+      <c r="P95" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q95" s="2">
+        <v>0</v>
+      </c>
+      <c r="R95" s="2">
         <f t="shared" si="22"/>
-        <v>10</v>
-      </c>
-      <c r="M95" s="2">
+        <v>100</v>
+      </c>
+      <c r="S95" s="2">
+        <v>0</v>
+      </c>
+      <c r="T95" s="2">
+        <v>0</v>
+      </c>
+      <c r="U95" s="2">
+        <v>0</v>
+      </c>
+      <c r="V95" s="2">
+        <v>0</v>
+      </c>
+      <c r="W95" s="2">
+        <v>0</v>
+      </c>
+      <c r="X95" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y95" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z95" s="2">
         <v>1012</v>
       </c>
-      <c r="N95" s="2">
+      <c r="AA95" s="2">
         <v>101</v>
       </c>
-      <c r="O95" s="2">
+      <c r="AB95" s="2">
         <v>92</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
         <v>93</v>
       </c>
@@ -6017,7 +9808,7 @@
       </c>
       <c r="G96" s="2">
         <f t="shared" si="17"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H96" s="2">
         <f t="shared" si="18"/>
@@ -6036,20 +9827,59 @@
         <v>10</v>
       </c>
       <c r="L96" s="2">
+        <v>0</v>
+      </c>
+      <c r="M96" s="2">
+        <v>0</v>
+      </c>
+      <c r="N96" s="2">
+        <v>0</v>
+      </c>
+      <c r="O96" s="2">
+        <v>0</v>
+      </c>
+      <c r="P96" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="2">
+        <v>0</v>
+      </c>
+      <c r="R96" s="2">
         <f t="shared" si="22"/>
-        <v>10</v>
-      </c>
-      <c r="M96" s="2">
+        <v>100</v>
+      </c>
+      <c r="S96" s="2">
+        <v>0</v>
+      </c>
+      <c r="T96" s="2">
+        <v>0</v>
+      </c>
+      <c r="U96" s="2">
+        <v>0</v>
+      </c>
+      <c r="V96" s="2">
+        <v>0</v>
+      </c>
+      <c r="W96" s="2">
+        <v>0</v>
+      </c>
+      <c r="X96" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="2">
         <v>1013</v>
       </c>
-      <c r="N96" s="2">
+      <c r="AA96" s="2">
         <v>102</v>
       </c>
-      <c r="O96" s="2">
+      <c r="AB96" s="2">
         <v>93</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
         <v>94</v>
       </c>
@@ -6075,7 +9905,7 @@
       </c>
       <c r="G97" s="2">
         <f t="shared" si="17"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H97" s="2">
         <f t="shared" si="18"/>
@@ -6094,20 +9924,59 @@
         <v>10</v>
       </c>
       <c r="L97" s="2">
+        <v>0</v>
+      </c>
+      <c r="M97" s="2">
+        <v>0</v>
+      </c>
+      <c r="N97" s="2">
+        <v>0</v>
+      </c>
+      <c r="O97" s="2">
+        <v>0</v>
+      </c>
+      <c r="P97" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="2">
+        <v>0</v>
+      </c>
+      <c r="R97" s="2">
         <f t="shared" si="22"/>
-        <v>10</v>
-      </c>
-      <c r="M97" s="2">
+        <v>100</v>
+      </c>
+      <c r="S97" s="2">
+        <v>0</v>
+      </c>
+      <c r="T97" s="2">
+        <v>0</v>
+      </c>
+      <c r="U97" s="2">
+        <v>0</v>
+      </c>
+      <c r="V97" s="2">
+        <v>0</v>
+      </c>
+      <c r="W97" s="2">
+        <v>0</v>
+      </c>
+      <c r="X97" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z97" s="2">
         <v>1014</v>
       </c>
-      <c r="N97" s="2">
+      <c r="AA97" s="2">
         <v>103</v>
       </c>
-      <c r="O97" s="2">
+      <c r="AB97" s="2">
         <v>94</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
         <v>95</v>
       </c>
@@ -6133,7 +10002,7 @@
       </c>
       <c r="G98" s="2">
         <f t="shared" si="17"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H98" s="2">
         <f t="shared" si="18"/>
@@ -6152,20 +10021,59 @@
         <v>10</v>
       </c>
       <c r="L98" s="2">
+        <v>0</v>
+      </c>
+      <c r="M98" s="2">
+        <v>0</v>
+      </c>
+      <c r="N98" s="2">
+        <v>0</v>
+      </c>
+      <c r="O98" s="2">
+        <v>0</v>
+      </c>
+      <c r="P98" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="2">
+        <v>0</v>
+      </c>
+      <c r="R98" s="2">
         <f t="shared" si="22"/>
-        <v>10</v>
-      </c>
-      <c r="M98" s="2">
+        <v>100</v>
+      </c>
+      <c r="S98" s="2">
+        <v>0</v>
+      </c>
+      <c r="T98" s="2">
+        <v>0</v>
+      </c>
+      <c r="U98" s="2">
+        <v>0</v>
+      </c>
+      <c r="V98" s="2">
+        <v>0</v>
+      </c>
+      <c r="W98" s="2">
+        <v>0</v>
+      </c>
+      <c r="X98" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z98" s="2">
         <v>1015</v>
       </c>
-      <c r="N98" s="2">
+      <c r="AA98" s="2">
         <v>104</v>
       </c>
-      <c r="O98" s="2">
+      <c r="AB98" s="2">
         <v>95</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
         <v>96</v>
       </c>
@@ -6191,7 +10099,7 @@
       </c>
       <c r="G99" s="2">
         <f t="shared" si="17"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H99" s="2">
         <f t="shared" si="18"/>
@@ -6210,20 +10118,59 @@
         <v>10</v>
       </c>
       <c r="L99" s="2">
+        <v>0</v>
+      </c>
+      <c r="M99" s="2">
+        <v>0</v>
+      </c>
+      <c r="N99" s="2">
+        <v>0</v>
+      </c>
+      <c r="O99" s="2">
+        <v>0</v>
+      </c>
+      <c r="P99" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="2">
+        <v>0</v>
+      </c>
+      <c r="R99" s="2">
         <f t="shared" si="22"/>
-        <v>10</v>
-      </c>
-      <c r="M99" s="2">
+        <v>100</v>
+      </c>
+      <c r="S99" s="2">
+        <v>0</v>
+      </c>
+      <c r="T99" s="2">
+        <v>0</v>
+      </c>
+      <c r="U99" s="2">
+        <v>0</v>
+      </c>
+      <c r="V99" s="2">
+        <v>0</v>
+      </c>
+      <c r="W99" s="2">
+        <v>0</v>
+      </c>
+      <c r="X99" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z99" s="2">
         <v>1016</v>
       </c>
-      <c r="N99" s="2">
+      <c r="AA99" s="2">
         <v>105</v>
       </c>
-      <c r="O99" s="2">
+      <c r="AB99" s="2">
         <v>96</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
         <v>97</v>
       </c>
@@ -6249,7 +10196,7 @@
       </c>
       <c r="G100" s="2">
         <f t="shared" si="17"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H100" s="2">
         <f t="shared" si="18"/>
@@ -6268,20 +10215,59 @@
         <v>10</v>
       </c>
       <c r="L100" s="2">
+        <v>0</v>
+      </c>
+      <c r="M100" s="2">
+        <v>0</v>
+      </c>
+      <c r="N100" s="2">
+        <v>0</v>
+      </c>
+      <c r="O100" s="2">
+        <v>0</v>
+      </c>
+      <c r="P100" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="2">
+        <v>0</v>
+      </c>
+      <c r="R100" s="2">
         <f t="shared" si="22"/>
-        <v>10</v>
-      </c>
-      <c r="M100" s="2">
+        <v>100</v>
+      </c>
+      <c r="S100" s="2">
+        <v>0</v>
+      </c>
+      <c r="T100" s="2">
+        <v>0</v>
+      </c>
+      <c r="U100" s="2">
+        <v>0</v>
+      </c>
+      <c r="V100" s="2">
+        <v>0</v>
+      </c>
+      <c r="W100" s="2">
+        <v>0</v>
+      </c>
+      <c r="X100" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="2">
         <v>1017</v>
       </c>
-      <c r="N100" s="2">
+      <c r="AA100" s="2">
         <v>106</v>
       </c>
-      <c r="O100" s="2">
+      <c r="AB100" s="2">
         <v>97</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
         <v>98</v>
       </c>
@@ -6307,7 +10293,7 @@
       </c>
       <c r="G101" s="2">
         <f t="shared" si="17"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H101" s="2">
         <f t="shared" si="18"/>
@@ -6326,20 +10312,59 @@
         <v>10</v>
       </c>
       <c r="L101" s="2">
+        <v>0</v>
+      </c>
+      <c r="M101" s="2">
+        <v>0</v>
+      </c>
+      <c r="N101" s="2">
+        <v>0</v>
+      </c>
+      <c r="O101" s="2">
+        <v>0</v>
+      </c>
+      <c r="P101" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="2">
+        <v>0</v>
+      </c>
+      <c r="R101" s="2">
         <f t="shared" si="22"/>
-        <v>10</v>
-      </c>
-      <c r="M101" s="2">
+        <v>100</v>
+      </c>
+      <c r="S101" s="2">
+        <v>0</v>
+      </c>
+      <c r="T101" s="2">
+        <v>0</v>
+      </c>
+      <c r="U101" s="2">
+        <v>0</v>
+      </c>
+      <c r="V101" s="2">
+        <v>0</v>
+      </c>
+      <c r="W101" s="2">
+        <v>0</v>
+      </c>
+      <c r="X101" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="2">
         <v>1018</v>
       </c>
-      <c r="N101" s="2">
+      <c r="AA101" s="2">
         <v>107</v>
       </c>
-      <c r="O101" s="2">
+      <c r="AB101" s="2">
         <v>98</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
         <v>99</v>
       </c>
@@ -6365,7 +10390,7 @@
       </c>
       <c r="G102" s="2">
         <f t="shared" si="17"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H102" s="2">
         <f t="shared" si="18"/>
@@ -6384,20 +10409,59 @@
         <v>10</v>
       </c>
       <c r="L102" s="2">
+        <v>0</v>
+      </c>
+      <c r="M102" s="2">
+        <v>0</v>
+      </c>
+      <c r="N102" s="2">
+        <v>0</v>
+      </c>
+      <c r="O102" s="2">
+        <v>0</v>
+      </c>
+      <c r="P102" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="2">
+        <v>0</v>
+      </c>
+      <c r="R102" s="2">
         <f t="shared" si="22"/>
-        <v>10</v>
-      </c>
-      <c r="M102" s="2">
+        <v>100</v>
+      </c>
+      <c r="S102" s="2">
+        <v>0</v>
+      </c>
+      <c r="T102" s="2">
+        <v>0</v>
+      </c>
+      <c r="U102" s="2">
+        <v>0</v>
+      </c>
+      <c r="V102" s="2">
+        <v>0</v>
+      </c>
+      <c r="W102" s="2">
+        <v>0</v>
+      </c>
+      <c r="X102" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="2">
         <v>1019</v>
       </c>
-      <c r="N102" s="2">
+      <c r="AA102" s="2">
         <v>108</v>
       </c>
-      <c r="O102" s="2">
+      <c r="AB102" s="2">
         <v>99</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
         <v>100</v>
       </c>
@@ -6423,7 +10487,7 @@
       </c>
       <c r="G103" s="2">
         <f t="shared" si="17"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H103" s="2">
         <f t="shared" si="18"/>
@@ -6442,16 +10506,55 @@
         <v>10</v>
       </c>
       <c r="L103" s="2">
+        <v>0</v>
+      </c>
+      <c r="M103" s="2">
+        <v>0</v>
+      </c>
+      <c r="N103" s="2">
+        <v>0</v>
+      </c>
+      <c r="O103" s="2">
+        <v>0</v>
+      </c>
+      <c r="P103" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q103" s="2">
+        <v>0</v>
+      </c>
+      <c r="R103" s="2">
         <f t="shared" si="22"/>
-        <v>10</v>
-      </c>
-      <c r="M103" s="2">
+        <v>100</v>
+      </c>
+      <c r="S103" s="2">
+        <v>0</v>
+      </c>
+      <c r="T103" s="2">
+        <v>0</v>
+      </c>
+      <c r="U103" s="2">
+        <v>0</v>
+      </c>
+      <c r="V103" s="2">
+        <v>0</v>
+      </c>
+      <c r="W103" s="2">
+        <v>0</v>
+      </c>
+      <c r="X103" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y103" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z103" s="2">
         <v>1020</v>
       </c>
-      <c r="N103" s="2">
+      <c r="AA103" s="2">
         <v>109</v>
       </c>
-      <c r="O103" s="2">
+      <c r="AB103" s="2">
         <v>100</v>
       </c>
     </row>

--- a/Assets/Excel/Stage.xlsx
+++ b/Assets/Excel/Stage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenBox\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69699C5B-E4DB-456D-BC68-96310EC4FEE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EFD84F9-BF97-42C2-9308-E4E7748A9F39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="48">
   <si>
     <t>Int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -216,6 +216,14 @@
   </si>
   <si>
     <t>PetDecrease</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宠物ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PetID</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -565,7 +573,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB103"/>
+  <dimension ref="A1:AC103"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.25" style="2" customWidth="1"/>
@@ -593,12 +601,13 @@
     <col min="23" max="24" width="11" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="11.75" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="14" style="2" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="17.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9" style="2"/>
+    <col min="27" max="27" width="14" style="2" customWidth="1"/>
+    <col min="28" max="28" width="13.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="17.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -633,27 +642,27 @@
         <v>23</v>
       </c>
       <c r="L1" s="1" t="str">
-        <f>"抗"&amp;F1</f>
+        <f t="shared" ref="L1:Q1" si="0">"抗"&amp;F1</f>
         <v>抗暴击</v>
       </c>
       <c r="M1" s="1" t="str">
-        <f>"抗"&amp;G1</f>
+        <f t="shared" si="0"/>
         <v>抗反击</v>
       </c>
       <c r="N1" s="1" t="str">
-        <f>"抗"&amp;H1</f>
+        <f t="shared" si="0"/>
         <v>抗连击</v>
       </c>
       <c r="O1" s="1" t="str">
-        <f>"抗"&amp;I1</f>
+        <f t="shared" si="0"/>
         <v>抗闪避</v>
       </c>
       <c r="P1" s="1" t="str">
-        <f>"抗"&amp;J1</f>
+        <f t="shared" si="0"/>
         <v>抗击晕</v>
       </c>
       <c r="Q1" s="1" t="str">
-        <f>"抗"&amp;K1</f>
+        <f t="shared" si="0"/>
         <v>抗吸血</v>
       </c>
       <c r="R1" s="1" t="s">
@@ -684,13 +693,16 @@
         <v>24</v>
       </c>
       <c r="AA1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -770,13 +782,16 @@
         <v>25</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AB2" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="AC2" s="2" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -811,27 +826,27 @@
         <v>13</v>
       </c>
       <c r="L3" s="3" t="str">
-        <f>"Anti"&amp;F3</f>
+        <f t="shared" ref="L3:Q3" si="1">"Anti"&amp;F3</f>
         <v>AntiCritRate</v>
       </c>
       <c r="M3" s="3" t="str">
-        <f>"Anti"&amp;G3</f>
+        <f t="shared" si="1"/>
         <v>AntiCounterRate</v>
       </c>
       <c r="N3" s="3" t="str">
-        <f>"Anti"&amp;H3</f>
+        <f t="shared" si="1"/>
         <v>AntiComboRate</v>
       </c>
       <c r="O3" s="3" t="str">
-        <f>"Anti"&amp;I3</f>
+        <f t="shared" si="1"/>
         <v>AntiDodgeRate</v>
       </c>
       <c r="P3" s="3" t="str">
-        <f>"Anti"&amp;J3</f>
+        <f t="shared" si="1"/>
         <v>AntiStunRate</v>
       </c>
       <c r="Q3" s="3" t="str">
-        <f>"Anti"&amp;K3</f>
+        <f t="shared" si="1"/>
         <v>AntiLifeStealRate</v>
       </c>
       <c r="R3" s="2" t="s">
@@ -863,13 +878,16 @@
         <v>26</v>
       </c>
       <c r="AA3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AB3" s="2" t="s">
+      <c r="AC3" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -949,13 +967,16 @@
         <v>1001</v>
       </c>
       <c r="AA4" s="2">
-        <v>10</v>
+        <v>101</v>
       </c>
       <c r="AB4" s="2">
+        <v>10</v>
+      </c>
+      <c r="AC4" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -980,23 +1001,23 @@
         <v>5</v>
       </c>
       <c r="G5" s="2">
-        <f t="shared" ref="G5:K5" si="0">G4</f>
+        <f t="shared" ref="G5:K5" si="2">G4</f>
         <v>10</v>
       </c>
       <c r="H5" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="I5" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="J5" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="K5" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="L5" s="2">
@@ -1046,54 +1067,57 @@
         <v>1002</v>
       </c>
       <c r="AA5" s="2">
+        <v>102</v>
+      </c>
+      <c r="AB5" s="2">
         <v>11</v>
       </c>
-      <c r="AB5" s="2">
+      <c r="AC5" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>3</v>
       </c>
       <c r="B6" s="2">
-        <f t="shared" ref="B6:B69" si="1">B5+5</f>
+        <f t="shared" ref="B6:B69" si="3">B5+5</f>
         <v>40</v>
       </c>
       <c r="C6" s="2">
-        <f t="shared" ref="C6:C69" si="2">C5+3</f>
+        <f t="shared" ref="C6:C69" si="4">C5+3</f>
         <v>11</v>
       </c>
       <c r="D6" s="2">
-        <f t="shared" ref="D6:D69" si="3">D5+120</f>
+        <f t="shared" ref="D6:D69" si="5">D5+120</f>
         <v>1440</v>
       </c>
       <c r="E6" s="2">
-        <f t="shared" ref="E6:E69" si="4">E5+2</f>
+        <f t="shared" ref="E6:E69" si="6">E5+2</f>
         <v>14</v>
       </c>
       <c r="F6" s="2">
-        <f t="shared" ref="F6:F69" si="5">F5</f>
+        <f t="shared" ref="F6:F69" si="7">F5</f>
         <v>5</v>
       </c>
       <c r="G6" s="2">
-        <f t="shared" ref="G6:G69" si="6">G5</f>
+        <f t="shared" ref="G6:G69" si="8">G5</f>
         <v>10</v>
       </c>
       <c r="H6" s="2">
-        <f t="shared" ref="H6:H69" si="7">H5</f>
+        <f t="shared" ref="H6:H69" si="9">H5</f>
         <v>10</v>
       </c>
       <c r="I6" s="2">
-        <f t="shared" ref="I6:I69" si="8">I5</f>
+        <f t="shared" ref="I6:I69" si="10">I5</f>
         <v>10</v>
       </c>
       <c r="J6" s="2">
-        <f t="shared" ref="J6:J69" si="9">J5</f>
+        <f t="shared" ref="J6:J69" si="11">J5</f>
         <v>10</v>
       </c>
       <c r="K6" s="2">
-        <f t="shared" ref="K6:K69" si="10">K5</f>
+        <f t="shared" ref="K6:K69" si="12">K5</f>
         <v>10</v>
       </c>
       <c r="L6" s="2">
@@ -1115,7 +1139,7 @@
         <v>0</v>
       </c>
       <c r="R6" s="2">
-        <f t="shared" ref="R6:R69" si="11">R5</f>
+        <f t="shared" ref="R6:R69" si="13">R5</f>
         <v>100</v>
       </c>
       <c r="S6" s="2">
@@ -1143,54 +1167,57 @@
         <v>1003</v>
       </c>
       <c r="AA6" s="2">
+        <v>103</v>
+      </c>
+      <c r="AB6" s="2">
         <v>12</v>
       </c>
-      <c r="AB6" s="2">
+      <c r="AC6" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>4</v>
       </c>
       <c r="B7" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>45</v>
       </c>
       <c r="C7" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>14</v>
       </c>
       <c r="D7" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1560</v>
       </c>
       <c r="E7" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="F7" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G7" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H7" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I7" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J7" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K7" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L7" s="2">
@@ -1212,7 +1239,7 @@
         <v>0</v>
       </c>
       <c r="R7" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S7" s="2">
@@ -1240,54 +1267,58 @@
         <v>1004</v>
       </c>
       <c r="AA7" s="2">
+        <f>AA4</f>
+        <v>101</v>
+      </c>
+      <c r="AB7" s="2">
         <v>13</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>5</v>
       </c>
       <c r="B8" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
       <c r="C8" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>17</v>
       </c>
       <c r="D8" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1680</v>
       </c>
       <c r="E8" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="F8" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G8" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H8" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I8" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J8" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K8" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L8" s="2">
@@ -1309,7 +1340,7 @@
         <v>0</v>
       </c>
       <c r="R8" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S8" s="2">
@@ -1337,54 +1368,58 @@
         <v>1005</v>
       </c>
       <c r="AA8" s="2">
+        <f t="shared" ref="AA8:AA71" si="14">AA5</f>
+        <v>102</v>
+      </c>
+      <c r="AB8" s="2">
         <v>14</v>
       </c>
-      <c r="AB8" s="2">
+      <c r="AC8" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>6</v>
       </c>
       <c r="B9" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>55</v>
       </c>
       <c r="C9" s="2">
-        <f t="shared" si="2"/>
-        <v>20</v>
-      </c>
-      <c r="D9" s="2">
-        <f t="shared" si="3"/>
-        <v>1800</v>
-      </c>
-      <c r="E9" s="2">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
+      <c r="D9" s="2">
+        <f t="shared" si="5"/>
+        <v>1800</v>
+      </c>
+      <c r="E9" s="2">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
       <c r="F9" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G9" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H9" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I9" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J9" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K9" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L9" s="2">
@@ -1406,7 +1441,7 @@
         <v>0</v>
       </c>
       <c r="R9" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S9" s="2">
@@ -1434,54 +1469,58 @@
         <v>1006</v>
       </c>
       <c r="AA9" s="2">
+        <f t="shared" si="14"/>
+        <v>103</v>
+      </c>
+      <c r="AB9" s="2">
         <v>15</v>
       </c>
-      <c r="AB9" s="2">
+      <c r="AC9" s="2">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>7</v>
       </c>
       <c r="B10" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>60</v>
       </c>
       <c r="C10" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="D10" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1920</v>
       </c>
       <c r="E10" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>22</v>
       </c>
       <c r="F10" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G10" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H10" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I10" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J10" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K10" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L10" s="2">
@@ -1503,7 +1542,7 @@
         <v>0</v>
       </c>
       <c r="R10" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S10" s="2">
@@ -1531,54 +1570,58 @@
         <v>1007</v>
       </c>
       <c r="AA10" s="2">
+        <f t="shared" si="14"/>
+        <v>101</v>
+      </c>
+      <c r="AB10" s="2">
         <v>16</v>
       </c>
-      <c r="AB10" s="2">
+      <c r="AC10" s="2">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>8</v>
       </c>
       <c r="B11" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>65</v>
       </c>
       <c r="C11" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>26</v>
       </c>
       <c r="D11" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2040</v>
       </c>
       <c r="E11" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>24</v>
       </c>
       <c r="F11" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G11" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H11" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I11" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J11" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K11" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L11" s="2">
@@ -1600,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="R11" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S11" s="2">
@@ -1628,54 +1671,58 @@
         <v>1008</v>
       </c>
       <c r="AA11" s="2">
+        <f t="shared" si="14"/>
+        <v>102</v>
+      </c>
+      <c r="AB11" s="2">
         <v>17</v>
       </c>
-      <c r="AB11" s="2">
+      <c r="AC11" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>9</v>
       </c>
       <c r="B12" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>70</v>
       </c>
       <c r="C12" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>29</v>
       </c>
       <c r="D12" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2160</v>
       </c>
       <c r="E12" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>26</v>
       </c>
       <c r="F12" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G12" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H12" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I12" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J12" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K12" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L12" s="2">
@@ -1697,7 +1744,7 @@
         <v>0</v>
       </c>
       <c r="R12" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S12" s="2">
@@ -1725,54 +1772,58 @@
         <v>1009</v>
       </c>
       <c r="AA12" s="2">
+        <f t="shared" si="14"/>
+        <v>103</v>
+      </c>
+      <c r="AB12" s="2">
         <v>18</v>
       </c>
-      <c r="AB12" s="2">
+      <c r="AC12" s="2">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>10</v>
       </c>
       <c r="B13" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>75</v>
       </c>
       <c r="C13" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>32</v>
       </c>
       <c r="D13" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2280</v>
       </c>
       <c r="E13" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>28</v>
       </c>
       <c r="F13" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G13" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H13" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I13" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J13" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K13" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L13" s="2">
@@ -1794,7 +1845,7 @@
         <v>0</v>
       </c>
       <c r="R13" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S13" s="2">
@@ -1822,54 +1873,58 @@
         <v>1010</v>
       </c>
       <c r="AA13" s="2">
+        <f t="shared" si="14"/>
+        <v>101</v>
+      </c>
+      <c r="AB13" s="2">
         <v>19</v>
       </c>
-      <c r="AB13" s="2">
+      <c r="AC13" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>11</v>
       </c>
       <c r="B14" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>80</v>
       </c>
       <c r="C14" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>35</v>
       </c>
       <c r="D14" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2400</v>
       </c>
       <c r="E14" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="F14" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G14" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H14" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I14" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J14" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K14" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L14" s="2">
@@ -1891,7 +1946,7 @@
         <v>0</v>
       </c>
       <c r="R14" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S14" s="2">
@@ -1919,54 +1974,58 @@
         <v>1011</v>
       </c>
       <c r="AA14" s="2">
+        <f t="shared" si="14"/>
+        <v>102</v>
+      </c>
+      <c r="AB14" s="2">
         <v>20</v>
       </c>
-      <c r="AB14" s="2">
+      <c r="AC14" s="2">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>12</v>
       </c>
       <c r="B15" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>85</v>
       </c>
       <c r="C15" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>38</v>
       </c>
       <c r="D15" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2520</v>
       </c>
       <c r="E15" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>32</v>
       </c>
       <c r="F15" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G15" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H15" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I15" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J15" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K15" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L15" s="2">
@@ -1988,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="R15" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S15" s="2">
@@ -2016,54 +2075,58 @@
         <v>1012</v>
       </c>
       <c r="AA15" s="2">
+        <f t="shared" si="14"/>
+        <v>103</v>
+      </c>
+      <c r="AB15" s="2">
         <v>21</v>
       </c>
-      <c r="AB15" s="2">
+      <c r="AC15" s="2">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>13</v>
       </c>
       <c r="B16" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>90</v>
       </c>
       <c r="C16" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>41</v>
       </c>
       <c r="D16" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2640</v>
       </c>
       <c r="E16" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>34</v>
       </c>
       <c r="F16" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G16" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H16" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I16" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J16" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K16" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L16" s="2">
@@ -2085,7 +2148,7 @@
         <v>0</v>
       </c>
       <c r="R16" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S16" s="2">
@@ -2113,54 +2176,58 @@
         <v>1013</v>
       </c>
       <c r="AA16" s="2">
+        <f t="shared" si="14"/>
+        <v>101</v>
+      </c>
+      <c r="AB16" s="2">
         <v>22</v>
       </c>
-      <c r="AB16" s="2">
+      <c r="AC16" s="2">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>14</v>
       </c>
       <c r="B17" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>95</v>
       </c>
       <c r="C17" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>44</v>
       </c>
       <c r="D17" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2760</v>
       </c>
       <c r="E17" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>36</v>
       </c>
       <c r="F17" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G17" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H17" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I17" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J17" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K17" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L17" s="2">
@@ -2182,7 +2249,7 @@
         <v>0</v>
       </c>
       <c r="R17" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S17" s="2">
@@ -2210,54 +2277,58 @@
         <v>1014</v>
       </c>
       <c r="AA17" s="2">
+        <f t="shared" si="14"/>
+        <v>102</v>
+      </c>
+      <c r="AB17" s="2">
         <v>23</v>
       </c>
-      <c r="AB17" s="2">
+      <c r="AC17" s="2">
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>15</v>
       </c>
       <c r="B18" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>100</v>
       </c>
       <c r="C18" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>47</v>
       </c>
       <c r="D18" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2880</v>
       </c>
       <c r="E18" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>38</v>
       </c>
       <c r="F18" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G18" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H18" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I18" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J18" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K18" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L18" s="2">
@@ -2279,7 +2350,7 @@
         <v>0</v>
       </c>
       <c r="R18" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S18" s="2">
@@ -2307,54 +2378,58 @@
         <v>1015</v>
       </c>
       <c r="AA18" s="2">
+        <f t="shared" si="14"/>
+        <v>103</v>
+      </c>
+      <c r="AB18" s="2">
         <v>24</v>
       </c>
-      <c r="AB18" s="2">
+      <c r="AC18" s="2">
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>16</v>
       </c>
       <c r="B19" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>105</v>
       </c>
       <c r="C19" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>50</v>
       </c>
       <c r="D19" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>3000</v>
       </c>
       <c r="E19" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>40</v>
       </c>
       <c r="F19" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G19" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H19" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I19" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J19" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K19" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L19" s="2">
@@ -2376,7 +2451,7 @@
         <v>0</v>
       </c>
       <c r="R19" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S19" s="2">
@@ -2404,54 +2479,58 @@
         <v>1016</v>
       </c>
       <c r="AA19" s="2">
+        <f t="shared" si="14"/>
+        <v>101</v>
+      </c>
+      <c r="AB19" s="2">
         <v>25</v>
       </c>
-      <c r="AB19" s="2">
+      <c r="AC19" s="2">
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>17</v>
       </c>
       <c r="B20" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>110</v>
       </c>
       <c r="C20" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>53</v>
       </c>
       <c r="D20" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>3120</v>
       </c>
       <c r="E20" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>42</v>
       </c>
       <c r="F20" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G20" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H20" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I20" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J20" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K20" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L20" s="2">
@@ -2473,7 +2552,7 @@
         <v>0</v>
       </c>
       <c r="R20" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S20" s="2">
@@ -2501,54 +2580,58 @@
         <v>1017</v>
       </c>
       <c r="AA20" s="2">
+        <f t="shared" si="14"/>
+        <v>102</v>
+      </c>
+      <c r="AB20" s="2">
         <v>26</v>
       </c>
-      <c r="AB20" s="2">
+      <c r="AC20" s="2">
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>18</v>
       </c>
       <c r="B21" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>115</v>
       </c>
       <c r="C21" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>56</v>
       </c>
       <c r="D21" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>3240</v>
       </c>
       <c r="E21" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>44</v>
       </c>
       <c r="F21" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G21" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H21" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I21" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J21" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K21" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L21" s="2">
@@ -2570,7 +2653,7 @@
         <v>0</v>
       </c>
       <c r="R21" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S21" s="2">
@@ -2598,54 +2681,58 @@
         <v>1018</v>
       </c>
       <c r="AA21" s="2">
+        <f t="shared" si="14"/>
+        <v>103</v>
+      </c>
+      <c r="AB21" s="2">
         <v>27</v>
       </c>
-      <c r="AB21" s="2">
+      <c r="AC21" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>19</v>
       </c>
       <c r="B22" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>120</v>
       </c>
       <c r="C22" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>59</v>
       </c>
       <c r="D22" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>3360</v>
       </c>
       <c r="E22" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>46</v>
       </c>
       <c r="F22" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G22" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H22" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I22" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J22" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K22" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L22" s="2">
@@ -2667,7 +2754,7 @@
         <v>0</v>
       </c>
       <c r="R22" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S22" s="2">
@@ -2695,54 +2782,58 @@
         <v>1019</v>
       </c>
       <c r="AA22" s="2">
+        <f t="shared" si="14"/>
+        <v>101</v>
+      </c>
+      <c r="AB22" s="2">
         <v>28</v>
       </c>
-      <c r="AB22" s="2">
+      <c r="AC22" s="2">
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>20</v>
       </c>
       <c r="B23" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>125</v>
       </c>
       <c r="C23" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>62</v>
       </c>
       <c r="D23" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>3480</v>
       </c>
       <c r="E23" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>48</v>
       </c>
       <c r="F23" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G23" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H23" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I23" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J23" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K23" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L23" s="2">
@@ -2764,7 +2855,7 @@
         <v>0</v>
       </c>
       <c r="R23" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S23" s="2">
@@ -2792,54 +2883,58 @@
         <v>1020</v>
       </c>
       <c r="AA23" s="2">
+        <f t="shared" si="14"/>
+        <v>102</v>
+      </c>
+      <c r="AB23" s="2">
         <v>29</v>
       </c>
-      <c r="AB23" s="2">
+      <c r="AC23" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>21</v>
       </c>
       <c r="B24" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>130</v>
       </c>
       <c r="C24" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>65</v>
       </c>
       <c r="D24" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>3600</v>
       </c>
       <c r="E24" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>50</v>
       </c>
       <c r="F24" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G24" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H24" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I24" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J24" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K24" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L24" s="2">
@@ -2861,7 +2956,7 @@
         <v>0</v>
       </c>
       <c r="R24" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S24" s="2">
@@ -2889,54 +2984,58 @@
         <v>1001</v>
       </c>
       <c r="AA24" s="2">
+        <f t="shared" si="14"/>
+        <v>103</v>
+      </c>
+      <c r="AB24" s="2">
         <v>30</v>
       </c>
-      <c r="AB24" s="2">
+      <c r="AC24" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>22</v>
       </c>
       <c r="B25" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>135</v>
       </c>
       <c r="C25" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>68</v>
       </c>
       <c r="D25" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>3720</v>
       </c>
       <c r="E25" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>52</v>
       </c>
       <c r="F25" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G25" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H25" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I25" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J25" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K25" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L25" s="2">
@@ -2958,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="R25" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S25" s="2">
@@ -2986,54 +3085,58 @@
         <v>1002</v>
       </c>
       <c r="AA25" s="2">
+        <f t="shared" si="14"/>
+        <v>101</v>
+      </c>
+      <c r="AB25" s="2">
         <v>31</v>
       </c>
-      <c r="AB25" s="2">
+      <c r="AC25" s="2">
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>23</v>
       </c>
       <c r="B26" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>140</v>
       </c>
       <c r="C26" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>71</v>
       </c>
       <c r="D26" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>3840</v>
       </c>
       <c r="E26" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>54</v>
       </c>
       <c r="F26" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G26" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H26" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I26" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J26" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K26" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L26" s="2">
@@ -3055,7 +3158,7 @@
         <v>0</v>
       </c>
       <c r="R26" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S26" s="2">
@@ -3083,54 +3186,58 @@
         <v>1003</v>
       </c>
       <c r="AA26" s="2">
+        <f t="shared" si="14"/>
+        <v>102</v>
+      </c>
+      <c r="AB26" s="2">
         <v>32</v>
       </c>
-      <c r="AB26" s="2">
+      <c r="AC26" s="2">
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>24</v>
       </c>
       <c r="B27" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>145</v>
       </c>
       <c r="C27" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>74</v>
       </c>
       <c r="D27" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>3960</v>
       </c>
       <c r="E27" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>56</v>
       </c>
       <c r="F27" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G27" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H27" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I27" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J27" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K27" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L27" s="2">
@@ -3152,7 +3259,7 @@
         <v>0</v>
       </c>
       <c r="R27" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S27" s="2">
@@ -3180,54 +3287,58 @@
         <v>1004</v>
       </c>
       <c r="AA27" s="2">
+        <f t="shared" si="14"/>
+        <v>103</v>
+      </c>
+      <c r="AB27" s="2">
         <v>33</v>
       </c>
-      <c r="AB27" s="2">
+      <c r="AC27" s="2">
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>25</v>
       </c>
       <c r="B28" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>150</v>
       </c>
       <c r="C28" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>77</v>
       </c>
       <c r="D28" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>4080</v>
       </c>
       <c r="E28" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>58</v>
       </c>
       <c r="F28" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G28" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H28" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I28" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J28" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K28" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L28" s="2">
@@ -3249,7 +3360,7 @@
         <v>0</v>
       </c>
       <c r="R28" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S28" s="2">
@@ -3277,54 +3388,58 @@
         <v>1005</v>
       </c>
       <c r="AA28" s="2">
+        <f t="shared" si="14"/>
+        <v>101</v>
+      </c>
+      <c r="AB28" s="2">
         <v>34</v>
       </c>
-      <c r="AB28" s="2">
+      <c r="AC28" s="2">
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>26</v>
       </c>
       <c r="B29" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>155</v>
       </c>
       <c r="C29" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>80</v>
       </c>
       <c r="D29" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>4200</v>
       </c>
       <c r="E29" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="F29" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G29" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H29" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I29" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J29" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K29" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L29" s="2">
@@ -3346,7 +3461,7 @@
         <v>0</v>
       </c>
       <c r="R29" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S29" s="2">
@@ -3374,54 +3489,58 @@
         <v>1006</v>
       </c>
       <c r="AA29" s="2">
+        <f t="shared" si="14"/>
+        <v>102</v>
+      </c>
+      <c r="AB29" s="2">
         <v>35</v>
       </c>
-      <c r="AB29" s="2">
+      <c r="AC29" s="2">
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>27</v>
       </c>
       <c r="B30" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>160</v>
       </c>
       <c r="C30" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>83</v>
       </c>
       <c r="D30" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>4320</v>
       </c>
       <c r="E30" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>62</v>
       </c>
       <c r="F30" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G30" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H30" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I30" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J30" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K30" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L30" s="2">
@@ -3443,7 +3562,7 @@
         <v>0</v>
       </c>
       <c r="R30" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S30" s="2">
@@ -3471,54 +3590,58 @@
         <v>1007</v>
       </c>
       <c r="AA30" s="2">
+        <f t="shared" si="14"/>
+        <v>103</v>
+      </c>
+      <c r="AB30" s="2">
         <v>36</v>
       </c>
-      <c r="AB30" s="2">
+      <c r="AC30" s="2">
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>28</v>
       </c>
       <c r="B31" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>165</v>
       </c>
       <c r="C31" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>86</v>
       </c>
       <c r="D31" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>4440</v>
       </c>
       <c r="E31" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>64</v>
       </c>
       <c r="F31" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G31" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H31" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I31" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J31" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K31" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L31" s="2">
@@ -3540,7 +3663,7 @@
         <v>0</v>
       </c>
       <c r="R31" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S31" s="2">
@@ -3568,54 +3691,58 @@
         <v>1008</v>
       </c>
       <c r="AA31" s="2">
+        <f t="shared" si="14"/>
+        <v>101</v>
+      </c>
+      <c r="AB31" s="2">
         <v>37</v>
       </c>
-      <c r="AB31" s="2">
+      <c r="AC31" s="2">
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>29</v>
       </c>
       <c r="B32" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>170</v>
       </c>
       <c r="C32" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>89</v>
       </c>
       <c r="D32" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>4560</v>
       </c>
       <c r="E32" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>66</v>
       </c>
       <c r="F32" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G32" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H32" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I32" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J32" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K32" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L32" s="2">
@@ -3637,7 +3764,7 @@
         <v>0</v>
       </c>
       <c r="R32" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S32" s="2">
@@ -3665,54 +3792,58 @@
         <v>1009</v>
       </c>
       <c r="AA32" s="2">
+        <f t="shared" si="14"/>
+        <v>102</v>
+      </c>
+      <c r="AB32" s="2">
         <v>38</v>
       </c>
-      <c r="AB32" s="2">
+      <c r="AC32" s="2">
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>30</v>
       </c>
       <c r="B33" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>175</v>
       </c>
       <c r="C33" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>92</v>
       </c>
       <c r="D33" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>4680</v>
       </c>
       <c r="E33" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>68</v>
       </c>
       <c r="F33" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G33" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H33" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I33" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J33" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K33" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L33" s="2">
@@ -3734,7 +3865,7 @@
         <v>0</v>
       </c>
       <c r="R33" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S33" s="2">
@@ -3762,54 +3893,58 @@
         <v>1010</v>
       </c>
       <c r="AA33" s="2">
+        <f t="shared" si="14"/>
+        <v>103</v>
+      </c>
+      <c r="AB33" s="2">
         <v>39</v>
       </c>
-      <c r="AB33" s="2">
+      <c r="AC33" s="2">
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>31</v>
       </c>
       <c r="B34" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>180</v>
       </c>
       <c r="C34" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>95</v>
       </c>
       <c r="D34" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>4800</v>
       </c>
       <c r="E34" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>70</v>
       </c>
       <c r="F34" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G34" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H34" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I34" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J34" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K34" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L34" s="2">
@@ -3831,7 +3966,7 @@
         <v>0</v>
       </c>
       <c r="R34" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S34" s="2">
@@ -3859,54 +3994,58 @@
         <v>1011</v>
       </c>
       <c r="AA34" s="2">
+        <f t="shared" si="14"/>
+        <v>101</v>
+      </c>
+      <c r="AB34" s="2">
         <v>40</v>
       </c>
-      <c r="AB34" s="2">
+      <c r="AC34" s="2">
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>32</v>
       </c>
       <c r="B35" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>185</v>
       </c>
       <c r="C35" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>98</v>
       </c>
       <c r="D35" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>4920</v>
       </c>
       <c r="E35" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>72</v>
       </c>
       <c r="F35" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G35" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H35" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I35" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J35" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K35" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L35" s="2">
@@ -3928,7 +4067,7 @@
         <v>0</v>
       </c>
       <c r="R35" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S35" s="2">
@@ -3956,54 +4095,58 @@
         <v>1012</v>
       </c>
       <c r="AA35" s="2">
+        <f t="shared" si="14"/>
+        <v>102</v>
+      </c>
+      <c r="AB35" s="2">
         <v>41</v>
       </c>
-      <c r="AB35" s="2">
+      <c r="AC35" s="2">
         <v>32</v>
       </c>
     </row>
-    <row r="36" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>33</v>
       </c>
       <c r="B36" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>190</v>
       </c>
       <c r="C36" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>101</v>
       </c>
       <c r="D36" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5040</v>
       </c>
       <c r="E36" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>74</v>
       </c>
       <c r="F36" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G36" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H36" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I36" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J36" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K36" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L36" s="2">
@@ -4025,7 +4168,7 @@
         <v>0</v>
       </c>
       <c r="R36" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S36" s="2">
@@ -4053,54 +4196,58 @@
         <v>1013</v>
       </c>
       <c r="AA36" s="2">
+        <f t="shared" si="14"/>
+        <v>103</v>
+      </c>
+      <c r="AB36" s="2">
         <v>42</v>
       </c>
-      <c r="AB36" s="2">
+      <c r="AC36" s="2">
         <v>33</v>
       </c>
     </row>
-    <row r="37" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>34</v>
       </c>
       <c r="B37" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>195</v>
       </c>
       <c r="C37" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>104</v>
       </c>
       <c r="D37" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5160</v>
       </c>
       <c r="E37" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>76</v>
       </c>
       <c r="F37" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G37" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H37" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I37" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J37" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K37" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L37" s="2">
@@ -4122,7 +4269,7 @@
         <v>0</v>
       </c>
       <c r="R37" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S37" s="2">
@@ -4150,54 +4297,58 @@
         <v>1014</v>
       </c>
       <c r="AA37" s="2">
+        <f t="shared" si="14"/>
+        <v>101</v>
+      </c>
+      <c r="AB37" s="2">
         <v>43</v>
       </c>
-      <c r="AB37" s="2">
+      <c r="AC37" s="2">
         <v>34</v>
       </c>
     </row>
-    <row r="38" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>35</v>
       </c>
       <c r="B38" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>200</v>
       </c>
       <c r="C38" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>107</v>
       </c>
       <c r="D38" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5280</v>
       </c>
       <c r="E38" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>78</v>
       </c>
       <c r="F38" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G38" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H38" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I38" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J38" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K38" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L38" s="2">
@@ -4219,7 +4370,7 @@
         <v>0</v>
       </c>
       <c r="R38" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S38" s="2">
@@ -4247,54 +4398,58 @@
         <v>1015</v>
       </c>
       <c r="AA38" s="2">
+        <f t="shared" si="14"/>
+        <v>102</v>
+      </c>
+      <c r="AB38" s="2">
         <v>44</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>36</v>
       </c>
       <c r="B39" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>205</v>
       </c>
       <c r="C39" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>110</v>
       </c>
       <c r="D39" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5400</v>
       </c>
       <c r="E39" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>80</v>
       </c>
       <c r="F39" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G39" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H39" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I39" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J39" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K39" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L39" s="2">
@@ -4316,7 +4471,7 @@
         <v>0</v>
       </c>
       <c r="R39" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S39" s="2">
@@ -4344,54 +4499,58 @@
         <v>1016</v>
       </c>
       <c r="AA39" s="2">
+        <f t="shared" si="14"/>
+        <v>103</v>
+      </c>
+      <c r="AB39" s="2">
         <v>45</v>
       </c>
-      <c r="AB39" s="2">
+      <c r="AC39" s="2">
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>37</v>
       </c>
       <c r="B40" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>210</v>
       </c>
       <c r="C40" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>113</v>
       </c>
       <c r="D40" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5520</v>
       </c>
       <c r="E40" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>82</v>
       </c>
       <c r="F40" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G40" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H40" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I40" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J40" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K40" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L40" s="2">
@@ -4413,7 +4572,7 @@
         <v>0</v>
       </c>
       <c r="R40" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S40" s="2">
@@ -4441,54 +4600,58 @@
         <v>1017</v>
       </c>
       <c r="AA40" s="2">
+        <f t="shared" si="14"/>
+        <v>101</v>
+      </c>
+      <c r="AB40" s="2">
         <v>46</v>
       </c>
-      <c r="AB40" s="2">
+      <c r="AC40" s="2">
         <v>37</v>
       </c>
     </row>
-    <row r="41" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>38</v>
       </c>
       <c r="B41" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>215</v>
       </c>
       <c r="C41" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>116</v>
       </c>
       <c r="D41" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5640</v>
       </c>
       <c r="E41" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>84</v>
       </c>
       <c r="F41" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G41" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H41" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I41" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J41" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K41" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L41" s="2">
@@ -4510,7 +4673,7 @@
         <v>0</v>
       </c>
       <c r="R41" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S41" s="2">
@@ -4538,54 +4701,58 @@
         <v>1018</v>
       </c>
       <c r="AA41" s="2">
+        <f t="shared" si="14"/>
+        <v>102</v>
+      </c>
+      <c r="AB41" s="2">
         <v>47</v>
       </c>
-      <c r="AB41" s="2">
+      <c r="AC41" s="2">
         <v>38</v>
       </c>
     </row>
-    <row r="42" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>39</v>
       </c>
       <c r="B42" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>220</v>
       </c>
       <c r="C42" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>119</v>
       </c>
       <c r="D42" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5760</v>
       </c>
       <c r="E42" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>86</v>
       </c>
       <c r="F42" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G42" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H42" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I42" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J42" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K42" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L42" s="2">
@@ -4607,7 +4774,7 @@
         <v>0</v>
       </c>
       <c r="R42" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S42" s="2">
@@ -4635,54 +4802,58 @@
         <v>1019</v>
       </c>
       <c r="AA42" s="2">
+        <f t="shared" si="14"/>
+        <v>103</v>
+      </c>
+      <c r="AB42" s="2">
         <v>48</v>
       </c>
-      <c r="AB42" s="2">
+      <c r="AC42" s="2">
         <v>39</v>
       </c>
     </row>
-    <row r="43" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>40</v>
       </c>
       <c r="B43" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>225</v>
       </c>
       <c r="C43" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>122</v>
       </c>
       <c r="D43" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5880</v>
       </c>
       <c r="E43" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>88</v>
       </c>
       <c r="F43" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G43" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H43" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I43" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J43" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K43" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L43" s="2">
@@ -4704,7 +4875,7 @@
         <v>0</v>
       </c>
       <c r="R43" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S43" s="2">
@@ -4732,54 +4903,58 @@
         <v>1020</v>
       </c>
       <c r="AA43" s="2">
+        <f t="shared" si="14"/>
+        <v>101</v>
+      </c>
+      <c r="AB43" s="2">
         <v>49</v>
       </c>
-      <c r="AB43" s="2">
+      <c r="AC43" s="2">
         <v>40</v>
       </c>
     </row>
-    <row r="44" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>41</v>
       </c>
       <c r="B44" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>230</v>
       </c>
       <c r="C44" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>125</v>
       </c>
       <c r="D44" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>6000</v>
       </c>
       <c r="E44" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>90</v>
       </c>
       <c r="F44" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G44" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H44" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I44" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J44" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K44" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L44" s="2">
@@ -4801,7 +4976,7 @@
         <v>0</v>
       </c>
       <c r="R44" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S44" s="2">
@@ -4829,54 +5004,58 @@
         <v>1001</v>
       </c>
       <c r="AA44" s="2">
+        <f t="shared" si="14"/>
+        <v>102</v>
+      </c>
+      <c r="AB44" s="2">
         <v>50</v>
       </c>
-      <c r="AB44" s="2">
+      <c r="AC44" s="2">
         <v>41</v>
       </c>
     </row>
-    <row r="45" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>42</v>
       </c>
       <c r="B45" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>235</v>
       </c>
       <c r="C45" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>128</v>
       </c>
       <c r="D45" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>6120</v>
       </c>
       <c r="E45" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>92</v>
       </c>
       <c r="F45" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G45" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H45" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I45" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J45" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K45" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L45" s="2">
@@ -4898,7 +5077,7 @@
         <v>0</v>
       </c>
       <c r="R45" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S45" s="2">
@@ -4926,54 +5105,58 @@
         <v>1002</v>
       </c>
       <c r="AA45" s="2">
+        <f t="shared" si="14"/>
+        <v>103</v>
+      </c>
+      <c r="AB45" s="2">
         <v>51</v>
       </c>
-      <c r="AB45" s="2">
+      <c r="AC45" s="2">
         <v>42</v>
       </c>
     </row>
-    <row r="46" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>43</v>
       </c>
       <c r="B46" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>240</v>
       </c>
       <c r="C46" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>131</v>
       </c>
       <c r="D46" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>6240</v>
       </c>
       <c r="E46" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>94</v>
       </c>
       <c r="F46" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G46" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H46" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I46" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J46" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K46" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L46" s="2">
@@ -4995,7 +5178,7 @@
         <v>0</v>
       </c>
       <c r="R46" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S46" s="2">
@@ -5023,54 +5206,58 @@
         <v>1003</v>
       </c>
       <c r="AA46" s="2">
+        <f t="shared" si="14"/>
+        <v>101</v>
+      </c>
+      <c r="AB46" s="2">
         <v>52</v>
       </c>
-      <c r="AB46" s="2">
+      <c r="AC46" s="2">
         <v>43</v>
       </c>
     </row>
-    <row r="47" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>44</v>
       </c>
       <c r="B47" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>245</v>
       </c>
       <c r="C47" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>134</v>
       </c>
       <c r="D47" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>6360</v>
       </c>
       <c r="E47" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>96</v>
       </c>
       <c r="F47" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G47" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H47" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I47" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J47" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K47" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L47" s="2">
@@ -5092,7 +5279,7 @@
         <v>0</v>
       </c>
       <c r="R47" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S47" s="2">
@@ -5120,54 +5307,58 @@
         <v>1004</v>
       </c>
       <c r="AA47" s="2">
+        <f t="shared" si="14"/>
+        <v>102</v>
+      </c>
+      <c r="AB47" s="2">
         <v>53</v>
       </c>
-      <c r="AB47" s="2">
+      <c r="AC47" s="2">
         <v>44</v>
       </c>
     </row>
-    <row r="48" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <v>45</v>
       </c>
       <c r="B48" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>250</v>
       </c>
       <c r="C48" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>137</v>
       </c>
       <c r="D48" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>6480</v>
       </c>
       <c r="E48" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>98</v>
       </c>
       <c r="F48" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G48" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H48" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I48" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J48" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K48" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L48" s="2">
@@ -5189,7 +5380,7 @@
         <v>0</v>
       </c>
       <c r="R48" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S48" s="2">
@@ -5217,54 +5408,58 @@
         <v>1005</v>
       </c>
       <c r="AA48" s="2">
+        <f t="shared" si="14"/>
+        <v>103</v>
+      </c>
+      <c r="AB48" s="2">
         <v>54</v>
       </c>
-      <c r="AB48" s="2">
+      <c r="AC48" s="2">
         <v>45</v>
       </c>
     </row>
-    <row r="49" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <v>46</v>
       </c>
       <c r="B49" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>255</v>
       </c>
       <c r="C49" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>140</v>
       </c>
       <c r="D49" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>6600</v>
       </c>
       <c r="E49" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>100</v>
       </c>
       <c r="F49" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G49" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H49" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I49" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J49" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K49" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L49" s="2">
@@ -5286,7 +5481,7 @@
         <v>0</v>
       </c>
       <c r="R49" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S49" s="2">
@@ -5314,54 +5509,58 @@
         <v>1006</v>
       </c>
       <c r="AA49" s="2">
+        <f t="shared" si="14"/>
+        <v>101</v>
+      </c>
+      <c r="AB49" s="2">
         <v>55</v>
       </c>
-      <c r="AB49" s="2">
+      <c r="AC49" s="2">
         <v>46</v>
       </c>
     </row>
-    <row r="50" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
         <v>47</v>
       </c>
       <c r="B50" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>260</v>
       </c>
       <c r="C50" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>143</v>
       </c>
       <c r="D50" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>6720</v>
       </c>
       <c r="E50" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>102</v>
       </c>
       <c r="F50" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G50" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H50" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I50" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J50" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K50" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L50" s="2">
@@ -5383,7 +5582,7 @@
         <v>0</v>
       </c>
       <c r="R50" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S50" s="2">
@@ -5411,54 +5610,58 @@
         <v>1007</v>
       </c>
       <c r="AA50" s="2">
+        <f t="shared" si="14"/>
+        <v>102</v>
+      </c>
+      <c r="AB50" s="2">
         <v>56</v>
       </c>
-      <c r="AB50" s="2">
+      <c r="AC50" s="2">
         <v>47</v>
       </c>
     </row>
-    <row r="51" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
         <v>48</v>
       </c>
       <c r="B51" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>265</v>
       </c>
       <c r="C51" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>146</v>
       </c>
       <c r="D51" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>6840</v>
       </c>
       <c r="E51" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>104</v>
       </c>
       <c r="F51" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G51" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H51" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I51" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J51" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K51" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L51" s="2">
@@ -5480,7 +5683,7 @@
         <v>0</v>
       </c>
       <c r="R51" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S51" s="2">
@@ -5508,54 +5711,58 @@
         <v>1008</v>
       </c>
       <c r="AA51" s="2">
+        <f t="shared" si="14"/>
+        <v>103</v>
+      </c>
+      <c r="AB51" s="2">
         <v>57</v>
       </c>
-      <c r="AB51" s="2">
+      <c r="AC51" s="2">
         <v>48</v>
       </c>
     </row>
-    <row r="52" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
         <v>49</v>
       </c>
       <c r="B52" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>270</v>
       </c>
       <c r="C52" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>149</v>
       </c>
       <c r="D52" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>6960</v>
       </c>
       <c r="E52" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>106</v>
       </c>
       <c r="F52" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G52" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H52" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I52" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J52" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K52" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L52" s="2">
@@ -5577,7 +5784,7 @@
         <v>0</v>
       </c>
       <c r="R52" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S52" s="2">
@@ -5605,54 +5812,58 @@
         <v>1009</v>
       </c>
       <c r="AA52" s="2">
+        <f t="shared" si="14"/>
+        <v>101</v>
+      </c>
+      <c r="AB52" s="2">
         <v>58</v>
       </c>
-      <c r="AB52" s="2">
+      <c r="AC52" s="2">
         <v>49</v>
       </c>
     </row>
-    <row r="53" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
         <v>50</v>
       </c>
       <c r="B53" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>275</v>
       </c>
       <c r="C53" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>152</v>
       </c>
       <c r="D53" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>7080</v>
       </c>
       <c r="E53" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>108</v>
       </c>
       <c r="F53" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G53" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H53" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I53" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J53" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K53" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L53" s="2">
@@ -5674,7 +5885,7 @@
         <v>0</v>
       </c>
       <c r="R53" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S53" s="2">
@@ -5702,54 +5913,58 @@
         <v>1010</v>
       </c>
       <c r="AA53" s="2">
+        <f t="shared" si="14"/>
+        <v>102</v>
+      </c>
+      <c r="AB53" s="2">
         <v>59</v>
       </c>
-      <c r="AB53" s="2">
+      <c r="AC53" s="2">
         <v>50</v>
       </c>
     </row>
-    <row r="54" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
         <v>51</v>
       </c>
       <c r="B54" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>280</v>
       </c>
       <c r="C54" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>155</v>
       </c>
       <c r="D54" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>7200</v>
       </c>
       <c r="E54" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>110</v>
       </c>
       <c r="F54" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G54" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H54" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I54" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J54" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K54" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L54" s="2">
@@ -5771,7 +5986,7 @@
         <v>0</v>
       </c>
       <c r="R54" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S54" s="2">
@@ -5799,54 +6014,58 @@
         <v>1011</v>
       </c>
       <c r="AA54" s="2">
+        <f t="shared" si="14"/>
+        <v>103</v>
+      </c>
+      <c r="AB54" s="2">
         <v>60</v>
       </c>
-      <c r="AB54" s="2">
+      <c r="AC54" s="2">
         <v>51</v>
       </c>
     </row>
-    <row r="55" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
         <v>52</v>
       </c>
       <c r="B55" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>285</v>
       </c>
       <c r="C55" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>158</v>
       </c>
       <c r="D55" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>7320</v>
       </c>
       <c r="E55" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>112</v>
       </c>
       <c r="F55" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G55" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H55" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I55" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J55" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K55" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L55" s="2">
@@ -5868,7 +6087,7 @@
         <v>0</v>
       </c>
       <c r="R55" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S55" s="2">
@@ -5896,54 +6115,58 @@
         <v>1012</v>
       </c>
       <c r="AA55" s="2">
+        <f t="shared" si="14"/>
+        <v>101</v>
+      </c>
+      <c r="AB55" s="2">
         <v>61</v>
       </c>
-      <c r="AB55" s="2">
+      <c r="AC55" s="2">
         <v>52</v>
       </c>
     </row>
-    <row r="56" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
         <v>53</v>
       </c>
       <c r="B56" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>290</v>
       </c>
       <c r="C56" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>161</v>
       </c>
       <c r="D56" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>7440</v>
       </c>
       <c r="E56" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>114</v>
       </c>
       <c r="F56" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G56" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H56" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I56" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J56" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K56" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L56" s="2">
@@ -5965,7 +6188,7 @@
         <v>0</v>
       </c>
       <c r="R56" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S56" s="2">
@@ -5993,54 +6216,58 @@
         <v>1013</v>
       </c>
       <c r="AA56" s="2">
+        <f t="shared" si="14"/>
+        <v>102</v>
+      </c>
+      <c r="AB56" s="2">
         <v>62</v>
       </c>
-      <c r="AB56" s="2">
+      <c r="AC56" s="2">
         <v>53</v>
       </c>
     </row>
-    <row r="57" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
         <v>54</v>
       </c>
       <c r="B57" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>295</v>
       </c>
       <c r="C57" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>164</v>
       </c>
       <c r="D57" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>7560</v>
       </c>
       <c r="E57" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>116</v>
       </c>
       <c r="F57" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G57" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H57" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I57" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J57" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K57" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L57" s="2">
@@ -6062,7 +6289,7 @@
         <v>0</v>
       </c>
       <c r="R57" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S57" s="2">
@@ -6090,54 +6317,58 @@
         <v>1014</v>
       </c>
       <c r="AA57" s="2">
+        <f t="shared" si="14"/>
+        <v>103</v>
+      </c>
+      <c r="AB57" s="2">
         <v>63</v>
       </c>
-      <c r="AB57" s="2">
+      <c r="AC57" s="2">
         <v>54</v>
       </c>
     </row>
-    <row r="58" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
         <v>55</v>
       </c>
       <c r="B58" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>300</v>
       </c>
       <c r="C58" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>167</v>
       </c>
       <c r="D58" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>7680</v>
       </c>
       <c r="E58" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>118</v>
       </c>
       <c r="F58" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G58" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H58" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I58" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J58" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K58" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L58" s="2">
@@ -6159,7 +6390,7 @@
         <v>0</v>
       </c>
       <c r="R58" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S58" s="2">
@@ -6187,54 +6418,58 @@
         <v>1015</v>
       </c>
       <c r="AA58" s="2">
+        <f t="shared" si="14"/>
+        <v>101</v>
+      </c>
+      <c r="AB58" s="2">
         <v>64</v>
       </c>
-      <c r="AB58" s="2">
+      <c r="AC58" s="2">
         <v>55</v>
       </c>
     </row>
-    <row r="59" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
         <v>56</v>
       </c>
       <c r="B59" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>305</v>
       </c>
       <c r="C59" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>170</v>
       </c>
       <c r="D59" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>7800</v>
       </c>
       <c r="E59" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>120</v>
       </c>
       <c r="F59" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G59" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H59" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I59" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J59" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K59" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L59" s="2">
@@ -6256,7 +6491,7 @@
         <v>0</v>
       </c>
       <c r="R59" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S59" s="2">
@@ -6284,54 +6519,58 @@
         <v>1016</v>
       </c>
       <c r="AA59" s="2">
+        <f t="shared" si="14"/>
+        <v>102</v>
+      </c>
+      <c r="AB59" s="2">
         <v>65</v>
       </c>
-      <c r="AB59" s="2">
+      <c r="AC59" s="2">
         <v>56</v>
       </c>
     </row>
-    <row r="60" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
         <v>57</v>
       </c>
       <c r="B60" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>310</v>
       </c>
       <c r="C60" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>173</v>
       </c>
       <c r="D60" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>7920</v>
       </c>
       <c r="E60" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>122</v>
       </c>
       <c r="F60" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G60" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H60" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I60" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J60" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K60" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L60" s="2">
@@ -6353,7 +6592,7 @@
         <v>0</v>
       </c>
       <c r="R60" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S60" s="2">
@@ -6381,54 +6620,58 @@
         <v>1017</v>
       </c>
       <c r="AA60" s="2">
+        <f t="shared" si="14"/>
+        <v>103</v>
+      </c>
+      <c r="AB60" s="2">
         <v>66</v>
       </c>
-      <c r="AB60" s="2">
+      <c r="AC60" s="2">
         <v>57</v>
       </c>
     </row>
-    <row r="61" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
         <v>58</v>
       </c>
       <c r="B61" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>315</v>
       </c>
       <c r="C61" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>176</v>
       </c>
       <c r="D61" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>8040</v>
       </c>
       <c r="E61" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>124</v>
       </c>
       <c r="F61" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G61" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H61" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I61" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J61" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K61" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L61" s="2">
@@ -6450,7 +6693,7 @@
         <v>0</v>
       </c>
       <c r="R61" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S61" s="2">
@@ -6478,54 +6721,58 @@
         <v>1018</v>
       </c>
       <c r="AA61" s="2">
+        <f t="shared" si="14"/>
+        <v>101</v>
+      </c>
+      <c r="AB61" s="2">
         <v>67</v>
       </c>
-      <c r="AB61" s="2">
+      <c r="AC61" s="2">
         <v>58</v>
       </c>
     </row>
-    <row r="62" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
         <v>59</v>
       </c>
       <c r="B62" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>320</v>
       </c>
       <c r="C62" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>179</v>
       </c>
       <c r="D62" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>8160</v>
       </c>
       <c r="E62" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>126</v>
       </c>
       <c r="F62" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G62" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H62" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I62" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J62" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K62" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L62" s="2">
@@ -6547,7 +6794,7 @@
         <v>0</v>
       </c>
       <c r="R62" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S62" s="2">
@@ -6575,54 +6822,58 @@
         <v>1019</v>
       </c>
       <c r="AA62" s="2">
+        <f t="shared" si="14"/>
+        <v>102</v>
+      </c>
+      <c r="AB62" s="2">
         <v>68</v>
       </c>
-      <c r="AB62" s="2">
+      <c r="AC62" s="2">
         <v>59</v>
       </c>
     </row>
-    <row r="63" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
         <v>60</v>
       </c>
       <c r="B63" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>325</v>
       </c>
       <c r="C63" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>182</v>
       </c>
       <c r="D63" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>8280</v>
       </c>
       <c r="E63" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>128</v>
       </c>
       <c r="F63" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G63" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H63" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I63" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J63" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K63" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L63" s="2">
@@ -6644,7 +6895,7 @@
         <v>0</v>
       </c>
       <c r="R63" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S63" s="2">
@@ -6672,54 +6923,58 @@
         <v>1020</v>
       </c>
       <c r="AA63" s="2">
+        <f t="shared" si="14"/>
+        <v>103</v>
+      </c>
+      <c r="AB63" s="2">
         <v>69</v>
       </c>
-      <c r="AB63" s="2">
+      <c r="AC63" s="2">
         <v>60</v>
       </c>
     </row>
-    <row r="64" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
         <v>61</v>
       </c>
       <c r="B64" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>330</v>
       </c>
       <c r="C64" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>185</v>
       </c>
       <c r="D64" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>8400</v>
       </c>
       <c r="E64" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>130</v>
       </c>
       <c r="F64" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G64" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H64" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I64" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J64" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K64" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L64" s="2">
@@ -6741,7 +6996,7 @@
         <v>0</v>
       </c>
       <c r="R64" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S64" s="2">
@@ -6769,54 +7024,58 @@
         <v>1001</v>
       </c>
       <c r="AA64" s="2">
+        <f t="shared" si="14"/>
+        <v>101</v>
+      </c>
+      <c r="AB64" s="2">
         <v>70</v>
       </c>
-      <c r="AB64" s="2">
+      <c r="AC64" s="2">
         <v>61</v>
       </c>
     </row>
-    <row r="65" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
         <v>62</v>
       </c>
       <c r="B65" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>335</v>
       </c>
       <c r="C65" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>188</v>
       </c>
       <c r="D65" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>8520</v>
       </c>
       <c r="E65" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>132</v>
       </c>
       <c r="F65" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G65" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H65" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I65" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J65" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K65" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L65" s="2">
@@ -6838,7 +7097,7 @@
         <v>0</v>
       </c>
       <c r="R65" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S65" s="2">
@@ -6866,54 +7125,58 @@
         <v>1002</v>
       </c>
       <c r="AA65" s="2">
+        <f t="shared" si="14"/>
+        <v>102</v>
+      </c>
+      <c r="AB65" s="2">
         <v>71</v>
       </c>
-      <c r="AB65" s="2">
+      <c r="AC65" s="2">
         <v>62</v>
       </c>
     </row>
-    <row r="66" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
         <v>63</v>
       </c>
       <c r="B66" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>340</v>
       </c>
       <c r="C66" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>191</v>
       </c>
       <c r="D66" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>8640</v>
       </c>
       <c r="E66" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>134</v>
       </c>
       <c r="F66" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G66" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H66" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I66" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J66" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K66" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L66" s="2">
@@ -6935,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="R66" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S66" s="2">
@@ -6963,54 +7226,58 @@
         <v>1003</v>
       </c>
       <c r="AA66" s="2">
+        <f t="shared" si="14"/>
+        <v>103</v>
+      </c>
+      <c r="AB66" s="2">
         <v>72</v>
       </c>
-      <c r="AB66" s="2">
+      <c r="AC66" s="2">
         <v>63</v>
       </c>
     </row>
-    <row r="67" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
         <v>64</v>
       </c>
       <c r="B67" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>345</v>
       </c>
       <c r="C67" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>194</v>
       </c>
       <c r="D67" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>8760</v>
       </c>
       <c r="E67" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>136</v>
       </c>
       <c r="F67" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G67" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H67" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I67" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J67" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K67" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L67" s="2">
@@ -7032,7 +7299,7 @@
         <v>0</v>
       </c>
       <c r="R67" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S67" s="2">
@@ -7060,54 +7327,58 @@
         <v>1004</v>
       </c>
       <c r="AA67" s="2">
+        <f t="shared" si="14"/>
+        <v>101</v>
+      </c>
+      <c r="AB67" s="2">
         <v>73</v>
       </c>
-      <c r="AB67" s="2">
+      <c r="AC67" s="2">
         <v>64</v>
       </c>
     </row>
-    <row r="68" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
         <v>65</v>
       </c>
       <c r="B68" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>350</v>
       </c>
       <c r="C68" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>197</v>
       </c>
       <c r="D68" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>8880</v>
       </c>
       <c r="E68" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>138</v>
       </c>
       <c r="F68" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G68" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H68" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I68" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J68" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K68" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L68" s="2">
@@ -7129,7 +7400,7 @@
         <v>0</v>
       </c>
       <c r="R68" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S68" s="2">
@@ -7157,54 +7428,58 @@
         <v>1005</v>
       </c>
       <c r="AA68" s="2">
+        <f t="shared" si="14"/>
+        <v>102</v>
+      </c>
+      <c r="AB68" s="2">
         <v>74</v>
       </c>
-      <c r="AB68" s="2">
+      <c r="AC68" s="2">
         <v>65</v>
       </c>
     </row>
-    <row r="69" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
         <v>66</v>
       </c>
       <c r="B69" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>355</v>
       </c>
       <c r="C69" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>200</v>
       </c>
       <c r="D69" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>9000</v>
       </c>
       <c r="E69" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>140</v>
       </c>
       <c r="F69" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G69" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="H69" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I69" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J69" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K69" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="L69" s="2">
@@ -7226,7 +7501,7 @@
         <v>0</v>
       </c>
       <c r="R69" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S69" s="2">
@@ -7254,54 +7529,58 @@
         <v>1006</v>
       </c>
       <c r="AA69" s="2">
+        <f t="shared" si="14"/>
+        <v>103</v>
+      </c>
+      <c r="AB69" s="2">
         <v>75</v>
       </c>
-      <c r="AB69" s="2">
+      <c r="AC69" s="2">
         <v>66</v>
       </c>
     </row>
-    <row r="70" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
         <v>67</v>
       </c>
       <c r="B70" s="2">
-        <f t="shared" ref="B70:B103" si="12">B69+5</f>
+        <f t="shared" ref="B70:B103" si="15">B69+5</f>
         <v>360</v>
       </c>
       <c r="C70" s="2">
-        <f t="shared" ref="C70:C103" si="13">C69+3</f>
+        <f t="shared" ref="C70:C103" si="16">C69+3</f>
         <v>203</v>
       </c>
       <c r="D70" s="2">
-        <f t="shared" ref="D70:D103" si="14">D69+120</f>
+        <f t="shared" ref="D70:D103" si="17">D69+120</f>
         <v>9120</v>
       </c>
       <c r="E70" s="2">
-        <f t="shared" ref="E70:E103" si="15">E69+2</f>
+        <f t="shared" ref="E70:E103" si="18">E69+2</f>
         <v>142</v>
       </c>
       <c r="F70" s="2">
-        <f t="shared" ref="F70:F103" si="16">F69</f>
+        <f t="shared" ref="F70:F103" si="19">F69</f>
         <v>5</v>
       </c>
       <c r="G70" s="2">
-        <f t="shared" ref="G70:G103" si="17">G69</f>
+        <f t="shared" ref="G70:G103" si="20">G69</f>
         <v>10</v>
       </c>
       <c r="H70" s="2">
-        <f t="shared" ref="H70:H103" si="18">H69</f>
+        <f t="shared" ref="H70:H103" si="21">H69</f>
         <v>10</v>
       </c>
       <c r="I70" s="2">
-        <f t="shared" ref="I70:I103" si="19">I69</f>
+        <f t="shared" ref="I70:I103" si="22">I69</f>
         <v>10</v>
       </c>
       <c r="J70" s="2">
-        <f t="shared" ref="J70:J103" si="20">J69</f>
+        <f t="shared" ref="J70:J103" si="23">J69</f>
         <v>10</v>
       </c>
       <c r="K70" s="2">
-        <f t="shared" ref="K70:K103" si="21">K69</f>
+        <f t="shared" ref="K70:K103" si="24">K69</f>
         <v>10</v>
       </c>
       <c r="L70" s="2">
@@ -7323,7 +7602,7 @@
         <v>0</v>
       </c>
       <c r="R70" s="2">
-        <f t="shared" ref="R70:R103" si="22">R69</f>
+        <f t="shared" ref="R70:R103" si="25">R69</f>
         <v>100</v>
       </c>
       <c r="S70" s="2">
@@ -7351,54 +7630,58 @@
         <v>1007</v>
       </c>
       <c r="AA70" s="2">
+        <f t="shared" si="14"/>
+        <v>101</v>
+      </c>
+      <c r="AB70" s="2">
         <v>76</v>
       </c>
-      <c r="AB70" s="2">
+      <c r="AC70" s="2">
         <v>67</v>
       </c>
     </row>
-    <row r="71" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
         <v>68</v>
       </c>
       <c r="B71" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>365</v>
       </c>
       <c r="C71" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>206</v>
       </c>
       <c r="D71" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>9240</v>
       </c>
       <c r="E71" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>144</v>
       </c>
       <c r="F71" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="G71" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>10</v>
       </c>
       <c r="H71" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>10</v>
       </c>
       <c r="I71" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>10</v>
       </c>
       <c r="J71" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>10</v>
       </c>
       <c r="K71" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>10</v>
       </c>
       <c r="L71" s="2">
@@ -7420,7 +7703,7 @@
         <v>0</v>
       </c>
       <c r="R71" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>100</v>
       </c>
       <c r="S71" s="2">
@@ -7448,54 +7731,58 @@
         <v>1008</v>
       </c>
       <c r="AA71" s="2">
+        <f t="shared" si="14"/>
+        <v>102</v>
+      </c>
+      <c r="AB71" s="2">
         <v>77</v>
       </c>
-      <c r="AB71" s="2">
+      <c r="AC71" s="2">
         <v>68</v>
       </c>
     </row>
-    <row r="72" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
         <v>69</v>
       </c>
       <c r="B72" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>370</v>
       </c>
       <c r="C72" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>209</v>
       </c>
       <c r="D72" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>9360</v>
       </c>
       <c r="E72" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>146</v>
       </c>
       <c r="F72" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="G72" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>10</v>
       </c>
       <c r="H72" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>10</v>
       </c>
       <c r="I72" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>10</v>
       </c>
       <c r="J72" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>10</v>
       </c>
       <c r="K72" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>10</v>
       </c>
       <c r="L72" s="2">
@@ -7517,7 +7804,7 @@
         <v>0</v>
       </c>
       <c r="R72" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>100</v>
       </c>
       <c r="S72" s="2">
@@ -7545,54 +7832,58 @@
         <v>1009</v>
       </c>
       <c r="AA72" s="2">
+        <f t="shared" ref="AA72:AA103" si="26">AA69</f>
+        <v>103</v>
+      </c>
+      <c r="AB72" s="2">
         <v>78</v>
       </c>
-      <c r="AB72" s="2">
+      <c r="AC72" s="2">
         <v>69</v>
       </c>
     </row>
-    <row r="73" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
         <v>70</v>
       </c>
       <c r="B73" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>375</v>
       </c>
       <c r="C73" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>212</v>
       </c>
       <c r="D73" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>9480</v>
       </c>
       <c r="E73" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>148</v>
       </c>
       <c r="F73" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="G73" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>10</v>
       </c>
       <c r="H73" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>10</v>
       </c>
       <c r="I73" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>10</v>
       </c>
       <c r="J73" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>10</v>
       </c>
       <c r="K73" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>10</v>
       </c>
       <c r="L73" s="2">
@@ -7614,7 +7905,7 @@
         <v>0</v>
       </c>
       <c r="R73" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>100</v>
       </c>
       <c r="S73" s="2">
@@ -7642,54 +7933,58 @@
         <v>1010</v>
       </c>
       <c r="AA73" s="2">
+        <f t="shared" si="26"/>
+        <v>101</v>
+      </c>
+      <c r="AB73" s="2">
         <v>79</v>
       </c>
-      <c r="AB73" s="2">
+      <c r="AC73" s="2">
         <v>70</v>
       </c>
     </row>
-    <row r="74" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
         <v>71</v>
       </c>
       <c r="B74" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>380</v>
       </c>
       <c r="C74" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>215</v>
       </c>
       <c r="D74" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>9600</v>
       </c>
       <c r="E74" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>150</v>
       </c>
       <c r="F74" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="G74" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>10</v>
       </c>
       <c r="H74" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>10</v>
       </c>
       <c r="I74" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>10</v>
       </c>
       <c r="J74" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>10</v>
       </c>
       <c r="K74" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>10</v>
       </c>
       <c r="L74" s="2">
@@ -7711,7 +8006,7 @@
         <v>0</v>
       </c>
       <c r="R74" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>100</v>
       </c>
       <c r="S74" s="2">
@@ -7739,54 +8034,58 @@
         <v>1011</v>
       </c>
       <c r="AA74" s="2">
+        <f t="shared" si="26"/>
+        <v>102</v>
+      </c>
+      <c r="AB74" s="2">
         <v>80</v>
       </c>
-      <c r="AB74" s="2">
+      <c r="AC74" s="2">
         <v>71</v>
       </c>
     </row>
-    <row r="75" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
         <v>72</v>
       </c>
       <c r="B75" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>385</v>
       </c>
       <c r="C75" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>218</v>
       </c>
       <c r="D75" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>9720</v>
       </c>
       <c r="E75" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>152</v>
       </c>
       <c r="F75" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="G75" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>10</v>
       </c>
       <c r="H75" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>10</v>
       </c>
       <c r="I75" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>10</v>
       </c>
       <c r="J75" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>10</v>
       </c>
       <c r="K75" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>10</v>
       </c>
       <c r="L75" s="2">
@@ -7808,7 +8107,7 @@
         <v>0</v>
       </c>
       <c r="R75" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>100</v>
       </c>
       <c r="S75" s="2">
@@ -7836,54 +8135,58 @@
         <v>1012</v>
       </c>
       <c r="AA75" s="2">
+        <f t="shared" si="26"/>
+        <v>103</v>
+      </c>
+      <c r="AB75" s="2">
         <v>81</v>
       </c>
-      <c r="AB75" s="2">
+      <c r="AC75" s="2">
         <v>72</v>
       </c>
     </row>
-    <row r="76" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
         <v>73</v>
       </c>
       <c r="B76" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>390</v>
       </c>
       <c r="C76" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>221</v>
       </c>
       <c r="D76" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>9840</v>
       </c>
       <c r="E76" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>154</v>
       </c>
       <c r="F76" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="G76" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>10</v>
       </c>
       <c r="H76" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>10</v>
       </c>
       <c r="I76" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>10</v>
       </c>
       <c r="J76" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>10</v>
       </c>
       <c r="K76" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>10</v>
       </c>
       <c r="L76" s="2">
@@ -7905,7 +8208,7 @@
         <v>0</v>
       </c>
       <c r="R76" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>100</v>
       </c>
       <c r="S76" s="2">
@@ -7933,54 +8236,58 @@
         <v>1013</v>
       </c>
       <c r="AA76" s="2">
+        <f t="shared" si="26"/>
+        <v>101</v>
+      </c>
+      <c r="AB76" s="2">
         <v>82</v>
       </c>
-      <c r="AB76" s="2">
+      <c r="AC76" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="77" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
         <v>74</v>
       </c>
       <c r="B77" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>395</v>
       </c>
       <c r="C77" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>224</v>
       </c>
       <c r="D77" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>9960</v>
       </c>
       <c r="E77" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>156</v>
       </c>
       <c r="F77" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="G77" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>10</v>
       </c>
       <c r="H77" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>10</v>
       </c>
       <c r="I77" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>10</v>
       </c>
       <c r="J77" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>10</v>
       </c>
       <c r="K77" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>10</v>
       </c>
       <c r="L77" s="2">
@@ -8002,7 +8309,7 @@
         <v>0</v>
       </c>
       <c r="R77" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>100</v>
       </c>
       <c r="S77" s="2">
@@ -8030,54 +8337,58 @@
         <v>1014</v>
       </c>
       <c r="AA77" s="2">
+        <f t="shared" si="26"/>
+        <v>102</v>
+      </c>
+      <c r="AB77" s="2">
         <v>83</v>
       </c>
-      <c r="AB77" s="2">
+      <c r="AC77" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="78" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
         <v>75</v>
       </c>
       <c r="B78" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>400</v>
       </c>
       <c r="C78" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>227</v>
       </c>
       <c r="D78" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>10080</v>
       </c>
       <c r="E78" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>158</v>
       </c>
       <c r="F78" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="G78" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>10</v>
       </c>
       <c r="H78" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>10</v>
       </c>
       <c r="I78" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>10</v>
       </c>
       <c r="J78" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>10</v>
       </c>
       <c r="K78" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>10</v>
       </c>
       <c r="L78" s="2">
@@ -8099,7 +8410,7 @@
         <v>0</v>
       </c>
       <c r="R78" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>100</v>
       </c>
       <c r="S78" s="2">
@@ -8127,54 +8438,58 @@
         <v>1015</v>
       </c>
       <c r="AA78" s="2">
+        <f t="shared" si="26"/>
+        <v>103</v>
+      </c>
+      <c r="AB78" s="2">
         <v>84</v>
       </c>
-      <c r="AB78" s="2">
+      <c r="AC78" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="79" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
         <v>76</v>
       </c>
       <c r="B79" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>405</v>
       </c>
       <c r="C79" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>230</v>
       </c>
       <c r="D79" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>10200</v>
       </c>
       <c r="E79" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>160</v>
       </c>
       <c r="F79" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="G79" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>10</v>
       </c>
       <c r="H79" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>10</v>
       </c>
       <c r="I79" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>10</v>
       </c>
       <c r="J79" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>10</v>
       </c>
       <c r="K79" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>10</v>
       </c>
       <c r="L79" s="2">
@@ -8196,7 +8511,7 @@
         <v>0</v>
       </c>
       <c r="R79" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>100</v>
       </c>
       <c r="S79" s="2">
@@ -8224,54 +8539,58 @@
         <v>1016</v>
       </c>
       <c r="AA79" s="2">
+        <f t="shared" si="26"/>
+        <v>101</v>
+      </c>
+      <c r="AB79" s="2">
         <v>85</v>
       </c>
-      <c r="AB79" s="2">
+      <c r="AC79" s="2">
         <v>76</v>
       </c>
     </row>
-    <row r="80" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
         <v>77</v>
       </c>
       <c r="B80" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>410</v>
       </c>
       <c r="C80" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>233</v>
       </c>
       <c r="D80" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>10320</v>
       </c>
       <c r="E80" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>162</v>
       </c>
       <c r="F80" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="G80" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>10</v>
       </c>
       <c r="H80" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>10</v>
       </c>
       <c r="I80" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>10</v>
       </c>
       <c r="J80" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>10</v>
       </c>
       <c r="K80" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>10</v>
       </c>
       <c r="L80" s="2">
@@ -8293,7 +8612,7 @@
         <v>0</v>
       </c>
       <c r="R80" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>100</v>
       </c>
       <c r="S80" s="2">
@@ -8321,54 +8640,58 @@
         <v>1017</v>
       </c>
       <c r="AA80" s="2">
+        <f t="shared" si="26"/>
+        <v>102</v>
+      </c>
+      <c r="AB80" s="2">
         <v>86</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="81" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
         <v>78</v>
       </c>
       <c r="B81" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>415</v>
       </c>
       <c r="C81" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>236</v>
       </c>
       <c r="D81" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>10440</v>
       </c>
       <c r="E81" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>164</v>
       </c>
       <c r="F81" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="G81" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>10</v>
       </c>
       <c r="H81" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>10</v>
       </c>
       <c r="I81" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>10</v>
       </c>
       <c r="J81" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>10</v>
       </c>
       <c r="K81" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>10</v>
       </c>
       <c r="L81" s="2">
@@ -8390,7 +8713,7 @@
         <v>0</v>
       </c>
       <c r="R81" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>100</v>
       </c>
       <c r="S81" s="2">
@@ -8418,54 +8741,58 @@
         <v>1018</v>
       </c>
       <c r="AA81" s="2">
+        <f t="shared" si="26"/>
+        <v>103</v>
+      </c>
+      <c r="AB81" s="2">
         <v>87</v>
       </c>
-      <c r="AB81" s="2">
+      <c r="AC81" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="82" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
         <v>79</v>
       </c>
       <c r="B82" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>420</v>
       </c>
       <c r="C82" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>239</v>
       </c>
       <c r="D82" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>10560</v>
       </c>
       <c r="E82" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>166</v>
       </c>
       <c r="F82" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="G82" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>10</v>
       </c>
       <c r="H82" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>10</v>
       </c>
       <c r="I82" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>10</v>
       </c>
       <c r="J82" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>10</v>
       </c>
       <c r="K82" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>10</v>
       </c>
       <c r="L82" s="2">
@@ -8487,7 +8814,7 @@
         <v>0</v>
       </c>
       <c r="R82" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>100</v>
       </c>
       <c r="S82" s="2">
@@ -8515,54 +8842,58 @@
         <v>1019</v>
       </c>
       <c r="AA82" s="2">
+        <f t="shared" si="26"/>
+        <v>101</v>
+      </c>
+      <c r="AB82" s="2">
         <v>88</v>
       </c>
-      <c r="AB82" s="2">
+      <c r="AC82" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="83" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
         <v>80</v>
       </c>
       <c r="B83" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>425</v>
       </c>
       <c r="C83" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>242</v>
       </c>
       <c r="D83" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>10680</v>
       </c>
       <c r="E83" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>168</v>
       </c>
       <c r="F83" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="G83" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>10</v>
       </c>
       <c r="H83" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>10</v>
       </c>
       <c r="I83" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>10</v>
       </c>
       <c r="J83" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>10</v>
       </c>
       <c r="K83" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>10</v>
       </c>
       <c r="L83" s="2">
@@ -8584,7 +8915,7 @@
         <v>0</v>
       </c>
       <c r="R83" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>100</v>
       </c>
       <c r="S83" s="2">
@@ -8612,54 +8943,58 @@
         <v>1020</v>
       </c>
       <c r="AA83" s="2">
+        <f t="shared" si="26"/>
+        <v>102</v>
+      </c>
+      <c r="AB83" s="2">
         <v>89</v>
       </c>
-      <c r="AB83" s="2">
+      <c r="AC83" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="84" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
         <v>81</v>
       </c>
       <c r="B84" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>430</v>
       </c>
       <c r="C84" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>245</v>
       </c>
       <c r="D84" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>10800</v>
       </c>
       <c r="E84" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>170</v>
       </c>
       <c r="F84" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="G84" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>10</v>
       </c>
       <c r="H84" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>10</v>
       </c>
       <c r="I84" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>10</v>
       </c>
       <c r="J84" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>10</v>
       </c>
       <c r="K84" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>10</v>
       </c>
       <c r="L84" s="2">
@@ -8681,7 +9016,7 @@
         <v>0</v>
       </c>
       <c r="R84" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>100</v>
       </c>
       <c r="S84" s="2">
@@ -8709,54 +9044,58 @@
         <v>1001</v>
       </c>
       <c r="AA84" s="2">
+        <f t="shared" si="26"/>
+        <v>103</v>
+      </c>
+      <c r="AB84" s="2">
         <v>90</v>
       </c>
-      <c r="AB84" s="2">
+      <c r="AC84" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="85" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
         <v>82</v>
       </c>
       <c r="B85" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>435</v>
       </c>
       <c r="C85" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>248</v>
       </c>
       <c r="D85" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>10920</v>
       </c>
       <c r="E85" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>172</v>
       </c>
       <c r="F85" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="G85" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>10</v>
       </c>
       <c r="H85" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>10</v>
       </c>
       <c r="I85" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>10</v>
       </c>
       <c r="J85" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>10</v>
       </c>
       <c r="K85" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>10</v>
       </c>
       <c r="L85" s="2">
@@ -8778,7 +9117,7 @@
         <v>0</v>
       </c>
       <c r="R85" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>100</v>
       </c>
       <c r="S85" s="2">
@@ -8806,54 +9145,58 @@
         <v>1002</v>
       </c>
       <c r="AA85" s="2">
+        <f t="shared" si="26"/>
+        <v>101</v>
+      </c>
+      <c r="AB85" s="2">
         <v>91</v>
       </c>
-      <c r="AB85" s="2">
+      <c r="AC85" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="86" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
         <v>83</v>
       </c>
       <c r="B86" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>440</v>
       </c>
       <c r="C86" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>251</v>
       </c>
       <c r="D86" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>11040</v>
       </c>
       <c r="E86" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>174</v>
       </c>
       <c r="F86" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="G86" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>10</v>
       </c>
       <c r="H86" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>10</v>
       </c>
       <c r="I86" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>10</v>
       </c>
       <c r="J86" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>10</v>
       </c>
       <c r="K86" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>10</v>
       </c>
       <c r="L86" s="2">
@@ -8875,7 +9218,7 @@
         <v>0</v>
       </c>
       <c r="R86" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>100</v>
       </c>
       <c r="S86" s="2">
@@ -8903,54 +9246,58 @@
         <v>1003</v>
       </c>
       <c r="AA86" s="2">
+        <f t="shared" si="26"/>
+        <v>102</v>
+      </c>
+      <c r="AB86" s="2">
         <v>92</v>
       </c>
-      <c r="AB86" s="2">
+      <c r="AC86" s="2">
         <v>83</v>
       </c>
     </row>
-    <row r="87" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
         <v>84</v>
       </c>
       <c r="B87" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>445</v>
       </c>
       <c r="C87" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>254</v>
       </c>
       <c r="D87" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>11160</v>
       </c>
       <c r="E87" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>176</v>
       </c>
       <c r="F87" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="G87" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>10</v>
       </c>
       <c r="H87" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>10</v>
       </c>
       <c r="I87" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>10</v>
       </c>
       <c r="J87" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>10</v>
       </c>
       <c r="K87" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>10</v>
       </c>
       <c r="L87" s="2">
@@ -8972,7 +9319,7 @@
         <v>0</v>
       </c>
       <c r="R87" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>100</v>
       </c>
       <c r="S87" s="2">
@@ -9000,54 +9347,58 @@
         <v>1004</v>
       </c>
       <c r="AA87" s="2">
+        <f t="shared" si="26"/>
+        <v>103</v>
+      </c>
+      <c r="AB87" s="2">
         <v>93</v>
       </c>
-      <c r="AB87" s="2">
+      <c r="AC87" s="2">
         <v>84</v>
       </c>
     </row>
-    <row r="88" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
         <v>85</v>
       </c>
       <c r="B88" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>450</v>
       </c>
       <c r="C88" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>257</v>
       </c>
       <c r="D88" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>11280</v>
       </c>
       <c r="E88" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>178</v>
       </c>
       <c r="F88" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="G88" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>10</v>
       </c>
       <c r="H88" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>10</v>
       </c>
       <c r="I88" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>10</v>
       </c>
       <c r="J88" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>10</v>
       </c>
       <c r="K88" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>10</v>
       </c>
       <c r="L88" s="2">
@@ -9069,7 +9420,7 @@
         <v>0</v>
       </c>
       <c r="R88" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>100</v>
       </c>
       <c r="S88" s="2">
@@ -9097,54 +9448,58 @@
         <v>1005</v>
       </c>
       <c r="AA88" s="2">
+        <f t="shared" si="26"/>
+        <v>101</v>
+      </c>
+      <c r="AB88" s="2">
         <v>94</v>
       </c>
-      <c r="AB88" s="2">
+      <c r="AC88" s="2">
         <v>85</v>
       </c>
     </row>
-    <row r="89" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
         <v>86</v>
       </c>
       <c r="B89" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>455</v>
       </c>
       <c r="C89" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>260</v>
       </c>
       <c r="D89" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>11400</v>
       </c>
       <c r="E89" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>180</v>
       </c>
       <c r="F89" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="G89" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>10</v>
       </c>
       <c r="H89" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>10</v>
       </c>
       <c r="I89" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>10</v>
       </c>
       <c r="J89" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>10</v>
       </c>
       <c r="K89" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>10</v>
       </c>
       <c r="L89" s="2">
@@ -9166,7 +9521,7 @@
         <v>0</v>
       </c>
       <c r="R89" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>100</v>
       </c>
       <c r="S89" s="2">
@@ -9194,54 +9549,58 @@
         <v>1006</v>
       </c>
       <c r="AA89" s="2">
+        <f t="shared" si="26"/>
+        <v>102</v>
+      </c>
+      <c r="AB89" s="2">
         <v>95</v>
       </c>
-      <c r="AB89" s="2">
+      <c r="AC89" s="2">
         <v>86</v>
       </c>
     </row>
-    <row r="90" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
         <v>87</v>
       </c>
       <c r="B90" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>460</v>
       </c>
       <c r="C90" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>263</v>
       </c>
       <c r="D90" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>11520</v>
       </c>
       <c r="E90" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>182</v>
       </c>
       <c r="F90" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="G90" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>10</v>
       </c>
       <c r="H90" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>10</v>
       </c>
       <c r="I90" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>10</v>
       </c>
       <c r="J90" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>10</v>
       </c>
       <c r="K90" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>10</v>
       </c>
       <c r="L90" s="2">
@@ -9263,7 +9622,7 @@
         <v>0</v>
       </c>
       <c r="R90" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>100</v>
       </c>
       <c r="S90" s="2">
@@ -9291,54 +9650,58 @@
         <v>1007</v>
       </c>
       <c r="AA90" s="2">
+        <f t="shared" si="26"/>
+        <v>103</v>
+      </c>
+      <c r="AB90" s="2">
         <v>96</v>
       </c>
-      <c r="AB90" s="2">
+      <c r="AC90" s="2">
         <v>87</v>
       </c>
     </row>
-    <row r="91" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
         <v>88</v>
       </c>
       <c r="B91" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>465</v>
       </c>
       <c r="C91" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>266</v>
       </c>
       <c r="D91" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>11640</v>
       </c>
       <c r="E91" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>184</v>
       </c>
       <c r="F91" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="G91" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>10</v>
       </c>
       <c r="H91" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>10</v>
       </c>
       <c r="I91" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>10</v>
       </c>
       <c r="J91" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>10</v>
       </c>
       <c r="K91" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>10</v>
       </c>
       <c r="L91" s="2">
@@ -9360,7 +9723,7 @@
         <v>0</v>
       </c>
       <c r="R91" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>100</v>
       </c>
       <c r="S91" s="2">
@@ -9388,54 +9751,58 @@
         <v>1008</v>
       </c>
       <c r="AA91" s="2">
+        <f t="shared" si="26"/>
+        <v>101</v>
+      </c>
+      <c r="AB91" s="2">
         <v>97</v>
       </c>
-      <c r="AB91" s="2">
+      <c r="AC91" s="2">
         <v>88</v>
       </c>
     </row>
-    <row r="92" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
         <v>89</v>
       </c>
       <c r="B92" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>470</v>
       </c>
       <c r="C92" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>269</v>
       </c>
       <c r="D92" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>11760</v>
       </c>
       <c r="E92" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>186</v>
       </c>
       <c r="F92" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="G92" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>10</v>
       </c>
       <c r="H92" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>10</v>
       </c>
       <c r="I92" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>10</v>
       </c>
       <c r="J92" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>10</v>
       </c>
       <c r="K92" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>10</v>
       </c>
       <c r="L92" s="2">
@@ -9457,7 +9824,7 @@
         <v>0</v>
       </c>
       <c r="R92" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>100</v>
       </c>
       <c r="S92" s="2">
@@ -9485,54 +9852,58 @@
         <v>1009</v>
       </c>
       <c r="AA92" s="2">
+        <f t="shared" si="26"/>
+        <v>102</v>
+      </c>
+      <c r="AB92" s="2">
         <v>98</v>
       </c>
-      <c r="AB92" s="2">
+      <c r="AC92" s="2">
         <v>89</v>
       </c>
     </row>
-    <row r="93" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
         <v>90</v>
       </c>
       <c r="B93" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>475</v>
       </c>
       <c r="C93" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>272</v>
       </c>
       <c r="D93" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>11880</v>
       </c>
       <c r="E93" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>188</v>
       </c>
       <c r="F93" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="G93" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>10</v>
       </c>
       <c r="H93" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>10</v>
       </c>
       <c r="I93" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>10</v>
       </c>
       <c r="J93" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>10</v>
       </c>
       <c r="K93" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>10</v>
       </c>
       <c r="L93" s="2">
@@ -9554,7 +9925,7 @@
         <v>0</v>
       </c>
       <c r="R93" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>100</v>
       </c>
       <c r="S93" s="2">
@@ -9582,54 +9953,58 @@
         <v>1010</v>
       </c>
       <c r="AA93" s="2">
+        <f t="shared" si="26"/>
+        <v>103</v>
+      </c>
+      <c r="AB93" s="2">
         <v>99</v>
       </c>
-      <c r="AB93" s="2">
+      <c r="AC93" s="2">
         <v>90</v>
       </c>
     </row>
-    <row r="94" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
         <v>91</v>
       </c>
       <c r="B94" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>480</v>
       </c>
       <c r="C94" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>275</v>
       </c>
       <c r="D94" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>12000</v>
       </c>
       <c r="E94" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>190</v>
       </c>
       <c r="F94" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="G94" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>10</v>
       </c>
       <c r="H94" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>10</v>
       </c>
       <c r="I94" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>10</v>
       </c>
       <c r="J94" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>10</v>
       </c>
       <c r="K94" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>10</v>
       </c>
       <c r="L94" s="2">
@@ -9651,7 +10026,7 @@
         <v>0</v>
       </c>
       <c r="R94" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>100</v>
       </c>
       <c r="S94" s="2">
@@ -9679,54 +10054,58 @@
         <v>1011</v>
       </c>
       <c r="AA94" s="2">
+        <f t="shared" si="26"/>
+        <v>101</v>
+      </c>
+      <c r="AB94" s="2">
         <v>100</v>
       </c>
-      <c r="AB94" s="2">
+      <c r="AC94" s="2">
         <v>91</v>
       </c>
     </row>
-    <row r="95" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
         <v>92</v>
       </c>
       <c r="B95" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>485</v>
       </c>
       <c r="C95" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>278</v>
       </c>
       <c r="D95" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>12120</v>
       </c>
       <c r="E95" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>192</v>
       </c>
       <c r="F95" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="G95" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>10</v>
       </c>
       <c r="H95" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>10</v>
       </c>
       <c r="I95" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>10</v>
       </c>
       <c r="J95" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>10</v>
       </c>
       <c r="K95" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>10</v>
       </c>
       <c r="L95" s="2">
@@ -9748,7 +10127,7 @@
         <v>0</v>
       </c>
       <c r="R95" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>100</v>
       </c>
       <c r="S95" s="2">
@@ -9776,54 +10155,58 @@
         <v>1012</v>
       </c>
       <c r="AA95" s="2">
+        <f t="shared" si="26"/>
+        <v>102</v>
+      </c>
+      <c r="AB95" s="2">
         <v>101</v>
       </c>
-      <c r="AB95" s="2">
+      <c r="AC95" s="2">
         <v>92</v>
       </c>
     </row>
-    <row r="96" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
         <v>93</v>
       </c>
       <c r="B96" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>490</v>
       </c>
       <c r="C96" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>281</v>
       </c>
       <c r="D96" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>12240</v>
       </c>
       <c r="E96" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>194</v>
       </c>
       <c r="F96" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="G96" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>10</v>
       </c>
       <c r="H96" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>10</v>
       </c>
       <c r="I96" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>10</v>
       </c>
       <c r="J96" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>10</v>
       </c>
       <c r="K96" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>10</v>
       </c>
       <c r="L96" s="2">
@@ -9845,7 +10228,7 @@
         <v>0</v>
       </c>
       <c r="R96" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>100</v>
       </c>
       <c r="S96" s="2">
@@ -9873,54 +10256,58 @@
         <v>1013</v>
       </c>
       <c r="AA96" s="2">
+        <f t="shared" si="26"/>
+        <v>103</v>
+      </c>
+      <c r="AB96" s="2">
         <v>102</v>
       </c>
-      <c r="AB96" s="2">
+      <c r="AC96" s="2">
         <v>93</v>
       </c>
     </row>
-    <row r="97" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
         <v>94</v>
       </c>
       <c r="B97" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>495</v>
       </c>
       <c r="C97" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>284</v>
       </c>
       <c r="D97" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>12360</v>
       </c>
       <c r="E97" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>196</v>
       </c>
       <c r="F97" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="G97" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>10</v>
       </c>
       <c r="H97" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>10</v>
       </c>
       <c r="I97" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>10</v>
       </c>
       <c r="J97" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>10</v>
       </c>
       <c r="K97" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>10</v>
       </c>
       <c r="L97" s="2">
@@ -9942,7 +10329,7 @@
         <v>0</v>
       </c>
       <c r="R97" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>100</v>
       </c>
       <c r="S97" s="2">
@@ -9970,54 +10357,58 @@
         <v>1014</v>
       </c>
       <c r="AA97" s="2">
+        <f t="shared" si="26"/>
+        <v>101</v>
+      </c>
+      <c r="AB97" s="2">
         <v>103</v>
       </c>
-      <c r="AB97" s="2">
+      <c r="AC97" s="2">
         <v>94</v>
       </c>
     </row>
-    <row r="98" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
         <v>95</v>
       </c>
       <c r="B98" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>500</v>
       </c>
       <c r="C98" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>287</v>
       </c>
       <c r="D98" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>12480</v>
       </c>
       <c r="E98" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>198</v>
       </c>
       <c r="F98" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="G98" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>10</v>
       </c>
       <c r="H98" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>10</v>
       </c>
       <c r="I98" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>10</v>
       </c>
       <c r="J98" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>10</v>
       </c>
       <c r="K98" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>10</v>
       </c>
       <c r="L98" s="2">
@@ -10039,7 +10430,7 @@
         <v>0</v>
       </c>
       <c r="R98" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>100</v>
       </c>
       <c r="S98" s="2">
@@ -10067,54 +10458,58 @@
         <v>1015</v>
       </c>
       <c r="AA98" s="2">
+        <f t="shared" si="26"/>
+        <v>102</v>
+      </c>
+      <c r="AB98" s="2">
         <v>104</v>
       </c>
-      <c r="AB98" s="2">
+      <c r="AC98" s="2">
         <v>95</v>
       </c>
     </row>
-    <row r="99" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
         <v>96</v>
       </c>
       <c r="B99" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>505</v>
       </c>
       <c r="C99" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>290</v>
       </c>
       <c r="D99" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>12600</v>
       </c>
       <c r="E99" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>200</v>
       </c>
       <c r="F99" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="G99" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>10</v>
       </c>
       <c r="H99" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>10</v>
       </c>
       <c r="I99" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>10</v>
       </c>
       <c r="J99" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>10</v>
       </c>
       <c r="K99" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>10</v>
       </c>
       <c r="L99" s="2">
@@ -10136,7 +10531,7 @@
         <v>0</v>
       </c>
       <c r="R99" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>100</v>
       </c>
       <c r="S99" s="2">
@@ -10164,54 +10559,58 @@
         <v>1016</v>
       </c>
       <c r="AA99" s="2">
+        <f t="shared" si="26"/>
+        <v>103</v>
+      </c>
+      <c r="AB99" s="2">
         <v>105</v>
       </c>
-      <c r="AB99" s="2">
+      <c r="AC99" s="2">
         <v>96</v>
       </c>
     </row>
-    <row r="100" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
         <v>97</v>
       </c>
       <c r="B100" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>510</v>
       </c>
       <c r="C100" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>293</v>
       </c>
       <c r="D100" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>12720</v>
       </c>
       <c r="E100" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>202</v>
       </c>
       <c r="F100" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="G100" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>10</v>
       </c>
       <c r="H100" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>10</v>
       </c>
       <c r="I100" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>10</v>
       </c>
       <c r="J100" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>10</v>
       </c>
       <c r="K100" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>10</v>
       </c>
       <c r="L100" s="2">
@@ -10233,7 +10632,7 @@
         <v>0</v>
       </c>
       <c r="R100" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>100</v>
       </c>
       <c r="S100" s="2">
@@ -10261,54 +10660,58 @@
         <v>1017</v>
       </c>
       <c r="AA100" s="2">
+        <f t="shared" si="26"/>
+        <v>101</v>
+      </c>
+      <c r="AB100" s="2">
         <v>106</v>
       </c>
-      <c r="AB100" s="2">
+      <c r="AC100" s="2">
         <v>97</v>
       </c>
     </row>
-    <row r="101" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
         <v>98</v>
       </c>
       <c r="B101" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>515</v>
       </c>
       <c r="C101" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>296</v>
       </c>
       <c r="D101" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>12840</v>
       </c>
       <c r="E101" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>204</v>
       </c>
       <c r="F101" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="G101" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>10</v>
       </c>
       <c r="H101" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>10</v>
       </c>
       <c r="I101" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>10</v>
       </c>
       <c r="J101" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>10</v>
       </c>
       <c r="K101" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>10</v>
       </c>
       <c r="L101" s="2">
@@ -10330,7 +10733,7 @@
         <v>0</v>
       </c>
       <c r="R101" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>100</v>
       </c>
       <c r="S101" s="2">
@@ -10358,54 +10761,58 @@
         <v>1018</v>
       </c>
       <c r="AA101" s="2">
+        <f t="shared" si="26"/>
+        <v>102</v>
+      </c>
+      <c r="AB101" s="2">
         <v>107</v>
       </c>
-      <c r="AB101" s="2">
+      <c r="AC101" s="2">
         <v>98</v>
       </c>
     </row>
-    <row r="102" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
         <v>99</v>
       </c>
       <c r="B102" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>520</v>
       </c>
       <c r="C102" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>299</v>
       </c>
       <c r="D102" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>12960</v>
       </c>
       <c r="E102" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>206</v>
       </c>
       <c r="F102" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="G102" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>10</v>
       </c>
       <c r="H102" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>10</v>
       </c>
       <c r="I102" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>10</v>
       </c>
       <c r="J102" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>10</v>
       </c>
       <c r="K102" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>10</v>
       </c>
       <c r="L102" s="2">
@@ -10427,7 +10834,7 @@
         <v>0</v>
       </c>
       <c r="R102" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>100</v>
       </c>
       <c r="S102" s="2">
@@ -10455,54 +10862,58 @@
         <v>1019</v>
       </c>
       <c r="AA102" s="2">
+        <f t="shared" si="26"/>
+        <v>103</v>
+      </c>
+      <c r="AB102" s="2">
         <v>108</v>
       </c>
-      <c r="AB102" s="2">
+      <c r="AC102" s="2">
         <v>99</v>
       </c>
     </row>
-    <row r="103" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
         <v>100</v>
       </c>
       <c r="B103" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>525</v>
       </c>
       <c r="C103" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>302</v>
       </c>
       <c r="D103" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>13080</v>
       </c>
       <c r="E103" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>208</v>
       </c>
       <c r="F103" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="G103" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>10</v>
       </c>
       <c r="H103" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>10</v>
       </c>
       <c r="I103" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>10</v>
       </c>
       <c r="J103" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>10</v>
       </c>
       <c r="K103" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>10</v>
       </c>
       <c r="L103" s="2">
@@ -10524,7 +10935,7 @@
         <v>0</v>
       </c>
       <c r="R103" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>100</v>
       </c>
       <c r="S103" s="2">
@@ -10552,9 +10963,13 @@
         <v>1020</v>
       </c>
       <c r="AA103" s="2">
+        <f t="shared" si="26"/>
+        <v>101</v>
+      </c>
+      <c r="AB103" s="2">
         <v>109</v>
       </c>
-      <c r="AB103" s="2">
+      <c r="AC103" s="2">
         <v>100</v>
       </c>
     </row>
